--- a/data/vessels/2026-10-17.xlsx
+++ b/data/vessels/2026-10-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="432062" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B5FC67B0-7EA0-4876-8826-4D4AEF3BA72D}"/>
+  <xr:revisionPtr revIDLastSave="432595" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4C4B9DE-6CA5-4A61-A8E7-86E46600545C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1026" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="238">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,6 +83,27 @@
     <t>T18</t>
   </si>
   <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>CMA CGM BYBLOS</t>
+  </si>
+  <si>
+    <t>CPN00/CPN01</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
     <t>EB Service 2</t>
   </si>
   <si>
@@ -98,30 +119,9 @@
     <t>Talon Marine Services LLC</t>
   </si>
   <si>
-    <t>Container</t>
-  </si>
-  <si>
     <t>In transit</t>
   </si>
   <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
     <t>Tacoma</t>
   </si>
   <si>
@@ -212,6 +212,15 @@
     <t>MSC</t>
   </si>
   <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
     <t>THEMISA</t>
   </si>
   <si>
@@ -221,13 +230,13 @@
     <t>Wallenius</t>
   </si>
   <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
   </si>
   <si>
     <t>FP2</t>
@@ -236,15 +245,6 @@
     <t>ONE OWL</t>
   </si>
   <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
     <t>MODERN LINK</t>
   </si>
   <si>
@@ -269,6 +269,12 @@
     <t>BEN LINES</t>
   </si>
   <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
     <t>WUT</t>
   </si>
   <si>
@@ -284,10 +290,13 @@
     <t>Yang Ming</t>
   </si>
   <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
   </si>
   <si>
     <t>T7</t>
@@ -296,15 +305,6 @@
     <t>THEMIS LEADER</t>
   </si>
   <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -539,16 +539,22 @@
     <t>OYNT0002E</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>NBBT0001E</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK643R</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>NBBT0001E</t>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
   </si>
   <si>
     <t>LAVENDER ACE</t>
@@ -557,12 +563,6 @@
     <t>123A</t>
   </si>
   <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
-  </si>
-  <si>
     <t>MANULANI</t>
   </si>
   <si>
@@ -632,6 +632,9 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>GLOVIS LEGEND</t>
   </si>
   <si>
@@ -642,9 +645,6 @@
   </si>
   <si>
     <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -825,10 +825,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L123" totalsRowShown="0">
-  <autoFilter ref="A1:L123" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L123">
-    <sortCondition ref="J2:J123"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L128" totalsRowShown="0">
+  <autoFilter ref="A1:L128" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L128">
+    <sortCondition ref="J2:J128"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1165,7 +1165,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L123"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1365,7 +1365,7 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>29</v>
@@ -1377,7 +1377,7 @@
         <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
         <v>32</v>
@@ -1392,42 +1392,42 @@
         <v>46312.666666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="J7" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.125</v>
       </c>
       <c r="K7" s="2">
-        <v>46313.166666666664</v>
+        <v>46312.666666666664</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -1435,37 +1435,40 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="H8" t="s">
+        <v>32</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="2">
-        <v>46312.3125</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K8" s="2">
-        <v>46314.75</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1476,66 +1479,69 @@
         <v>13</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
+        <v>32</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="2">
-        <v>46312.541666666664</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K9" s="2">
-        <v>46314.791666666664</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G10" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="2">
-        <v>46313.208333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K10" s="2">
-        <v>46314.208333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1543,66 +1549,66 @@
         <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>17</v>
       </c>
       <c r="G11" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46313.25</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K11" s="2">
-        <v>46314.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I12" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46314.25</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46314.75</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L12" t="s">
         <v>26</v>
@@ -1610,31 +1616,31 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F13" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I13" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46314.25</v>
+        <v>46313.25</v>
       </c>
       <c r="K13" s="2">
         <v>46314.75</v>
@@ -1648,31 +1654,31 @@
         <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
-      </c>
-      <c r="E14" s="1">
-        <v>34</v>
+        <v>57</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>58</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J14" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K14" s="2">
-        <v>46318.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L14" t="s">
         <v>20</v>
@@ -1680,34 +1686,34 @@
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C15" t="s">
+        <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F15" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J15" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K15" s="2">
-        <v>46315.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
@@ -1715,34 +1721,34 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="1">
-        <v>2</v>
+        <v>63</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F16" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H16" t="s">
+        <v>32</v>
       </c>
       <c r="I16" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J16" s="2">
-        <v>46315.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K16" s="2">
-        <v>46315.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L16" t="s">
         <v>26</v>
@@ -1753,34 +1759,34 @@
         <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="E17" s="1">
+        <v>34</v>
       </c>
       <c r="F17" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="G17" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
         <v>19</v>
       </c>
       <c r="J17" s="2">
-        <v>46315.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K17" s="2">
-        <v>46317.166666666664</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1788,31 +1794,31 @@
         <v>27</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C18" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
+      </c>
+      <c r="E18" s="1">
+        <v>2</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="G18" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J18" s="2">
-        <v>46315.666666666664</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46317.75</v>
+        <v>46315.75</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -1820,69 +1826,69 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="G19" t="s">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>46315.666666666664</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K19" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C20" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D20" t="s">
-        <v>84</v>
-      </c>
-      <c r="E20" s="1">
-        <v>63</v>
+        <v>76</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G20" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46316.25</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K20" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L20" t="s">
         <v>26</v>
@@ -1893,34 +1899,31 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D21" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="I21" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J21" s="2">
-        <v>46316.25</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K21" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -1931,34 +1934,34 @@
         <v>27</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F22" t="s">
-        <v>92</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
       <c r="H22" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J22" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K22" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L22" t="s">
         <v>20</v>
@@ -1969,31 +1972,31 @@
         <v>27</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>93</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>94</v>
+        <v>87</v>
+      </c>
+      <c r="E23" s="1">
+        <v>63</v>
       </c>
       <c r="F23" t="s">
-        <v>95</v>
+        <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J23" s="2">
-        <v>46316.625</v>
+        <v>46316.25</v>
       </c>
       <c r="K23" s="2">
-        <v>46319.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
@@ -2004,34 +2007,37 @@
         <v>27</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>89</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="G24" t="s">
-        <v>25</v>
+        <v>92</v>
+      </c>
+      <c r="H24" t="s">
+        <v>32</v>
       </c>
       <c r="I24" t="s">
         <v>19</v>
       </c>
       <c r="J24" s="2">
-        <v>46316.625</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46319.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:12">
@@ -2039,37 +2045,34 @@
         <v>27</v>
       </c>
       <c r="B25" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
-      </c>
-      <c r="E25" s="1">
-        <v>26169</v>
+        <v>93</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G25" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J25" s="2">
         <v>46316.625</v>
       </c>
       <c r="K25" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26" spans="1:12">
@@ -2077,34 +2080,31 @@
         <v>27</v>
       </c>
       <c r="B26" t="s">
-        <v>83</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D26" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F26" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
-      </c>
-      <c r="H26" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
       <c r="I26" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K26" s="2">
-        <v>46317.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L26" t="s">
         <v>26</v>
@@ -2115,60 +2115,72 @@
         <v>27</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>103</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>104</v>
+        <v>98</v>
+      </c>
+      <c r="E27" s="1">
+        <v>26169</v>
       </c>
       <c r="F27" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>100</v>
+      </c>
+      <c r="H27" t="s">
+        <v>100</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="J27" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K27" s="2">
-        <v>46318.708333333336</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>52</v>
+        <v>86</v>
       </c>
       <c r="C28" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>107</v>
+        <v>83</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
+        <v>62</v>
+      </c>
+      <c r="G28" t="s">
+        <v>18</v>
+      </c>
+      <c r="H28" t="s">
+        <v>85</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J28" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46318.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L28" t="s">
         <v>20</v>
@@ -2179,31 +2191,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C29" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
+        <v>103</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="F29" t="s">
-        <v>110</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="I29" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46317.541666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K29" s="2">
-        <v>46320.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L29" t="s">
         <v>26</v>
@@ -2211,34 +2220,31 @@
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D30" t="s">
-        <v>109</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
+        <v>107</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>108</v>
       </c>
       <c r="F30" t="s">
-        <v>110</v>
-      </c>
-      <c r="G30" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I30" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J30" s="2">
-        <v>46317.541666666664</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46320.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L30" t="s">
         <v>26</v>
@@ -2246,31 +2252,34 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C31" t="s">
-        <v>111</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>113</v>
+        <v>109</v>
+      </c>
+      <c r="E31" s="1">
+        <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>110</v>
+      </c>
+      <c r="G31" t="s">
+        <v>18</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J31" s="2">
-        <v>46317.927777777775</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K31" s="2">
-        <v>46318.969444444447</v>
+        <v>46320.75</v>
       </c>
       <c r="L31" t="s">
         <v>20</v>
@@ -2281,66 +2290,63 @@
         <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>114</v>
+        <v>109</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="G32" t="s">
-        <v>92</v>
-      </c>
-      <c r="H32" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J32" s="2">
-        <v>46318.104166666664</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K32" s="2">
-        <v>46318.916666666664</v>
+        <v>46320.75</v>
       </c>
       <c r="L32" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="D33" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F33" t="s">
-        <v>31</v>
-      </c>
-      <c r="G33" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I33" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46318.25</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K33" s="2">
-        <v>46318.75</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -2348,25 +2354,22 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B34" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="C34" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="G34" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="H34" t="s">
         <v>32</v>
@@ -2375,10 +2378,10 @@
         <v>19</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.25</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K34" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L34" t="s">
         <v>20</v>
@@ -2389,34 +2392,31 @@
         <v>27</v>
       </c>
       <c r="B35" t="s">
-        <v>88</v>
+        <v>28</v>
       </c>
       <c r="C35" t="s">
-        <v>119</v>
+        <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="F35" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>92</v>
-      </c>
-      <c r="H35" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J35" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46319.125</v>
+        <v>46318.75</v>
       </c>
       <c r="L35" t="s">
         <v>20</v>
@@ -2424,40 +2424,40 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="C36" t="s">
-        <v>122</v>
+        <v>34</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
-      </c>
-      <c r="E36" s="1">
-        <v>26168</v>
+        <v>117</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="F36" t="s">
-        <v>99</v>
+        <v>37</v>
       </c>
       <c r="G36" t="s">
-        <v>100</v>
+        <v>38</v>
       </c>
       <c r="H36" t="s">
-        <v>100</v>
+        <v>32</v>
       </c>
       <c r="I36" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46318.625</v>
+        <v>46318.25</v>
       </c>
       <c r="K36" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L36" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
     </row>
     <row r="37" spans="1:12">
@@ -2468,10 +2468,10 @@
         <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="D37" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>121</v>
@@ -2479,17 +2479,23 @@
       <c r="F37" t="s">
         <v>92</v>
       </c>
+      <c r="G37" t="s">
+        <v>92</v>
+      </c>
+      <c r="H37" t="s">
+        <v>32</v>
+      </c>
       <c r="I37" t="s">
         <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K37" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.125</v>
       </c>
       <c r="L37" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
@@ -2497,34 +2503,37 @@
         <v>27</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>21</v>
+        <v>122</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E38" s="1">
-        <v>4</v>
+        <v>26168</v>
       </c>
       <c r="F38" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="G38" t="s">
-        <v>25</v>
+        <v>100</v>
+      </c>
+      <c r="H38" t="s">
+        <v>100</v>
       </c>
       <c r="I38" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="J38" s="2">
-        <v>46319.208333333336</v>
+        <v>46318.625</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.75</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>26</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="1:12">
@@ -2532,31 +2541,28 @@
         <v>27</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F39" t="s">
-        <v>59</v>
-      </c>
-      <c r="G39" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="I39" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46319.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -2567,69 +2573,66 @@
         <v>27</v>
       </c>
       <c r="B40" t="s">
-        <v>83</v>
+        <v>28</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>129</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>130</v>
+        <v>126</v>
+      </c>
+      <c r="E40" s="1">
+        <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="G40" t="s">
-        <v>38</v>
-      </c>
-      <c r="H40" t="s">
-        <v>132</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J40" s="2">
-        <v>46319.25</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K40" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C41" t="s">
+        <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>133</v>
-      </c>
-      <c r="E41" s="1" t="s">
-        <v>66</v>
+        <v>126</v>
+      </c>
+      <c r="E41" s="1">
+        <v>4</v>
       </c>
       <c r="F41" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
-      </c>
-      <c r="H41" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J41" s="2">
-        <v>46319.625</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K41" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L41" t="s">
         <v>20</v>
@@ -2640,31 +2643,31 @@
         <v>27</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C42" t="s">
-        <v>134</v>
+        <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F42" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="G42" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J42" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.25</v>
       </c>
       <c r="K42" s="2">
-        <v>46321.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L42" t="s">
         <v>20</v>
@@ -2675,28 +2678,34 @@
         <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C43" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="F43" t="s">
-        <v>74</v>
+        <v>131</v>
+      </c>
+      <c r="G43" t="s">
+        <v>38</v>
+      </c>
+      <c r="H43" t="s">
+        <v>132</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J43" s="2">
-        <v>46320</v>
+        <v>46319.25</v>
       </c>
       <c r="K43" s="2">
-        <v>46322</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L43" t="s">
         <v>20</v>
@@ -2709,198 +2718,195 @@
       <c r="B44" t="s">
         <v>13</v>
       </c>
-      <c r="C44" t="s">
-        <v>44</v>
-      </c>
       <c r="D44" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="F44" t="s">
-        <v>24</v>
+        <v>65</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" t="s">
+        <v>32</v>
       </c>
       <c r="I44" t="s">
         <v>19</v>
       </c>
       <c r="J44" s="2">
-        <v>46320.21875</v>
+        <v>46319.625</v>
       </c>
       <c r="K44" s="2">
-        <v>46324.59375</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L44" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C45" t="s">
-        <v>47</v>
+        <v>134</v>
       </c>
       <c r="D45" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="F45" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="G45" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46321.208333333336</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K45" s="2">
-        <v>46322.166666666664</v>
+        <v>46321.75</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C46" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D46" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="F46" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46321.21875</v>
+        <v>46320</v>
       </c>
       <c r="K46" s="2">
-        <v>46323.21875</v>
+        <v>46322</v>
       </c>
       <c r="L46" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>76</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="D47" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="F47" t="s">
-        <v>80</v>
-      </c>
-      <c r="G47" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46321.25</v>
+        <v>46320.21875</v>
       </c>
       <c r="K47" s="2">
-        <v>46323.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L47" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="D48" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="1">
-        <v>21</v>
+        <v>141</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="F48" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="G48" t="s">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.625</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K48" s="2">
-        <v>46325.75</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L48" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>149</v>
+        <v>143</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="F49" t="s">
-        <v>131</v>
-      </c>
-      <c r="G49" t="s">
-        <v>38</v>
-      </c>
-      <c r="H49" t="s">
-        <v>132</v>
+        <v>56</v>
       </c>
       <c r="I49" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46322.25</v>
+        <v>46321.21875</v>
       </c>
       <c r="K49" s="2">
-        <v>46322.75</v>
+        <v>46323.21875</v>
       </c>
       <c r="L49" t="s">
         <v>26</v>
@@ -2911,34 +2917,34 @@
         <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C50" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="D50" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F50" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46322.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K50" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L50" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2946,31 +2952,31 @@
         <v>27</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C51" t="s">
+        <v>66</v>
+      </c>
+      <c r="D51" t="s">
+        <v>147</v>
+      </c>
+      <c r="E51" s="1">
         <v>21</v>
       </c>
-      <c r="D51" t="s">
-        <v>152</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>153</v>
-      </c>
       <c r="F51" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I51" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46323.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L51" t="s">
         <v>26</v>
@@ -2981,28 +2987,34 @@
         <v>27</v>
       </c>
       <c r="B52" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="C52" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="D52" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="F52" t="s">
-        <v>92</v>
+        <v>131</v>
+      </c>
+      <c r="G52" t="s">
+        <v>38</v>
+      </c>
+      <c r="H52" t="s">
+        <v>132</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J52" s="2">
-        <v>46323.291666666664</v>
+        <v>46322.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46323.791666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L52" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53" spans="1:12">
@@ -3010,37 +3022,34 @@
         <v>27</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>39</v>
       </c>
       <c r="C53" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="D53" t="s">
-        <v>98</v>
-      </c>
-      <c r="E53" s="1">
-        <v>26173</v>
+        <v>150</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>151</v>
       </c>
       <c r="F53" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="G53" t="s">
-        <v>100</v>
-      </c>
-      <c r="H53" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="I53" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46323.625</v>
+        <v>46322.625</v>
       </c>
       <c r="K53" s="2">
-        <v>46324.041666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L53" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3048,10 +3057,10 @@
         <v>27</v>
       </c>
       <c r="B54" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="C54" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D54" t="s">
         <v>152</v>
@@ -3063,19 +3072,19 @@
         <v>31</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K54" s="2">
-        <v>46324.75</v>
+        <v>46323.75</v>
       </c>
       <c r="L54" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3083,25 +3092,25 @@
         <v>27</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>88</v>
+      </c>
+      <c r="C55" t="s">
+        <v>89</v>
       </c>
       <c r="D55" t="s">
-        <v>155</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F55" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="I55" t="s">
         <v>19</v>
       </c>
       <c r="J55" s="2">
-        <v>46324</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46326</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L55" t="s">
         <v>20</v>
@@ -3109,63 +3118,72 @@
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>157</v>
+        <v>97</v>
       </c>
       <c r="D56" t="s">
-        <v>158</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>159</v>
+        <v>98</v>
+      </c>
+      <c r="E56" s="1">
+        <v>26173</v>
       </c>
       <c r="F56" t="s">
-        <v>24</v>
+        <v>99</v>
+      </c>
+      <c r="G56" t="s">
+        <v>100</v>
+      </c>
+      <c r="H56" t="s">
+        <v>100</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="J56" s="2">
-        <v>46324.647916666669</v>
+        <v>46323.625</v>
       </c>
       <c r="K56" s="2">
-        <v>46326.147916666669</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L56" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B57" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="C57" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D57" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="F57" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="G57" t="s">
+        <v>18</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J57" s="2">
-        <v>46325.003472222219</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46325.878472222219</v>
+        <v>46324.75</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
@@ -3173,133 +3191,127 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
-      </c>
-      <c r="C58" t="s">
-        <v>14</v>
+        <v>70</v>
       </c>
       <c r="D58" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F58" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="I58" t="s">
         <v>19</v>
       </c>
       <c r="J58" s="2">
-        <v>46325.056944444441</v>
+        <v>46324</v>
       </c>
       <c r="K58" s="2">
-        <v>46326.098611111112</v>
+        <v>46326</v>
       </c>
       <c r="L58" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>89</v>
+        <v>157</v>
       </c>
       <c r="D59" t="s">
-        <v>90</v>
+        <v>158</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F59" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46325.333333333336</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K59" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L59" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C60" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="D60" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F60" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.625</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K60" s="2">
-        <v>46329.708333333336</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L60" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>96</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D61" t="s">
-        <v>123</v>
-      </c>
-      <c r="E61" s="1">
-        <v>26172</v>
+        <v>162</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F61" t="s">
-        <v>99</v>
-      </c>
-      <c r="G61" t="s">
-        <v>100</v>
-      </c>
-      <c r="H61" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="I61" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.625</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K61" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L61" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3307,63 +3319,66 @@
         <v>27</v>
       </c>
       <c r="B62" t="s">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="D62" t="s">
-        <v>164</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>165</v>
+        <v>90</v>
       </c>
       <c r="F62" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K62" s="2">
-        <v>46329.708333333336</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L62" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>122</v>
       </c>
       <c r="D63" t="s">
-        <v>166</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>167</v>
+        <v>123</v>
+      </c>
+      <c r="E63" s="1">
+        <v>26172</v>
       </c>
       <c r="F63" t="s">
-        <v>56</v>
+        <v>99</v>
+      </c>
+      <c r="G63" t="s">
+        <v>100</v>
+      </c>
+      <c r="H63" t="s">
+        <v>100</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="J63" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46328.125</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3371,16 +3386,16 @@
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="C64" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="D64" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F64" t="s">
         <v>31</v>
@@ -3389,13 +3404,13 @@
         <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46328.916666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L64" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:12">
@@ -3403,31 +3418,28 @@
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>148</v>
+        <v>39</v>
       </c>
       <c r="C65" t="s">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="D65" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="F65" t="s">
         <v>31</v>
       </c>
-      <c r="G65" t="s">
-        <v>25</v>
-      </c>
       <c r="I65" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J65" s="2">
-        <v>46326.25</v>
+        <v>46325.625</v>
       </c>
       <c r="K65" s="2">
-        <v>46326.75</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L65" t="s">
         <v>26</v>
@@ -3438,31 +3450,28 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="C66" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="D66" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F66" t="s">
-        <v>59</v>
-      </c>
-      <c r="G66" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I66" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J66" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46326.75</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L66" t="s">
         <v>26</v>
@@ -3470,28 +3479,31 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C67" t="s">
-        <v>119</v>
+        <v>53</v>
       </c>
       <c r="D67" t="s">
-        <v>174</v>
+        <v>168</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="F67" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
       </c>
       <c r="J67" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L67" t="s">
         <v>26</v>
@@ -3502,31 +3514,28 @@
         <v>27</v>
       </c>
       <c r="B68" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="C68" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="D68" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="F68" t="s">
-        <v>59</v>
-      </c>
-      <c r="G68" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="I68" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J68" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46327.75</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L68" t="s">
         <v>26</v>
@@ -3534,63 +3543,66 @@
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C69" t="s">
-        <v>134</v>
+        <v>53</v>
       </c>
       <c r="D69" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="F69" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46329.583333333336</v>
+        <v>46328.125</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B70" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D70" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F70" t="s">
-        <v>24</v>
+        <v>62</v>
+      </c>
+      <c r="G70" t="s">
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J70" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K70" s="2">
-        <v>46328.541666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
@@ -3604,54 +3616,57 @@
         <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D71" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F71" t="s">
         <v>31</v>
       </c>
       <c r="G71" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J71" s="2">
-        <v>46327.25</v>
+        <v>46326.25</v>
       </c>
       <c r="K71" s="2">
-        <v>46327.708333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B72" t="s">
-        <v>13</v>
+        <v>88</v>
+      </c>
+      <c r="C72" t="s">
+        <v>119</v>
       </c>
       <c r="D72" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="I72" t="s">
         <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46327.708333333336</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46328.833333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L72" t="s">
         <v>20</v>
@@ -3662,28 +3677,31 @@
         <v>27</v>
       </c>
       <c r="B73" t="s">
-        <v>76</v>
+        <v>148</v>
       </c>
       <c r="C73" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D73" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
       <c r="F73" t="s">
-        <v>31</v>
+        <v>62</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J73" s="2">
-        <v>46327.904861111114</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K73" s="2">
-        <v>46331.196527777778</v>
+        <v>46327.75</v>
       </c>
       <c r="L73" t="s">
         <v>20</v>
@@ -3694,63 +3712,60 @@
         <v>27</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>71</v>
+        <v>134</v>
       </c>
       <c r="D74" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="F74" t="s">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="I74" t="s">
         <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46329</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K74" s="2">
-        <v>46330</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L74" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F75" t="s">
-        <v>31</v>
-      </c>
-      <c r="G75" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46329.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46329.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -3761,28 +3776,31 @@
         <v>27</v>
       </c>
       <c r="B76" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D76" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F76" t="s">
-        <v>177</v>
+        <v>31</v>
+      </c>
+      <c r="G76" t="s">
+        <v>18</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J76" s="2">
-        <v>46329.333333333336</v>
+        <v>46327.25</v>
       </c>
       <c r="K76" s="2">
-        <v>46332.625</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L76" t="s">
         <v>20</v>
@@ -3790,34 +3808,25 @@
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>148</v>
-      </c>
-      <c r="C77" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>187</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="F77" t="s">
-        <v>31</v>
-      </c>
-      <c r="G77" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I77" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46329.791666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K77" s="2">
-        <v>46330.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L77" t="s">
         <v>26</v>
@@ -3828,16 +3837,16 @@
         <v>27</v>
       </c>
       <c r="B78" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C78" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D78" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F78" t="s">
         <v>31</v>
@@ -3846,13 +3855,13 @@
         <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46330.208333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K78" s="2">
-        <v>46334</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3860,31 +3869,31 @@
         <v>27</v>
       </c>
       <c r="B79" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C79" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="D79" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F79" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="I79" t="s">
         <v>19</v>
       </c>
       <c r="J79" s="2">
-        <v>46330.208333333336</v>
+        <v>46329</v>
       </c>
       <c r="K79" s="2">
-        <v>46334</v>
+        <v>46330</v>
       </c>
       <c r="L79" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3892,25 +3901,31 @@
         <v>27</v>
       </c>
       <c r="B80" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>187</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F80" t="s">
-        <v>99</v>
+        <v>31</v>
+      </c>
+      <c r="G80" t="s">
+        <v>18</v>
       </c>
       <c r="I80" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="J80" s="2">
-        <v>46330.625</v>
+        <v>46329.25</v>
       </c>
       <c r="K80" s="2">
-        <v>46331.125</v>
+        <v>46329.75</v>
       </c>
       <c r="L80" t="s">
         <v>20</v>
@@ -3927,10 +3942,10 @@
         <v>40</v>
       </c>
       <c r="D81" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="F81" t="s">
         <v>177</v>
@@ -3939,13 +3954,13 @@
         <v>19</v>
       </c>
       <c r="J81" s="2">
-        <v>46330.633333333331</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K81" s="2">
-        <v>46333.925000000003</v>
+        <v>46332.625</v>
       </c>
       <c r="L81" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3953,28 +3968,31 @@
         <v>27</v>
       </c>
       <c r="B82" t="s">
-        <v>39</v>
+        <v>148</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D82" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="F82" t="s">
-        <v>177</v>
+        <v>31</v>
+      </c>
+      <c r="G82" t="s">
+        <v>18</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J82" s="2">
-        <v>46330.633333333331</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46333.925000000003</v>
+        <v>46330.75</v>
       </c>
       <c r="L82" t="s">
         <v>20</v>
@@ -3985,60 +4003,63 @@
         <v>27</v>
       </c>
       <c r="B83" t="s">
-        <v>88</v>
+        <v>39</v>
       </c>
       <c r="C83" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="D83" t="s">
-        <v>125</v>
+        <v>191</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F83" t="s">
-        <v>92</v>
+        <v>31</v>
       </c>
       <c r="I83" t="s">
         <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K83" s="2">
-        <v>46331.204861111109</v>
+        <v>46334</v>
       </c>
       <c r="L83" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B84" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D84" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="F84" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="I84" t="s">
         <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.75</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K84" s="2">
-        <v>46332.75</v>
+        <v>46334</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4046,31 +4067,25 @@
         <v>27</v>
       </c>
       <c r="B85" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>97</v>
       </c>
       <c r="D85" t="s">
-        <v>197</v>
-      </c>
-      <c r="E85" s="1">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="F85" t="s">
-        <v>69</v>
-      </c>
-      <c r="G85" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="I85" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="J85" s="2">
-        <v>46331.25</v>
+        <v>46330.625</v>
       </c>
       <c r="K85" s="2">
-        <v>46331.75</v>
+        <v>46331.125</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -4081,34 +4096,28 @@
         <v>27</v>
       </c>
       <c r="B86" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C86" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D86" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F86" t="s">
-        <v>59</v>
-      </c>
-      <c r="G86" t="s">
-        <v>25</v>
-      </c>
-      <c r="H86" t="s">
-        <v>200</v>
+        <v>177</v>
       </c>
       <c r="I86" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46331.25</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K86" s="2">
-        <v>46331.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L86" t="s">
         <v>26</v>
@@ -4119,31 +4128,28 @@
         <v>27</v>
       </c>
       <c r="B87" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="C87" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D87" t="s">
-        <v>201</v>
-      </c>
-      <c r="E87" s="1">
-        <v>10</v>
+        <v>193</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>194</v>
       </c>
       <c r="F87" t="s">
-        <v>69</v>
-      </c>
-      <c r="G87" t="s">
-        <v>25</v>
+        <v>177</v>
       </c>
       <c r="I87" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46331.25</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L87" t="s">
         <v>26</v>
@@ -4151,66 +4157,63 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B88" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="C88" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="D88" t="s">
-        <v>202</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>203</v>
+        <v>125</v>
       </c>
       <c r="F88" t="s">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="I88" t="s">
         <v>19</v>
       </c>
       <c r="J88" s="2">
-        <v>46331.291666666664</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K88" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L88" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C89" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D89" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>163</v>
+        <v>196</v>
       </c>
       <c r="F89" t="s">
-        <v>177</v>
+        <v>56</v>
       </c>
       <c r="I89" t="s">
         <v>19</v>
       </c>
       <c r="J89" s="2">
-        <v>46331.496527777781</v>
+        <v>46330.75</v>
       </c>
       <c r="K89" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L89" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4218,28 +4221,31 @@
         <v>27</v>
       </c>
       <c r="B90" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="C90" t="s">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>204</v>
-      </c>
-      <c r="E90" s="1" t="s">
-        <v>163</v>
+        <v>197</v>
+      </c>
+      <c r="E90" s="1">
+        <v>10</v>
       </c>
       <c r="F90" t="s">
-        <v>177</v>
+        <v>69</v>
+      </c>
+      <c r="G90" t="s">
+        <v>18</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J90" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46334.746527777781</v>
+        <v>46331.75</v>
       </c>
       <c r="L90" t="s">
         <v>20</v>
@@ -4253,31 +4259,31 @@
         <v>148</v>
       </c>
       <c r="C91" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E91" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F91" t="s">
         <v>69</v>
       </c>
       <c r="G91" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I91" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J91" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K91" s="2">
-        <v>46332.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L91" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4285,69 +4291,66 @@
         <v>27</v>
       </c>
       <c r="B92" t="s">
-        <v>148</v>
+        <v>28</v>
       </c>
       <c r="C92" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F92" t="s">
+        <v>62</v>
+      </c>
+      <c r="G92" t="s">
+        <v>18</v>
+      </c>
+      <c r="H92" t="s">
+        <v>201</v>
+      </c>
+      <c r="I92" t="s">
         <v>59</v>
       </c>
-      <c r="G92" t="s">
-        <v>25</v>
-      </c>
-      <c r="H92" t="s">
-        <v>200</v>
-      </c>
-      <c r="I92" t="s">
-        <v>60</v>
-      </c>
       <c r="J92" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K92" s="2">
-        <v>46332.75</v>
+        <v>46331.75</v>
       </c>
       <c r="L92" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="D93" t="s">
-        <v>197</v>
-      </c>
-      <c r="E93" s="1">
-        <v>1</v>
+        <v>202</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F93" t="s">
-        <v>69</v>
-      </c>
-      <c r="G93" t="s">
-        <v>25</v>
+        <v>56</v>
       </c>
       <c r="I93" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K93" s="2">
-        <v>46332.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -4355,34 +4358,34 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B94" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C94" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="D94" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="F94" t="s">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="I94" t="s">
         <v>19</v>
       </c>
       <c r="J94" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K94" s="2">
-        <v>46332.597916666666</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L94" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4390,25 +4393,28 @@
         <v>27</v>
       </c>
       <c r="B95" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C95" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="D95" t="s">
-        <v>154</v>
+        <v>204</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F95" t="s">
-        <v>92</v>
+        <v>177</v>
       </c>
       <c r="I95" t="s">
         <v>19</v>
       </c>
       <c r="J95" s="2">
-        <v>46332.291666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.791666666664</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -4416,25 +4422,34 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>28</v>
+      </c>
+      <c r="C96" t="s">
+        <v>14</v>
       </c>
       <c r="D96" t="s">
-        <v>207</v>
+        <v>198</v>
+      </c>
+      <c r="E96" s="1">
+        <v>1</v>
       </c>
       <c r="F96" t="s">
-        <v>67</v>
+        <v>69</v>
+      </c>
+      <c r="G96" t="s">
+        <v>18</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J96" s="2">
-        <v>46332.375</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K96" s="2">
-        <v>46333.5</v>
+        <v>46332.75</v>
       </c>
       <c r="L96" t="s">
         <v>20</v>
@@ -4442,25 +4457,34 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>148</v>
+      </c>
+      <c r="C97" t="s">
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>207</v>
+        <v>197</v>
+      </c>
+      <c r="E97" s="1">
+        <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>67</v>
+        <v>69</v>
+      </c>
+      <c r="G97" t="s">
+        <v>18</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J97" s="2">
-        <v>46332.375</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46333.5</v>
+        <v>46332.75</v>
       </c>
       <c r="L97" t="s">
         <v>20</v>
@@ -4471,28 +4495,37 @@
         <v>27</v>
       </c>
       <c r="B98" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="C98" t="s">
-        <v>122</v>
+        <v>14</v>
       </c>
       <c r="D98" t="s">
-        <v>123</v>
+        <v>199</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F98" t="s">
-        <v>99</v>
+        <v>62</v>
+      </c>
+      <c r="G98" t="s">
+        <v>18</v>
+      </c>
+      <c r="H98" t="s">
+        <v>201</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J98" s="2">
-        <v>46332.541666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K98" s="2">
-        <v>46333.041666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L98" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:12">
@@ -4503,57 +4536,54 @@
         <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>34</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F99" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="I99" t="s">
         <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.875</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K99" s="2">
-        <v>46334.25</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L99" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="C100" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="D100" t="s">
-        <v>210</v>
-      </c>
-      <c r="E100" s="1" t="s">
-        <v>211</v>
+        <v>154</v>
       </c>
       <c r="F100" t="s">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="I100" t="s">
         <v>19</v>
       </c>
       <c r="J100" s="2">
-        <v>46333</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46334</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L100" t="s">
         <v>20</v>
@@ -4566,58 +4596,49 @@
       <c r="B101" t="s">
         <v>13</v>
       </c>
-      <c r="C101" t="s">
-        <v>47</v>
-      </c>
       <c r="D101" t="s">
-        <v>210</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F101" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="I101" t="s">
         <v>19</v>
       </c>
       <c r="J101" s="2">
-        <v>46333</v>
+        <v>46332.375</v>
       </c>
       <c r="K101" s="2">
-        <v>46334</v>
+        <v>46333.5</v>
       </c>
       <c r="L101" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="D102" t="s">
-        <v>212</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F102" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
       </c>
       <c r="J102" s="2">
-        <v>46333.041666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K102" s="2">
-        <v>46335.041666666664</v>
+        <v>46333.5</v>
       </c>
       <c r="L102" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4625,57 +4646,60 @@
         <v>27</v>
       </c>
       <c r="B103" t="s">
-        <v>70</v>
+        <v>96</v>
+      </c>
+      <c r="C103" t="s">
+        <v>122</v>
       </c>
       <c r="D103" t="s">
-        <v>212</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>213</v>
+        <v>123</v>
       </c>
       <c r="F103" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
       </c>
       <c r="J103" s="2">
+        <v>46332.541666666664</v>
+      </c>
+      <c r="K103" s="2">
         <v>46333.041666666664</v>
       </c>
-      <c r="K103" s="2">
-        <v>46335.041666666664</v>
-      </c>
       <c r="L103" t="s">
-        <v>20</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C104" t="s">
-        <v>119</v>
+        <v>34</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>208</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>209</v>
       </c>
       <c r="F104" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
       </c>
       <c r="J104" s="2">
-        <v>46333.416666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K104" s="2">
-        <v>46333.75</v>
+        <v>46334.25</v>
       </c>
       <c r="L104" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4686,60 +4710,57 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D105" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="F105" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="I105" t="s">
         <v>19</v>
       </c>
       <c r="J105" s="2">
-        <v>46333.666666666664</v>
+        <v>46333</v>
       </c>
       <c r="K105" s="2">
-        <v>46335.041666666664</v>
+        <v>46334</v>
       </c>
       <c r="L105" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C106" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="D106" t="s">
-        <v>216</v>
-      </c>
-      <c r="E106" s="1">
-        <v>11</v>
+        <v>210</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>211</v>
       </c>
       <c r="F106" t="s">
-        <v>69</v>
-      </c>
-      <c r="G106" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I106" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J106" s="2">
-        <v>46334.25</v>
+        <v>46333</v>
       </c>
       <c r="K106" s="2">
-        <v>46334.75</v>
+        <v>46334</v>
       </c>
       <c r="L106" t="s">
         <v>26</v>
@@ -4750,31 +4771,28 @@
         <v>27</v>
       </c>
       <c r="B107" t="s">
-        <v>76</v>
-      </c>
-      <c r="C107" t="s">
-        <v>134</v>
+        <v>70</v>
       </c>
       <c r="D107" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="F107" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="I107" t="s">
         <v>19</v>
       </c>
       <c r="J107" s="2">
-        <v>46334.958333333336</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K107" s="2">
-        <v>46337.708333333336</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L107" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="108" spans="1:12">
@@ -4782,31 +4800,25 @@
         <v>27</v>
       </c>
       <c r="B108" t="s">
-        <v>148</v>
-      </c>
-      <c r="C108" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D108" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F108" t="s">
-        <v>31</v>
-      </c>
-      <c r="G108" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="I108" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J108" s="2">
-        <v>46335.25</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K108" s="2">
-        <v>46335.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L108" t="s">
         <v>26</v>
@@ -4817,31 +4829,25 @@
         <v>27</v>
       </c>
       <c r="B109" t="s">
-        <v>28</v>
+        <v>88</v>
       </c>
       <c r="C109" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="D109" t="s">
-        <v>219</v>
-      </c>
-      <c r="E109" s="1" t="s">
-        <v>220</v>
+        <v>120</v>
       </c>
       <c r="F109" t="s">
-        <v>31</v>
-      </c>
-      <c r="G109" t="s">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="I109" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J109" s="2">
-        <v>46335.791666666664</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K109" s="2">
-        <v>46336.75</v>
+        <v>46333.75</v>
       </c>
       <c r="L109" t="s">
         <v>26</v>
@@ -4849,34 +4855,34 @@
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C110" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F110" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="I110" t="s">
         <v>19</v>
       </c>
       <c r="J110" s="2">
-        <v>46337</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K110" s="2">
-        <v>46339</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L110" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4884,28 +4890,31 @@
         <v>27</v>
       </c>
       <c r="B111" t="s">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="C111" t="s">
-        <v>71</v>
+        <v>14</v>
       </c>
       <c r="D111" t="s">
-        <v>223</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>224</v>
+        <v>216</v>
+      </c>
+      <c r="E111" s="1">
+        <v>11</v>
       </c>
       <c r="F111" t="s">
-        <v>74</v>
+        <v>69</v>
+      </c>
+      <c r="G111" t="s">
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J111" s="2">
-        <v>46337.208333333336</v>
+        <v>46334.25</v>
       </c>
       <c r="K111" s="2">
-        <v>46340.208333333336</v>
+        <v>46334.75</v>
       </c>
       <c r="L111" t="s">
         <v>20</v>
@@ -4916,31 +4925,28 @@
         <v>27</v>
       </c>
       <c r="B112" t="s">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="C112" t="s">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="D112" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F112" t="s">
         <v>31</v>
       </c>
-      <c r="G112" t="s">
-        <v>25</v>
-      </c>
       <c r="I112" t="s">
-        <v>60</v>
+        <v>19</v>
       </c>
       <c r="J112" s="2">
-        <v>46337.25</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K112" s="2">
-        <v>46337.75</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L112" t="s">
         <v>26</v>
@@ -4951,25 +4957,31 @@
         <v>27</v>
       </c>
       <c r="B113" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="C113" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="D113" t="s">
-        <v>90</v>
+        <v>219</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="F113" t="s">
-        <v>92</v>
+        <v>31</v>
+      </c>
+      <c r="G113" t="s">
+        <v>18</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J113" s="2">
-        <v>46337.333333333336</v>
+        <v>46335.25</v>
       </c>
       <c r="K113" s="2">
-        <v>46337.833333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L113" t="s">
         <v>20</v>
@@ -4980,25 +4992,31 @@
         <v>27</v>
       </c>
       <c r="B114" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="C114" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="D114" t="s">
-        <v>98</v>
+        <v>219</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="F114" t="s">
-        <v>99</v>
+        <v>31</v>
+      </c>
+      <c r="G114" t="s">
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>101</v>
+        <v>59</v>
       </c>
       <c r="J114" s="2">
-        <v>46337.625</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K114" s="2">
-        <v>46338.125</v>
+        <v>46336.75</v>
       </c>
       <c r="L114" t="s">
         <v>20</v>
@@ -5006,92 +5024,98 @@
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B115" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C115" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D115" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="F115" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="I115" t="s">
         <v>19</v>
       </c>
       <c r="J115" s="2">
-        <v>46337.75</v>
+        <v>46337</v>
       </c>
       <c r="K115" s="2">
-        <v>46339.75</v>
+        <v>46339</v>
       </c>
       <c r="L115" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C116" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="D116" t="s">
-        <v>229</v>
+        <v>223</v>
+      </c>
+      <c r="E116" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="F116" t="s">
-        <v>17</v>
+        <v>74</v>
       </c>
       <c r="I116" t="s">
         <v>19</v>
       </c>
       <c r="J116" s="2">
-        <v>46338.431250000001</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K116" s="2">
-        <v>46339.472916666666</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L116" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B117" t="s">
-        <v>52</v>
+        <v>148</v>
       </c>
       <c r="C117" t="s">
-        <v>106</v>
+        <v>14</v>
       </c>
       <c r="D117" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="F117" t="s">
-        <v>56</v>
+        <v>31</v>
+      </c>
+      <c r="G117" t="s">
+        <v>18</v>
       </c>
       <c r="I117" t="s">
-        <v>19</v>
+        <v>59</v>
       </c>
       <c r="J117" s="2">
-        <v>46338.709027777775</v>
+        <v>46337.25</v>
       </c>
       <c r="K117" s="2">
-        <v>46339.584027777775</v>
+        <v>46337.75</v>
       </c>
       <c r="L117" t="s">
         <v>20</v>
@@ -5099,34 +5123,31 @@
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>88</v>
       </c>
       <c r="C118" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="D118" t="s">
-        <v>232</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>233</v>
+        <v>90</v>
       </c>
       <c r="F118" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
       <c r="I118" t="s">
         <v>19</v>
       </c>
       <c r="J118" s="2">
-        <v>46338.791666666664</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K118" s="2">
-        <v>46340.166666666664</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L118" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="119" spans="1:12">
@@ -5134,63 +5155,60 @@
         <v>27</v>
       </c>
       <c r="B119" t="s">
-        <v>76</v>
+        <v>96</v>
       </c>
       <c r="C119" t="s">
-        <v>77</v>
+        <v>97</v>
       </c>
       <c r="D119" t="s">
-        <v>234</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>235</v>
+        <v>98</v>
       </c>
       <c r="F119" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="J119" s="2">
-        <v>46338.958333333336</v>
+        <v>46337.625</v>
       </c>
       <c r="K119" s="2">
-        <v>46342.208333333336</v>
+        <v>46338.125</v>
       </c>
       <c r="L119" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="C120" t="s">
-        <v>77</v>
+        <v>53</v>
       </c>
       <c r="D120" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F120" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="I120" t="s">
         <v>19</v>
       </c>
       <c r="J120" s="2">
-        <v>46338.958333333336</v>
+        <v>46337.75</v>
       </c>
       <c r="K120" s="2">
-        <v>46342.208333333336</v>
+        <v>46339.75</v>
       </c>
       <c r="L120" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="121" spans="1:12">
@@ -5201,86 +5219,243 @@
         <v>13</v>
       </c>
       <c r="C121" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D121" t="s">
-        <v>236</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="F121" t="s">
-        <v>177</v>
+        <v>24</v>
       </c>
       <c r="I121" t="s">
         <v>19</v>
       </c>
       <c r="J121" s="2">
-        <v>46339.083333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K121" s="2">
-        <v>46340.291666666664</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L121" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>96</v>
+        <v>52</v>
       </c>
       <c r="C122" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D122" t="s">
-        <v>123</v>
+        <v>230</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="F122" t="s">
-        <v>99</v>
+        <v>56</v>
       </c>
       <c r="I122" t="s">
         <v>19</v>
       </c>
       <c r="J122" s="2">
-        <v>46339.541666666664</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K122" s="2">
-        <v>46340.041666666664</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L122" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
+        <v>13</v>
+      </c>
+      <c r="C123" t="s">
+        <v>34</v>
+      </c>
+      <c r="D123" t="s">
+        <v>232</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F123" t="s">
+        <v>37</v>
+      </c>
+      <c r="I123" t="s">
+        <v>19</v>
+      </c>
+      <c r="J123" s="2">
+        <v>46338.791666666664</v>
+      </c>
+      <c r="K123" s="2">
+        <v>46340.166666666664</v>
+      </c>
+      <c r="L123" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12">
+      <c r="A124" t="s">
+        <v>27</v>
+      </c>
+      <c r="B124" t="s">
+        <v>78</v>
+      </c>
+      <c r="C124" t="s">
+        <v>79</v>
+      </c>
+      <c r="D124" t="s">
+        <v>234</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F124" t="s">
+        <v>82</v>
+      </c>
+      <c r="I124" t="s">
+        <v>19</v>
+      </c>
+      <c r="J124" s="2">
+        <v>46338.958333333336</v>
+      </c>
+      <c r="K124" s="2">
+        <v>46342.208333333336</v>
+      </c>
+      <c r="L124" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12">
+      <c r="A125" t="s">
+        <v>27</v>
+      </c>
+      <c r="B125" t="s">
+        <v>78</v>
+      </c>
+      <c r="C125" t="s">
+        <v>79</v>
+      </c>
+      <c r="D125" t="s">
+        <v>234</v>
+      </c>
+      <c r="E125" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F125" t="s">
+        <v>82</v>
+      </c>
+      <c r="I125" t="s">
+        <v>19</v>
+      </c>
+      <c r="J125" s="2">
+        <v>46338.958333333336</v>
+      </c>
+      <c r="K125" s="2">
+        <v>46342.208333333336</v>
+      </c>
+      <c r="L125" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12">
+      <c r="A126" t="s">
+        <v>12</v>
+      </c>
+      <c r="B126" t="s">
+        <v>13</v>
+      </c>
+      <c r="C126" t="s">
+        <v>47</v>
+      </c>
+      <c r="D126" t="s">
+        <v>236</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F126" t="s">
+        <v>177</v>
+      </c>
+      <c r="I126" t="s">
+        <v>19</v>
+      </c>
+      <c r="J126" s="2">
+        <v>46339.083333333336</v>
+      </c>
+      <c r="K126" s="2">
+        <v>46340.291666666664</v>
+      </c>
+      <c r="L126" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12">
+      <c r="A127" t="s">
+        <v>27</v>
+      </c>
+      <c r="B127" t="s">
+        <v>96</v>
+      </c>
+      <c r="C127" t="s">
+        <v>122</v>
+      </c>
+      <c r="D127" t="s">
+        <v>123</v>
+      </c>
+      <c r="F127" t="s">
+        <v>99</v>
+      </c>
+      <c r="I127" t="s">
+        <v>19</v>
+      </c>
+      <c r="J127" s="2">
+        <v>46339.541666666664</v>
+      </c>
+      <c r="K127" s="2">
+        <v>46340.041666666664</v>
+      </c>
+      <c r="L127" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12">
+      <c r="A128" t="s">
+        <v>27</v>
+      </c>
+      <c r="B128" t="s">
         <v>88</v>
       </c>
-      <c r="C123" t="s">
+      <c r="C128" t="s">
         <v>89</v>
       </c>
-      <c r="D123" t="s">
+      <c r="D128" t="s">
         <v>125</v>
       </c>
-      <c r="F123" t="s">
+      <c r="F128" t="s">
         <v>92</v>
       </c>
-      <c r="I123" t="s">
-        <v>19</v>
-      </c>
-      <c r="J123" s="2">
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+      <c r="J128" s="2">
         <v>46339.704861111109</v>
       </c>
-      <c r="K123" s="2">
+      <c r="K128" s="2">
         <v>46340.204861111109</v>
       </c>
-      <c r="L123" t="s">
-        <v>20</v>
+      <c r="L128" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -5292,6 +5467,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5299,13 +5483,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5443,27 +5627,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-17.xlsx
+++ b/data/vessels/2026-10-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="432595" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4C4B9DE-6CA5-4A61-A8E7-86E46600545C}"/>
+  <xr:revisionPtr revIDLastSave="433156" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B5A69DC-A7CF-4414-88CA-D95D5BB62291}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="235">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,6 +83,27 @@
     <t>T18</t>
   </si>
   <si>
+    <t>EB Service 2</t>
+  </si>
+  <si>
+    <t>SUVA CHIEF</t>
+  </si>
+  <si>
+    <t>007E/008W</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>Talon Marine Services LLC</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
     <t>Ad Hoc</t>
   </si>
   <si>
@@ -98,126 +119,96 @@
     <t>Norton Lilly International</t>
   </si>
   <si>
-    <t>Container</t>
-  </si>
-  <si>
     <t>Not available</t>
   </si>
   <si>
-    <t>EB Service 2</t>
-  </si>
-  <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>In transit</t>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
   </si>
   <si>
     <t>Tacoma</t>
   </si>
   <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
     <t>EB1</t>
   </si>
   <si>
-    <t>IRIS ACE</t>
-  </si>
-  <si>
-    <t>110A</t>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
   </si>
   <si>
     <t>ONE</t>
   </si>
   <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Ro-Ro</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>Husky</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
     <t>Car Carrier</t>
   </si>
   <si>
@@ -269,27 +260,27 @@
     <t>BEN LINES</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
     <t>MSC DENISSE X</t>
   </si>
   <si>
     <t>UK641R</t>
   </si>
   <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
     <t>ARC ENDEAVOR</t>
   </si>
   <si>
@@ -320,6 +311,24 @@
     <t>Matson</t>
   </si>
   <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
     <t>VIENNA EXPRESS</t>
   </si>
   <si>
@@ -329,24 +338,6 @@
     <t>Hapag-Lloyd</t>
   </si>
   <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
     <t>KW664</t>
   </si>
   <si>
@@ -539,18 +530,18 @@
     <t>OYNT0002E</t>
   </si>
   <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
     <t>NBBT0001E</t>
   </si>
   <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
@@ -632,19 +623,19 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -825,10 +816,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L128" totalsRowShown="0">
-  <autoFilter ref="A1:L128" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L128">
-    <sortCondition ref="J2:J128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L131" totalsRowShown="0">
+  <autoFilter ref="A1:L131" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L131">
+    <sortCondition ref="J2:J131"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1165,7 +1156,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1260,19 +1251,19 @@
         <v>13</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
         <v>19</v>
@@ -1284,7 +1275,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12">
@@ -1295,19 +1286,19 @@
         <v>13</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
         <v>19</v>
@@ -1319,7 +1310,7 @@
         <v>46312.708333333336</v>
       </c>
       <c r="L4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:12">
@@ -1359,37 +1350,37 @@
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
         <v>27</v>
       </c>
-      <c r="B6" t="s">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>18</v>
       </c>
       <c r="H6" t="s">
         <v>32</v>
       </c>
       <c r="I6" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46312.125</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46312.666666666664</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L6" t="s">
         <v>20</v>
@@ -1397,37 +1388,37 @@
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="E7" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" t="s">
         <v>30</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>31</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
       </c>
       <c r="H7" t="s">
         <v>32</v>
       </c>
       <c r="I7" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46312.125</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K7" s="2">
-        <v>46312.666666666664</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L7" t="s">
         <v>20</v>
@@ -1435,113 +1426,107 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I8" t="s">
         <v>19</v>
       </c>
       <c r="J8" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K8" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I9" t="s">
         <v>19</v>
       </c>
       <c r="J9" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K9" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" t="s">
         <v>39</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>40</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I10" t="s">
         <v>19</v>
       </c>
       <c r="J10" s="2">
-        <v>46312.3125</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K10" s="2">
-        <v>46314.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -1552,31 +1537,31 @@
         <v>13</v>
       </c>
       <c r="C11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="G11" t="s">
         <v>46</v>
       </c>
-      <c r="F11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" t="s">
-        <v>18</v>
-      </c>
       <c r="I11" t="s">
         <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46312.541666666664</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K11" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1584,63 +1569,63 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" t="s">
-        <v>51</v>
+        <v>25</v>
       </c>
       <c r="I12" t="s">
         <v>19</v>
       </c>
       <c r="J12" s="2">
-        <v>46313.208333333336</v>
+        <v>46313.25</v>
       </c>
       <c r="K12" s="2">
-        <v>46314.208333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L12" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
         <v>52</v>
       </c>
       <c r="C13" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" t="s">
         <v>53</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" t="s">
         <v>55</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
+        <v>25</v>
+      </c>
+      <c r="I13" t="s">
         <v>56</v>
       </c>
-      <c r="G13" t="s">
-        <v>18</v>
-      </c>
-      <c r="I13" t="s">
-        <v>19</v>
-      </c>
       <c r="J13" s="2">
-        <v>46313.25</v>
+        <v>46314.25</v>
       </c>
       <c r="K13" s="2">
         <v>46314.75</v>
@@ -1651,13 +1636,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C14" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D14" t="s">
         <v>57</v>
@@ -1666,13 +1651,13 @@
         <v>58</v>
       </c>
       <c r="F14" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I14" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J14" s="2">
         <v>46314.25</v>
@@ -1681,18 +1666,15 @@
         <v>46314.75</v>
       </c>
       <c r="L14" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D15" t="s">
         <v>60</v>
@@ -1704,16 +1686,19 @@
         <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>18</v>
+        <v>25</v>
+      </c>
+      <c r="H15" t="s">
+        <v>32</v>
       </c>
       <c r="I15" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K15" s="2">
-        <v>46314.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L15" t="s">
         <v>20</v>
@@ -1721,25 +1706,25 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>34</v>
+      </c>
+      <c r="C16" t="s">
+        <v>63</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
-      </c>
-      <c r="E16" s="1" t="s">
         <v>64</v>
       </c>
+      <c r="E16" s="1">
+        <v>34</v>
+      </c>
       <c r="F16" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
-      </c>
-      <c r="H16" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I16" t="s">
         <v>19</v>
@@ -1748,42 +1733,42 @@
         <v>46314.625</v>
       </c>
       <c r="K16" s="2">
-        <v>46315.166666666664</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L16" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D17" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="1">
+        <v>2</v>
+      </c>
+      <c r="F17" t="s">
         <v>66</v>
       </c>
-      <c r="D17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E17" s="1">
-        <v>34</v>
-      </c>
-      <c r="F17" t="s">
-        <v>31</v>
-      </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J17" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K17" s="2">
-        <v>46318.166666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L17" t="s">
         <v>26</v>
@@ -1791,34 +1776,34 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D18" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="1">
-        <v>2</v>
+        <v>69</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>72</v>
       </c>
       <c r="I18" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
         <v>46315.208333333336</v>
       </c>
       <c r="K18" s="2">
-        <v>46315.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L18" t="s">
         <v>20</v>
@@ -1826,37 +1811,37 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="I19" t="s">
         <v>19</v>
       </c>
       <c r="J19" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L19" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1864,22 +1849,22 @@
         <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G20" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I20" t="s">
         <v>19</v>
@@ -1891,18 +1876,18 @@
         <v>46317.75</v>
       </c>
       <c r="L20" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D21" t="s">
         <v>80</v>
@@ -1911,19 +1896,22 @@
         <v>81</v>
       </c>
       <c r="F21" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+      <c r="H21" t="s">
         <v>82</v>
       </c>
-      <c r="G21" t="s">
-        <v>38</v>
-      </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J21" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K21" s="2">
-        <v>46317.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L21" t="s">
         <v>26</v>
@@ -1931,31 +1919,28 @@
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>83</v>
       </c>
       <c r="C22" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="1" t="s">
         <v>84</v>
       </c>
+      <c r="E22" s="1">
+        <v>63</v>
+      </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>18</v>
-      </c>
-      <c r="H22" t="s">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="I22" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J22" s="2">
         <v>46316.25</v>
@@ -1964,39 +1949,42 @@
         <v>46316.75</v>
       </c>
       <c r="L22" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
         <v>86</v>
-      </c>
-      <c r="C23" t="s">
-        <v>14</v>
       </c>
       <c r="D23" t="s">
         <v>87</v>
       </c>
-      <c r="E23" s="1">
-        <v>63</v>
+      <c r="E23" s="1" t="s">
+        <v>88</v>
       </c>
       <c r="F23" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s">
-        <v>38</v>
+        <v>89</v>
+      </c>
+      <c r="H23" t="s">
+        <v>32</v>
       </c>
       <c r="I23" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J23" s="2">
-        <v>46316.25</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46316.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L23" t="s">
         <v>20</v>
@@ -2004,63 +1992,63 @@
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
+      </c>
+      <c r="E24" s="1">
+        <v>26169</v>
       </c>
       <c r="F24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G24" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
+        <v>94</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="J24" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K24" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L24" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B25" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C25" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G25" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I25" t="s">
         <v>19</v>
@@ -2072,30 +2060,30 @@
         <v>46319.75</v>
       </c>
       <c r="L25" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F26" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="G26" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I26" t="s">
         <v>19</v>
@@ -2107,42 +2095,42 @@
         <v>46319.75</v>
       </c>
       <c r="L26" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="C27" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>98</v>
-      </c>
-      <c r="E27" s="1">
-        <v>26169</v>
+        <v>80</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="F27" t="s">
-        <v>99</v>
+        <v>59</v>
       </c>
       <c r="G27" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="H27" t="s">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="I27" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="J27" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K27" s="2">
-        <v>46317.041666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L27" t="s">
         <v>26</v>
@@ -2150,37 +2138,31 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B28" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" t="s">
         <v>102</v>
       </c>
-      <c r="F28" t="s">
-        <v>62</v>
-      </c>
-      <c r="G28" t="s">
-        <v>18</v>
-      </c>
-      <c r="H28" t="s">
-        <v>85</v>
-      </c>
       <c r="I28" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J28" s="2">
         <v>46317.208333333336</v>
       </c>
       <c r="K28" s="2">
-        <v>46317.75</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L28" t="s">
         <v>20</v>
@@ -2188,63 +2170,66 @@
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>103</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>74</v>
-      </c>
-      <c r="G29" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="I29" t="s">
         <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K29" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="C30" t="s">
+        <v>21</v>
+      </c>
+      <c r="D30" t="s">
         <v>106</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" s="1">
+        <v>1</v>
+      </c>
+      <c r="F30" t="s">
         <v>107</v>
       </c>
-      <c r="E30" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="G30" t="s">
+        <v>25</v>
+      </c>
+      <c r="I30" t="s">
         <v>56</v>
       </c>
-      <c r="I30" t="s">
-        <v>19</v>
-      </c>
       <c r="J30" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46318.166666666664</v>
+        <v>46320.75</v>
       </c>
       <c r="L30" t="s">
         <v>26</v>
@@ -2252,28 +2237,28 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D31" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E31" s="1">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I31" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J31" s="2">
         <v>46317.541666666664</v>
@@ -2282,39 +2267,36 @@
         <v>46320.75</v>
       </c>
       <c r="L31" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="D32" t="s">
         <v>109</v>
       </c>
-      <c r="E32" s="1">
-        <v>1</v>
+      <c r="E32" s="1" t="s">
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I32" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46317.541666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K32" s="2">
-        <v>46320.75</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L32" t="s">
         <v>20</v>
@@ -2322,31 +2304,34 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C33" t="s">
+        <v>21</v>
+      </c>
+      <c r="D33" t="s">
         <v>111</v>
       </c>
-      <c r="D33" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="F33" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G33" t="s">
+        <v>89</v>
+      </c>
+      <c r="H33" t="s">
+        <v>32</v>
       </c>
       <c r="I33" t="s">
         <v>19</v>
       </c>
       <c r="J33" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K33" s="2">
-        <v>46318.969444444447</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L33" t="s">
         <v>26</v>
@@ -2354,69 +2339,72 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
+        <v>112</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="F34" t="s">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="G34" t="s">
-        <v>92</v>
-      </c>
-      <c r="H34" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L34" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" t="s">
         <v>27</v>
       </c>
-      <c r="B35" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" t="s">
-        <v>14</v>
-      </c>
       <c r="D35" t="s">
+        <v>114</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>116</v>
-      </c>
       <c r="F35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" t="s">
         <v>31</v>
       </c>
-      <c r="G35" t="s">
-        <v>18</v>
+      <c r="H35" t="s">
+        <v>32</v>
       </c>
       <c r="I35" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J35" s="2">
         <v>46318.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46318.75</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L35" t="s">
         <v>20</v>
@@ -2424,13 +2412,13 @@
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B36" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C36" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="D36" t="s">
         <v>117</v>
@@ -2439,10 +2427,10 @@
         <v>118</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>89</v>
       </c>
       <c r="G36" t="s">
-        <v>38</v>
+        <v>89</v>
       </c>
       <c r="H36" t="s">
         <v>32</v>
@@ -2451,21 +2439,21 @@
         <v>19</v>
       </c>
       <c r="J36" s="2">
-        <v>46318.25</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K36" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L36" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C37" t="s">
         <v>119</v>
@@ -2473,96 +2461,93 @@
       <c r="D37" t="s">
         <v>120</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="1">
+        <v>26168</v>
+      </c>
+      <c r="F37" t="s">
+        <v>93</v>
+      </c>
+      <c r="G37" t="s">
+        <v>94</v>
+      </c>
+      <c r="H37" t="s">
+        <v>94</v>
+      </c>
+      <c r="I37" t="s">
+        <v>95</v>
+      </c>
+      <c r="J37" s="2">
+        <v>46318.625</v>
+      </c>
+      <c r="K37" s="2">
+        <v>46319.041666666664</v>
+      </c>
+      <c r="L37" t="s">
         <v>121</v>
-      </c>
-      <c r="F37" t="s">
-        <v>92</v>
-      </c>
-      <c r="G37" t="s">
-        <v>92</v>
-      </c>
-      <c r="H37" t="s">
-        <v>32</v>
-      </c>
-      <c r="I37" t="s">
-        <v>19</v>
-      </c>
-      <c r="J37" s="2">
-        <v>46318.291666666664</v>
-      </c>
-      <c r="K37" s="2">
-        <v>46319.125</v>
-      </c>
-      <c r="L37" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C38" t="s">
+        <v>86</v>
+      </c>
+      <c r="D38" t="s">
         <v>122</v>
       </c>
-      <c r="D38" t="s">
-        <v>123</v>
-      </c>
-      <c r="E38" s="1">
-        <v>26168</v>
+      <c r="E38" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="F38" t="s">
-        <v>99</v>
-      </c>
-      <c r="G38" t="s">
-        <v>100</v>
-      </c>
-      <c r="H38" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46318.625</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L38" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C39" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
+      </c>
+      <c r="E39" s="1">
+        <v>4</v>
       </c>
       <c r="F39" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="G39" t="s">
+        <v>25</v>
       </c>
       <c r="I39" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J39" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.75</v>
       </c>
       <c r="L39" t="s">
         <v>26</v>
@@ -2570,28 +2555,28 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C40" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E40" s="1">
         <v>4</v>
       </c>
       <c r="F40" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="G40" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I40" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J40" s="2">
         <v>46319.208333333336</v>
@@ -2600,68 +2585,68 @@
         <v>46319.75</v>
       </c>
       <c r="L40" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C41" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D41" t="s">
-        <v>126</v>
-      </c>
-      <c r="E41" s="1">
-        <v>4</v>
+        <v>124</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>125</v>
       </c>
       <c r="F41" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I41" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J41" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K41" s="2">
         <v>46319.75</v>
       </c>
       <c r="L41" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B42" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C42" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D42" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I42" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J42" s="2">
         <v>46319.25</v>
@@ -2670,36 +2655,36 @@
         <v>46319.75</v>
       </c>
       <c r="L42" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B43" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C43" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D43" t="s">
+        <v>126</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F43" t="s">
+        <v>128</v>
+      </c>
+      <c r="G43" t="s">
+        <v>31</v>
+      </c>
+      <c r="H43" t="s">
         <v>129</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="F43" t="s">
-        <v>131</v>
-      </c>
-      <c r="G43" t="s">
-        <v>38</v>
-      </c>
-      <c r="H43" t="s">
-        <v>132</v>
-      </c>
       <c r="I43" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J43" s="2">
         <v>46319.25</v>
@@ -2708,36 +2693,39 @@
         <v>46320.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>83</v>
+      </c>
+      <c r="C44" t="s">
+        <v>21</v>
       </c>
       <c r="D44" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="H44" t="s">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K44" s="2">
         <v>46320.166666666664</v>
@@ -2748,101 +2736,104 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
-        <v>78</v>
-      </c>
-      <c r="C45" t="s">
-        <v>134</v>
+        <v>13</v>
       </c>
       <c r="D45" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>136</v>
+        <v>61</v>
       </c>
       <c r="F45" t="s">
-        <v>82</v>
+        <v>62</v>
       </c>
       <c r="G45" t="s">
-        <v>38</v>
+        <v>25</v>
+      </c>
+      <c r="H45" t="s">
+        <v>32</v>
       </c>
       <c r="I45" t="s">
         <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.625</v>
       </c>
       <c r="K45" s="2">
-        <v>46321.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C46" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="D46" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F46" t="s">
-        <v>74</v>
+        <v>77</v>
+      </c>
+      <c r="G46" t="s">
+        <v>31</v>
       </c>
       <c r="I46" t="s">
         <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46320</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K46" s="2">
-        <v>46322</v>
+        <v>46321.75</v>
       </c>
       <c r="L46" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>67</v>
       </c>
       <c r="C47" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="D47" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F47" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="I47" t="s">
         <v>19</v>
       </c>
       <c r="J47" s="2">
-        <v>46320.21875</v>
+        <v>46320</v>
       </c>
       <c r="K47" s="2">
-        <v>46324.59375</v>
+        <v>46322</v>
       </c>
       <c r="L47" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2853,31 +2844,28 @@
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F48" t="s">
-        <v>50</v>
-      </c>
-      <c r="G48" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="I48" t="s">
         <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.208333333336</v>
+        <v>46320.21875</v>
       </c>
       <c r="K48" s="2">
-        <v>46322.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L48" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2885,133 +2873,133 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="D49" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F49" t="s">
-        <v>56</v>
+        <v>45</v>
+      </c>
+      <c r="G49" t="s">
+        <v>46</v>
       </c>
       <c r="I49" t="s">
         <v>19</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K49" s="2">
-        <v>46323.21875</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L49" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="D50" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F50" t="s">
-        <v>82</v>
-      </c>
-      <c r="G50" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="I50" t="s">
         <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.25</v>
+        <v>46321.21875</v>
       </c>
       <c r="K50" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L50" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C51" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="D51" t="s">
-        <v>147</v>
-      </c>
-      <c r="E51" s="1">
-        <v>21</v>
+        <v>142</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="F51" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G51" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="I51" t="s">
         <v>19</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B52" t="s">
-        <v>148</v>
+        <v>34</v>
       </c>
       <c r="C52" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s">
-        <v>149</v>
+        <v>144</v>
+      </c>
+      <c r="E52" s="1">
+        <v>21</v>
       </c>
       <c r="F52" t="s">
-        <v>131</v>
+        <v>77</v>
       </c>
       <c r="G52" t="s">
-        <v>38</v>
-      </c>
-      <c r="H52" t="s">
-        <v>132</v>
+        <v>25</v>
       </c>
       <c r="I52" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J52" s="2">
-        <v>46322.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K52" s="2">
-        <v>46322.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L52" t="s">
         <v>20</v>
@@ -3019,34 +3007,34 @@
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B53" t="s">
-        <v>39</v>
+        <v>145</v>
       </c>
       <c r="C53" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D53" t="s">
-        <v>150</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F53" t="s">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="G53" t="s">
-        <v>18</v>
+        <v>31</v>
+      </c>
+      <c r="H53" t="s">
+        <v>129</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J53" s="2">
-        <v>46322.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K53" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L53" t="s">
         <v>26</v>
@@ -3054,34 +3042,34 @@
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C54" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D54" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F54" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I54" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K54" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L54" t="s">
         <v>20</v>
@@ -3089,66 +3077,63 @@
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B55" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C55" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="D55" t="s">
-        <v>154</v>
+        <v>149</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>92</v>
+        <v>55</v>
+      </c>
+      <c r="G55" t="s">
+        <v>25</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K55" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L55" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B56" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C56" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="D56" t="s">
-        <v>98</v>
-      </c>
-      <c r="E56" s="1">
-        <v>26173</v>
+        <v>151</v>
       </c>
       <c r="F56" t="s">
-        <v>99</v>
-      </c>
-      <c r="G56" t="s">
-        <v>100</v>
-      </c>
-      <c r="H56" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I56" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K56" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L56" t="s">
         <v>26</v>
@@ -3156,34 +3141,37 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B57" t="s">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="C57" t="s">
-        <v>14</v>
+        <v>91</v>
       </c>
       <c r="D57" t="s">
-        <v>152</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>153</v>
+        <v>92</v>
+      </c>
+      <c r="E57" s="1">
+        <v>26173</v>
       </c>
       <c r="F57" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="G57" t="s">
-        <v>18</v>
+        <v>94</v>
+      </c>
+      <c r="H57" t="s">
+        <v>94</v>
       </c>
       <c r="I57" t="s">
-        <v>59</v>
+        <v>95</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K57" s="2">
-        <v>46324.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L57" t="s">
         <v>20</v>
@@ -3191,28 +3179,34 @@
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>145</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
       </c>
       <c r="D58" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F58" t="s">
-        <v>74</v>
+        <v>55</v>
+      </c>
+      <c r="G58" t="s">
+        <v>25</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J58" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K58" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L58" t="s">
         <v>26</v>
@@ -3220,34 +3214,31 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B59" t="s">
-        <v>13</v>
-      </c>
-      <c r="C59" t="s">
-        <v>157</v>
+        <v>67</v>
       </c>
       <c r="D59" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="F59" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="I59" t="s">
         <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46324.647916666669</v>
+        <v>46324</v>
       </c>
       <c r="K59" s="2">
-        <v>46326.147916666669</v>
+        <v>46326</v>
       </c>
       <c r="L59" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3255,31 +3246,31 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>106</v>
+        <v>154</v>
       </c>
       <c r="D60" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="F60" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I60" t="s">
         <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.003472222219</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K60" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L60" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3287,150 +3278,150 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C61" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="D61" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="F61" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I61" t="s">
         <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K61" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L61" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B62" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C62" t="s">
-        <v>89</v>
+        <v>14</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>159</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="F62" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
       <c r="I62" t="s">
         <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K62" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L62" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B63" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>123</v>
-      </c>
-      <c r="E63" s="1">
-        <v>26172</v>
+        <v>87</v>
       </c>
       <c r="F63" t="s">
-        <v>99</v>
-      </c>
-      <c r="G63" t="s">
-        <v>100</v>
-      </c>
-      <c r="H63" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="I63" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K63" s="2">
-        <v>46326.041666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L63" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B64" t="s">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c r="C64" t="s">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D64" t="s">
-        <v>164</v>
-      </c>
-      <c r="E64" s="1" t="s">
-        <v>165</v>
+        <v>120</v>
+      </c>
+      <c r="E64" s="1">
+        <v>26172</v>
       </c>
       <c r="F64" t="s">
-        <v>31</v>
+        <v>93</v>
+      </c>
+      <c r="G64" t="s">
+        <v>94</v>
+      </c>
+      <c r="H64" t="s">
+        <v>94</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="J64" s="2">
         <v>46325.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L64" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B65" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C65" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D65" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F65" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I65" t="s">
         <v>19</v>
@@ -3442,39 +3433,39 @@
         <v>46329.708333333336</v>
       </c>
       <c r="L65" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B66" t="s">
-        <v>78</v>
+        <v>34</v>
       </c>
       <c r="C66" t="s">
-        <v>134</v>
+        <v>63</v>
       </c>
       <c r="D66" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="F66" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I66" t="s">
         <v>19</v>
       </c>
       <c r="J66" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K66" s="2">
-        <v>46328.916666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L66" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3482,19 +3473,19 @@
         <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C67" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D67" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F67" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I67" t="s">
         <v>19</v>
@@ -3506,27 +3497,27 @@
         <v>46328.125</v>
       </c>
       <c r="L67" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B68" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C68" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D68" t="s">
+        <v>165</v>
+      </c>
+      <c r="E68" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E68" s="1" t="s">
-        <v>167</v>
-      </c>
       <c r="F68" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="I68" t="s">
         <v>19</v>
@@ -3538,7 +3529,7 @@
         <v>46328.916666666664</v>
       </c>
       <c r="L68" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3546,19 +3537,19 @@
         <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C69" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D69" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="F69" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="I69" t="s">
         <v>19</v>
@@ -3570,39 +3561,36 @@
         <v>46328.125</v>
       </c>
       <c r="L69" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B70" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="C70" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D70" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
-      </c>
-      <c r="G70" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="I70" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J70" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K70" s="2">
-        <v>46326.75</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L70" t="s">
         <v>20</v>
@@ -3610,28 +3598,28 @@
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B71" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="C71" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D71" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F71" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I71" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J71" s="2">
         <v>46326.25</v>
@@ -3640,100 +3628,109 @@
         <v>46326.75</v>
       </c>
       <c r="L71" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B72" t="s">
-        <v>88</v>
+        <v>52</v>
       </c>
       <c r="C72" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="D72" t="s">
-        <v>174</v>
+        <v>167</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>168</v>
       </c>
       <c r="F72" t="s">
-        <v>92</v>
+        <v>59</v>
+      </c>
+      <c r="G72" t="s">
+        <v>25</v>
       </c>
       <c r="I72" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K72" s="2">
         <v>46326.75</v>
       </c>
       <c r="L72" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B73" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C73" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D73" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="F73" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="G73" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I73" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K73" s="2">
-        <v>46327.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L73" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="C74" t="s">
-        <v>134</v>
+        <v>21</v>
       </c>
       <c r="D74" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="F74" t="s">
-        <v>177</v>
+        <v>55</v>
+      </c>
+      <c r="G74" t="s">
+        <v>25</v>
       </c>
       <c r="I74" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J74" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.25</v>
       </c>
       <c r="K74" s="2">
-        <v>46329.583333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L74" t="s">
         <v>26</v>
@@ -3741,31 +3738,28 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
       <c r="D75" t="s">
-        <v>178</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="I75" t="s">
         <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46328.541666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L75" t="s">
         <v>26</v>
@@ -3773,124 +3767,133 @@
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C76" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D76" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="G76" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I76" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J76" s="2">
-        <v>46327.25</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K76" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L76" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>73</v>
+      </c>
+      <c r="C77" t="s">
+        <v>131</v>
       </c>
       <c r="D77" t="s">
-        <v>182</v>
+        <v>172</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F77" t="s">
-        <v>65</v>
+        <v>174</v>
       </c>
       <c r="I77" t="s">
         <v>19</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.708333333336</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K77" s="2">
-        <v>46328.833333333336</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L77" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="D78" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I78" t="s">
         <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K78" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L78" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B79" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="C79" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="D79" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>74</v>
+        <v>55</v>
+      </c>
+      <c r="G79" t="s">
+        <v>25</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J79" s="2">
-        <v>46329</v>
+        <v>46327.25</v>
       </c>
       <c r="K79" s="2">
-        <v>46330</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L79" t="s">
         <v>26</v>
@@ -3898,34 +3901,25 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>28</v>
-      </c>
-      <c r="C80" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>187</v>
-      </c>
-      <c r="E80" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F80" t="s">
-        <v>31</v>
-      </c>
-      <c r="G80" t="s">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="I80" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.25</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46329.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L80" t="s">
         <v>20</v>
@@ -3933,66 +3927,63 @@
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B81" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="D81" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F81" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="I81" t="s">
         <v>19</v>
       </c>
       <c r="J81" s="2">
-        <v>46329.333333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K81" s="2">
-        <v>46332.625</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L81" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B82" t="s">
-        <v>148</v>
+        <v>67</v>
       </c>
       <c r="C82" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="F82" t="s">
-        <v>31</v>
-      </c>
-      <c r="G82" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="I82" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J82" s="2">
-        <v>46329.791666666664</v>
+        <v>46329</v>
       </c>
       <c r="K82" s="2">
-        <v>46330.75</v>
+        <v>46330</v>
       </c>
       <c r="L82" t="s">
         <v>20</v>
@@ -4000,31 +3991,34 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B83" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="C83" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="D83" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F83" t="s">
-        <v>31</v>
+        <v>55</v>
+      </c>
+      <c r="G83" t="s">
+        <v>25</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J83" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.25</v>
       </c>
       <c r="K83" s="2">
-        <v>46334</v>
+        <v>46329.75</v>
       </c>
       <c r="L83" t="s">
         <v>26</v>
@@ -4032,60 +4026,66 @@
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B84" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C84" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="D84" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F84" t="s">
-        <v>31</v>
+        <v>174</v>
       </c>
       <c r="I84" t="s">
         <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K84" s="2">
-        <v>46334</v>
+        <v>46332.625</v>
       </c>
       <c r="L84" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B85" t="s">
-        <v>96</v>
+        <v>145</v>
       </c>
       <c r="C85" t="s">
-        <v>97</v>
+        <v>21</v>
       </c>
       <c r="D85" t="s">
-        <v>98</v>
+        <v>184</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>185</v>
       </c>
       <c r="F85" t="s">
-        <v>99</v>
+        <v>55</v>
+      </c>
+      <c r="G85" t="s">
+        <v>25</v>
       </c>
       <c r="I85" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.625</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K85" s="2">
-        <v>46331.125</v>
+        <v>46330.75</v>
       </c>
       <c r="L85" t="s">
         <v>26</v>
@@ -4093,159 +4093,156 @@
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B86" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C86" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D86" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F86" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="I86" t="s">
         <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K86" s="2">
-        <v>46333.925000000003</v>
+        <v>46334</v>
       </c>
       <c r="L86" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B87" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C87" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="D87" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="F87" t="s">
-        <v>177</v>
+        <v>55</v>
       </c>
       <c r="I87" t="s">
         <v>19</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K87" s="2">
-        <v>46333.925000000003</v>
+        <v>46334</v>
       </c>
       <c r="L87" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B88" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C88" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D88" t="s">
-        <v>125</v>
+        <v>92</v>
       </c>
       <c r="F88" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.625</v>
       </c>
       <c r="K88" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.125</v>
       </c>
       <c r="L88" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B89" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C89" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="D89" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F89" t="s">
-        <v>56</v>
+        <v>174</v>
       </c>
       <c r="I89" t="s">
         <v>19</v>
       </c>
       <c r="J89" s="2">
-        <v>46330.75</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K89" s="2">
-        <v>46332.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L89" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B90" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C90" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D90" t="s">
-        <v>197</v>
-      </c>
-      <c r="E90" s="1">
-        <v>10</v>
+        <v>190</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="F90" t="s">
-        <v>69</v>
-      </c>
-      <c r="G90" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="I90" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J90" s="2">
-        <v>46331.25</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K90" s="2">
-        <v>46331.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L90" t="s">
         <v>20</v>
@@ -4253,34 +4250,28 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B91" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="C91" t="s">
-        <v>14</v>
+        <v>86</v>
       </c>
       <c r="D91" t="s">
-        <v>198</v>
-      </c>
-      <c r="E91" s="1">
-        <v>1</v>
+        <v>122</v>
       </c>
       <c r="F91" t="s">
-        <v>69</v>
-      </c>
-      <c r="G91" t="s">
-        <v>18</v>
+        <v>89</v>
       </c>
       <c r="I91" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46331.25</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K91" s="2">
-        <v>46331.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L91" t="s">
         <v>20</v>
@@ -4288,37 +4279,31 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C92" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="D92" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="F92" t="s">
-        <v>62</v>
-      </c>
-      <c r="G92" t="s">
-        <v>18</v>
-      </c>
-      <c r="H92" t="s">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="I92" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.25</v>
+        <v>46330.75</v>
       </c>
       <c r="K92" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L92" t="s">
         <v>20</v>
@@ -4326,31 +4311,37 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B93" t="s">
         <v>52</v>
       </c>
       <c r="C93" t="s">
-        <v>106</v>
+        <v>21</v>
       </c>
       <c r="D93" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="F93" t="s">
+        <v>59</v>
+      </c>
+      <c r="G93" t="s">
+        <v>25</v>
+      </c>
+      <c r="H93" t="s">
+        <v>196</v>
+      </c>
+      <c r="I93" t="s">
         <v>56</v>
       </c>
-      <c r="I93" t="s">
-        <v>19</v>
-      </c>
       <c r="J93" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K93" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L93" t="s">
         <v>26</v>
@@ -4358,31 +4349,34 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B94" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="C94" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D94" t="s">
-        <v>204</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>163</v>
+        <v>197</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>177</v>
+        <v>66</v>
+      </c>
+      <c r="G94" t="s">
+        <v>25</v>
       </c>
       <c r="I94" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.25</v>
       </c>
       <c r="K94" s="2">
-        <v>46334.746527777781</v>
+        <v>46331.75</v>
       </c>
       <c r="L94" t="s">
         <v>26</v>
@@ -4390,31 +4384,34 @@
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B95" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="C95" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="D95" t="s">
-        <v>204</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>163</v>
+        <v>198</v>
+      </c>
+      <c r="E95" s="1">
+        <v>10</v>
       </c>
       <c r="F95" t="s">
-        <v>177</v>
+        <v>66</v>
+      </c>
+      <c r="G95" t="s">
+        <v>25</v>
       </c>
       <c r="I95" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.25</v>
       </c>
       <c r="K95" s="2">
-        <v>46334.746527777781</v>
+        <v>46331.75</v>
       </c>
       <c r="L95" t="s">
         <v>26</v>
@@ -4422,34 +4419,31 @@
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C96" t="s">
-        <v>14</v>
+        <v>103</v>
       </c>
       <c r="D96" t="s">
-        <v>198</v>
-      </c>
-      <c r="E96" s="1">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>200</v>
       </c>
       <c r="F96" t="s">
-        <v>69</v>
-      </c>
-      <c r="G96" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="I96" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K96" s="2">
-        <v>46332.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L96" t="s">
         <v>20</v>
@@ -4457,34 +4451,31 @@
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="C97" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D97" t="s">
-        <v>197</v>
-      </c>
-      <c r="E97" s="1">
-        <v>10</v>
+        <v>201</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="F97" t="s">
-        <v>69</v>
-      </c>
-      <c r="G97" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="I97" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K97" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L97" t="s">
         <v>20</v>
@@ -4492,37 +4483,31 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="C98" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="D98" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F98" t="s">
-        <v>62</v>
-      </c>
-      <c r="G98" t="s">
-        <v>18</v>
-      </c>
-      <c r="H98" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="I98" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L98" t="s">
         <v>20</v>
@@ -4530,31 +4515,34 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="C99" t="s">
-        <v>111</v>
+        <v>21</v>
       </c>
       <c r="D99" t="s">
-        <v>205</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
+      </c>
+      <c r="E99" s="1">
+        <v>1</v>
       </c>
       <c r="F99" t="s">
-        <v>24</v>
+        <v>66</v>
+      </c>
+      <c r="G99" t="s">
+        <v>25</v>
       </c>
       <c r="I99" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L99" t="s">
         <v>26</v>
@@ -4562,54 +4550,72 @@
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B100" t="s">
-        <v>88</v>
+        <v>145</v>
       </c>
       <c r="C100" t="s">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>198</v>
+      </c>
+      <c r="E100" s="1">
+        <v>10</v>
       </c>
       <c r="F100" t="s">
-        <v>92</v>
+        <v>66</v>
+      </c>
+      <c r="G100" t="s">
+        <v>25</v>
       </c>
       <c r="I100" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J100" s="2">
-        <v>46332.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L100" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>145</v>
+      </c>
+      <c r="C101" t="s">
+        <v>21</v>
       </c>
       <c r="D101" t="s">
-        <v>207</v>
+        <v>194</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="F101" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="G101" t="s">
+        <v>25</v>
+      </c>
+      <c r="H101" t="s">
+        <v>196</v>
       </c>
       <c r="I101" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J101" s="2">
-        <v>46332.375</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K101" s="2">
-        <v>46333.5</v>
+        <v>46332.75</v>
       </c>
       <c r="L101" t="s">
         <v>26</v>
@@ -4622,52 +4628,58 @@
       <c r="B102" t="s">
         <v>13</v>
       </c>
+      <c r="C102" t="s">
+        <v>108</v>
+      </c>
       <c r="D102" t="s">
-        <v>207</v>
+        <v>202</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F102" t="s">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="I102" t="s">
         <v>19</v>
       </c>
       <c r="J102" s="2">
-        <v>46332.375</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K102" s="2">
-        <v>46333.5</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L102" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B103" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C103" t="s">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="D103" t="s">
-        <v>123</v>
+        <v>151</v>
       </c>
       <c r="F103" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="I103" t="s">
         <v>19</v>
       </c>
       <c r="J103" s="2">
-        <v>46332.541666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K103" s="2">
-        <v>46333.041666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>124</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4677,29 +4689,23 @@
       <c r="B104" t="s">
         <v>13</v>
       </c>
-      <c r="C104" t="s">
-        <v>34</v>
-      </c>
       <c r="D104" t="s">
-        <v>208</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="F104" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="I104" t="s">
         <v>19</v>
       </c>
       <c r="J104" s="2">
-        <v>46332.875</v>
+        <v>46332.375</v>
       </c>
       <c r="K104" s="2">
-        <v>46334.25</v>
+        <v>46333.5</v>
       </c>
       <c r="L104" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4709,212 +4715,203 @@
       <c r="B105" t="s">
         <v>13</v>
       </c>
-      <c r="C105" t="s">
-        <v>47</v>
-      </c>
       <c r="D105" t="s">
-        <v>210</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F105" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I105" t="s">
         <v>19</v>
       </c>
       <c r="J105" s="2">
-        <v>46333</v>
+        <v>46332.375</v>
       </c>
       <c r="K105" s="2">
-        <v>46334</v>
+        <v>46333.5</v>
       </c>
       <c r="L105" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="C106" t="s">
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="D106" t="s">
-        <v>210</v>
-      </c>
-      <c r="E106" s="1" t="s">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="F106" t="s">
-        <v>50</v>
+        <v>93</v>
       </c>
       <c r="I106" t="s">
         <v>19</v>
       </c>
       <c r="J106" s="2">
-        <v>46333</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K106" s="2">
-        <v>46334</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L106" t="s">
-        <v>26</v>
+        <v>121</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
+        <v>12</v>
+      </c>
+      <c r="B107" t="s">
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
         <v>27</v>
       </c>
-      <c r="B107" t="s">
-        <v>70</v>
-      </c>
       <c r="D107" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F107" t="s">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="I107" t="s">
         <v>19</v>
       </c>
       <c r="J107" s="2">
-        <v>46333.041666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K107" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="L107" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>13</v>
+      </c>
+      <c r="C108" t="s">
+        <v>42</v>
       </c>
       <c r="D108" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="F108" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="I108" t="s">
         <v>19</v>
       </c>
       <c r="J108" s="2">
-        <v>46333.041666666664</v>
+        <v>46333</v>
       </c>
       <c r="K108" s="2">
-        <v>46335.041666666664</v>
+        <v>46334</v>
       </c>
       <c r="L108" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>88</v>
+        <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>119</v>
+        <v>42</v>
       </c>
       <c r="D109" t="s">
-        <v>120</v>
+        <v>207</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="F109" t="s">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="I109" t="s">
         <v>19</v>
       </c>
       <c r="J109" s="2">
-        <v>46333.416666666664</v>
+        <v>46333</v>
       </c>
       <c r="K109" s="2">
-        <v>46333.75</v>
+        <v>46334</v>
       </c>
       <c r="L109" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
-      </c>
-      <c r="C110" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D110" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F110" t="s">
-        <v>17</v>
+        <v>71</v>
       </c>
       <c r="I110" t="s">
         <v>19</v>
       </c>
       <c r="J110" s="2">
-        <v>46333.666666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K110" s="2">
         <v>46335.041666666664</v>
       </c>
       <c r="L110" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B111" t="s">
-        <v>28</v>
-      </c>
-      <c r="C111" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="D111" t="s">
-        <v>216</v>
-      </c>
-      <c r="E111" s="1">
-        <v>11</v>
+        <v>209</v>
+      </c>
+      <c r="E111" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F111" t="s">
-        <v>69</v>
-      </c>
-      <c r="G111" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="I111" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J111" s="2">
-        <v>46334.25</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K111" s="2">
-        <v>46334.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L111" t="s">
         <v>20</v>
@@ -4922,66 +4919,60 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B112" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C112" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="D112" t="s">
-        <v>217</v>
-      </c>
-      <c r="E112" s="1" t="s">
-        <v>218</v>
+        <v>117</v>
       </c>
       <c r="F112" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="I112" t="s">
         <v>19</v>
       </c>
       <c r="J112" s="2">
-        <v>46334.958333333336</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K112" s="2">
-        <v>46337.708333333336</v>
+        <v>46333.75</v>
       </c>
       <c r="L112" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>148</v>
+        <v>13</v>
       </c>
       <c r="C113" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D113" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="F113" t="s">
-        <v>31</v>
-      </c>
-      <c r="G113" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I113" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="J113" s="2">
-        <v>46335.25</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K113" s="2">
-        <v>46335.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L113" t="s">
         <v>20</v>
@@ -4989,98 +4980,101 @@
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="C114" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D114" t="s">
-        <v>219</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>220</v>
+        <v>213</v>
+      </c>
+      <c r="E114" s="1">
+        <v>11</v>
       </c>
       <c r="F114" t="s">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="G114" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I114" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J114" s="2">
-        <v>46335.791666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K114" s="2">
-        <v>46336.75</v>
+        <v>46334.75</v>
       </c>
       <c r="L114" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C115" t="s">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="D115" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F115" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="I115" t="s">
         <v>19</v>
       </c>
       <c r="J115" s="2">
-        <v>46337</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K115" s="2">
-        <v>46339</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L115" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>145</v>
       </c>
       <c r="C116" t="s">
-        <v>71</v>
+        <v>21</v>
       </c>
       <c r="D116" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="F116" t="s">
-        <v>74</v>
+        <v>55</v>
+      </c>
+      <c r="G116" t="s">
+        <v>25</v>
       </c>
       <c r="I116" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="J116" s="2">
-        <v>46337.208333333336</v>
+        <v>46335.25</v>
       </c>
       <c r="K116" s="2">
-        <v>46340.208333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L116" t="s">
         <v>26</v>
@@ -5088,124 +5082,133 @@
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B117" t="s">
-        <v>148</v>
+        <v>52</v>
       </c>
       <c r="C117" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D117" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="F117" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="G117" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="I117" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J117" s="2">
-        <v>46337.25</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K117" s="2">
-        <v>46337.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L117" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B118" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="C118" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D118" t="s">
-        <v>90</v>
+        <v>218</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="F118" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="I118" t="s">
         <v>19</v>
       </c>
       <c r="J118" s="2">
-        <v>46337.333333333336</v>
+        <v>46337</v>
       </c>
       <c r="K118" s="2">
-        <v>46337.833333333336</v>
+        <v>46339</v>
       </c>
       <c r="L118" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B119" t="s">
-        <v>96</v>
+        <v>67</v>
       </c>
       <c r="C119" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
       <c r="D119" t="s">
-        <v>98</v>
+        <v>220</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="F119" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="I119" t="s">
-        <v>101</v>
+        <v>19</v>
       </c>
       <c r="J119" s="2">
-        <v>46337.625</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K119" s="2">
-        <v>46338.125</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L119" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B120" t="s">
-        <v>52</v>
+        <v>145</v>
       </c>
       <c r="C120" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D120" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="F120" t="s">
+        <v>55</v>
+      </c>
+      <c r="G120" t="s">
+        <v>25</v>
+      </c>
+      <c r="I120" t="s">
         <v>56</v>
       </c>
-      <c r="I120" t="s">
-        <v>19</v>
-      </c>
       <c r="J120" s="2">
+        <v>46337.25</v>
+      </c>
+      <c r="K120" s="2">
         <v>46337.75</v>
-      </c>
-      <c r="K120" s="2">
-        <v>46339.75</v>
       </c>
       <c r="L120" t="s">
         <v>26</v>
@@ -5213,63 +5216,60 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B121" t="s">
-        <v>13</v>
+        <v>85</v>
       </c>
       <c r="C121" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="D121" t="s">
-        <v>229</v>
+        <v>87</v>
       </c>
       <c r="F121" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="I121" t="s">
         <v>19</v>
       </c>
       <c r="J121" s="2">
-        <v>46338.431250000001</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K121" s="2">
-        <v>46339.472916666666</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L121" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="B122" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="C122" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="D122" t="s">
-        <v>230</v>
-      </c>
-      <c r="E122" s="1" t="s">
-        <v>231</v>
+        <v>92</v>
       </c>
       <c r="F122" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="I122" t="s">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="J122" s="2">
-        <v>46338.709027777775</v>
+        <v>46337.625</v>
       </c>
       <c r="K122" s="2">
-        <v>46339.584027777775</v>
+        <v>46338.125</v>
       </c>
       <c r="L122" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:12">
@@ -5277,95 +5277,92 @@
         <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="C123" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D123" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="F123" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="I123" t="s">
         <v>19</v>
       </c>
       <c r="J123" s="2">
-        <v>46338.791666666664</v>
+        <v>46337.75</v>
       </c>
       <c r="K123" s="2">
-        <v>46340.166666666664</v>
+        <v>46339.75</v>
       </c>
       <c r="L123" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C124" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D124" t="s">
-        <v>234</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="F124" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="I124" t="s">
         <v>19</v>
       </c>
       <c r="J124" s="2">
-        <v>46338.958333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K124" s="2">
-        <v>46342.208333333336</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L124" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="125" spans="1:12">
       <c r="A125" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="C125" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="D125" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F125" t="s">
-        <v>82</v>
+        <v>51</v>
       </c>
       <c r="I125" t="s">
         <v>19</v>
       </c>
       <c r="J125" s="2">
-        <v>46338.958333333336</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K125" s="2">
-        <v>46342.208333333336</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L125" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:12">
@@ -5376,86 +5373,182 @@
         <v>13</v>
       </c>
       <c r="C126" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D126" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F126" t="s">
-        <v>177</v>
+        <v>30</v>
       </c>
       <c r="I126" t="s">
         <v>19</v>
       </c>
       <c r="J126" s="2">
-        <v>46339.083333333336</v>
+        <v>46338.791666666664</v>
       </c>
       <c r="K126" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.166666666664</v>
       </c>
       <c r="L126" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B127" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="C127" t="s">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="D127" t="s">
-        <v>123</v>
+        <v>231</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="F127" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="I127" t="s">
         <v>19</v>
       </c>
       <c r="J127" s="2">
-        <v>46339.541666666664</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K127" s="2">
-        <v>46340.041666666664</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L127" t="s">
-        <v>124</v>
+        <v>20</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B128" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="C128" t="s">
+        <v>74</v>
+      </c>
+      <c r="D128" t="s">
+        <v>231</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F128" t="s">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s">
+        <v>19</v>
+      </c>
+      <c r="J128" s="2">
+        <v>46338.958333333336</v>
+      </c>
+      <c r="K128" s="2">
+        <v>46342.208333333336</v>
+      </c>
+      <c r="L128" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>12</v>
+      </c>
+      <c r="B129" t="s">
+        <v>13</v>
+      </c>
+      <c r="C129" t="s">
+        <v>42</v>
+      </c>
+      <c r="D129" t="s">
+        <v>233</v>
+      </c>
+      <c r="E129" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="F129" t="s">
+        <v>174</v>
+      </c>
+      <c r="I129" t="s">
+        <v>19</v>
+      </c>
+      <c r="J129" s="2">
+        <v>46339.083333333336</v>
+      </c>
+      <c r="K129" s="2">
+        <v>46340.291666666664</v>
+      </c>
+      <c r="L129" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>33</v>
+      </c>
+      <c r="B130" t="s">
+        <v>90</v>
+      </c>
+      <c r="C130" t="s">
+        <v>119</v>
+      </c>
+      <c r="D130" t="s">
+        <v>120</v>
+      </c>
+      <c r="F130" t="s">
+        <v>93</v>
+      </c>
+      <c r="I130" t="s">
+        <v>19</v>
+      </c>
+      <c r="J130" s="2">
+        <v>46339.541666666664</v>
+      </c>
+      <c r="K130" s="2">
+        <v>46340.041666666664</v>
+      </c>
+      <c r="L130" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>33</v>
+      </c>
+      <c r="B131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C131" t="s">
+        <v>86</v>
+      </c>
+      <c r="D131" t="s">
+        <v>122</v>
+      </c>
+      <c r="F131" t="s">
         <v>89</v>
       </c>
-      <c r="D128" t="s">
-        <v>125</v>
-      </c>
-      <c r="F128" t="s">
-        <v>92</v>
-      </c>
-      <c r="I128" t="s">
-        <v>19</v>
-      </c>
-      <c r="J128" s="2">
+      <c r="I131" t="s">
+        <v>19</v>
+      </c>
+      <c r="J131" s="2">
         <v>46339.704861111109</v>
       </c>
-      <c r="K128" s="2">
+      <c r="K131" s="2">
         <v>46340.204861111109</v>
       </c>
-      <c r="L128" t="s">
-        <v>26</v>
+      <c r="L131" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -5467,15 +5560,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5483,13 +5567,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5627,18 +5711,27 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-17.xlsx
+++ b/data/vessels/2026-10-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433156" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B5A69DC-A7CF-4414-88CA-D95D5BB62291}"/>
+  <xr:revisionPtr revIDLastSave="433430" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B93023C9-DA8C-4454-B058-94159EBDFDDE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="230">
   <si>
     <t>Harbor</t>
   </si>
@@ -83,441 +83,426 @@
     <t>T18</t>
   </si>
   <si>
+    <t>PNW1</t>
+  </si>
+  <si>
+    <t>OOCL NEW YORK</t>
+  </si>
+  <si>
+    <t>122E/122W</t>
+  </si>
+  <si>
+    <t>OOCL</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER ELITE</t>
+  </si>
+  <si>
+    <t>186W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINES</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC636A</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
+  </si>
+  <si>
+    <t>Matson - HI2</t>
+  </si>
+  <si>
+    <t>MAUNAWILI</t>
+  </si>
+  <si>
+    <t>642S</t>
+  </si>
+  <si>
+    <t>Tote - AK2</t>
+  </si>
+  <si>
+    <t>NORTH STAR</t>
+  </si>
+  <si>
+    <t>Waiting 3.1 days</t>
+  </si>
+  <si>
+    <t>RJ PFEIFFER</t>
+  </si>
+  <si>
+    <t>POLARIS MILA</t>
+  </si>
+  <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
+    <t>SM PORTLAND</t>
+  </si>
+  <si>
+    <t>PN3</t>
+  </si>
+  <si>
+    <t>YM WEALTH</t>
+  </si>
+  <si>
+    <t>193E</t>
+  </si>
+  <si>
+    <t>EVER SALUTE</t>
+  </si>
+  <si>
+    <t>494-129E</t>
+  </si>
+  <si>
+    <t>CMA CGM FORT JAMES</t>
+  </si>
+  <si>
+    <t>CPN040S19</t>
+  </si>
+  <si>
+    <t>COSCO VENICE</t>
+  </si>
+  <si>
+    <t>081N/081S</t>
+  </si>
+  <si>
+    <t>MSC IVANA</t>
+  </si>
+  <si>
+    <t>UK638A</t>
+  </si>
+  <si>
+    <t>YM PLUM</t>
+  </si>
+  <si>
+    <t>197E</t>
+  </si>
+  <si>
+    <t>YM TUTORIAL</t>
+  </si>
+  <si>
+    <t>Blair</t>
+  </si>
+  <si>
+    <t>LIBERTY PASSION</t>
+  </si>
+  <si>
+    <t>FRANKFURT EXPRESS</t>
+  </si>
+  <si>
+    <t>640E/643W</t>
+  </si>
+  <si>
+    <t>PATARA</t>
+  </si>
+  <si>
+    <t>005A</t>
+  </si>
+  <si>
+    <t>MATSON KODIAK</t>
+  </si>
+  <si>
+    <t>EVER MODE</t>
+  </si>
+  <si>
+    <t>1473-010E</t>
+  </si>
+  <si>
+    <t>Oceania</t>
+  </si>
+  <si>
+    <t>CMA CGM DUTCH HARBOR</t>
+  </si>
+  <si>
+    <t>638N</t>
+  </si>
+  <si>
+    <t>MSC NITYA B</t>
+  </si>
+  <si>
+    <t>MC637A</t>
+  </si>
+  <si>
     <t>EB Service 2</t>
   </si>
   <si>
-    <t>SUVA CHIEF</t>
-  </si>
-  <si>
-    <t>007E/008W</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>Talon Marine Services LLC</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>CMA CGM BYBLOS</t>
-  </si>
-  <si>
-    <t>CPN00/CPN01</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>PNW1</t>
-  </si>
-  <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
-  </si>
-  <si>
-    <t>OOCL</t>
-  </si>
-  <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Tacoma</t>
-  </si>
-  <si>
-    <t>Husky</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
-    <t>Matson - HI2</t>
-  </si>
-  <si>
-    <t>MAUNAWILI</t>
-  </si>
-  <si>
-    <t>642S</t>
-  </si>
-  <si>
-    <t>Tote - AK2</t>
-  </si>
-  <si>
-    <t>NORTH STAR</t>
-  </si>
-  <si>
-    <t>Waiting 3.1 days</t>
-  </si>
-  <si>
-    <t>RJ PFEIFFER</t>
-  </si>
-  <si>
-    <t>POLARIS MILA</t>
-  </si>
-  <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
-    <t>SM PORTLAND</t>
-  </si>
-  <si>
-    <t>PN3</t>
-  </si>
-  <si>
-    <t>YM WEALTH</t>
-  </si>
-  <si>
-    <t>193E</t>
-  </si>
-  <si>
-    <t>EVER SALUTE</t>
-  </si>
-  <si>
-    <t>494-129E</t>
-  </si>
-  <si>
-    <t>CMA CGM FORT JAMES</t>
-  </si>
-  <si>
-    <t>CPN040S19</t>
-  </si>
-  <si>
-    <t>COSCO VENICE</t>
-  </si>
-  <si>
-    <t>081N/081S</t>
-  </si>
-  <si>
-    <t>MSC IVANA</t>
-  </si>
-  <si>
-    <t>UK638A</t>
-  </si>
-  <si>
-    <t>YM PLUM</t>
-  </si>
-  <si>
-    <t>197E</t>
-  </si>
-  <si>
-    <t>YM TUTORIAL</t>
-  </si>
-  <si>
-    <t>Blair</t>
-  </si>
-  <si>
-    <t>LIBERTY PASSION</t>
-  </si>
-  <si>
-    <t>FRANKFURT EXPRESS</t>
-  </si>
-  <si>
-    <t>640E/643W</t>
-  </si>
-  <si>
-    <t>PATARA</t>
-  </si>
-  <si>
-    <t>005A</t>
-  </si>
-  <si>
-    <t>MATSON KODIAK</t>
-  </si>
-  <si>
-    <t>EVER MODE</t>
-  </si>
-  <si>
-    <t>1473-010E</t>
-  </si>
-  <si>
-    <t>Oceania</t>
-  </si>
-  <si>
-    <t>CMA CGM DUTCH HARBOR</t>
-  </si>
-  <si>
-    <t>638N</t>
-  </si>
-  <si>
-    <t>MSC NITYA B</t>
-  </si>
-  <si>
-    <t>MC637A</t>
-  </si>
-  <si>
     <t>NADI CHIEF</t>
   </si>
   <si>
@@ -542,18 +527,18 @@
     <t>NBBT0001E</t>
   </si>
   <si>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
+  </si>
+  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
     <t>KW665</t>
   </si>
   <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
     <t>MANULANI</t>
   </si>
   <si>
@@ -623,6 +608,12 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -630,12 +621,6 @@
   </si>
   <si>
     <t>Jones Stevedoring Co</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -816,10 +801,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L131" totalsRowShown="0">
-  <autoFilter ref="A1:L131" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L131">
-    <sortCondition ref="J2:J131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L128" totalsRowShown="0">
+  <autoFilter ref="A1:L128" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L128">
+    <sortCondition ref="J2:J128"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1156,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1230,17 +1215,20 @@
       <c r="G2" t="s">
         <v>18</v>
       </c>
+      <c r="H2" t="s">
+        <v>19</v>
+      </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J2" s="2">
-        <v>46310.583333333336</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K2" s="2">
-        <v>46312.708333333336</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1265,87 +1253,90 @@
       <c r="G3" t="s">
         <v>18</v>
       </c>
+      <c r="H3" t="s">
+        <v>19</v>
+      </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2">
-        <v>46310.583333333336</v>
+        <v>46312.208333333336</v>
       </c>
       <c r="K3" s="2">
-        <v>46312.708333333336</v>
+        <v>46313.166666666664</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J4" s="2">
-        <v>46310.583333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K4" s="2">
-        <v>46312.708333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F5" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2">
-        <v>46310.583333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K5" s="2">
-        <v>46312.708333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:12">
@@ -1356,34 +1347,31 @@
         <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" t="s">
-        <v>31</v>
-      </c>
-      <c r="H6" t="s">
-        <v>32</v>
-      </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K6" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:12">
@@ -1394,174 +1382,171 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J7" s="2">
-        <v>46312.208333333336</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K7" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G8" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J8" s="2">
-        <v>46312.3125</v>
+        <v>46313.25</v>
       </c>
       <c r="K8" s="2">
         <v>46314.75</v>
       </c>
       <c r="L8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D9" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J9" s="2">
-        <v>46312.3125</v>
+        <v>46314.25</v>
       </c>
       <c r="K9" s="2">
         <v>46314.75</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F10" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J10" s="2">
-        <v>46312.541666666664</v>
+        <v>46314.25</v>
       </c>
       <c r="K10" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L10" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
+      </c>
+      <c r="E11" s="1">
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="G11" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="2">
-        <v>46313.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K11" s="2">
-        <v>46314.208333333336</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -1569,104 +1554,104 @@
         <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" t="s">
-        <v>48</v>
+        <v>13</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>19</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J12" s="2">
-        <v>46313.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K12" s="2">
-        <v>46314.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>54</v>
+        <v>58</v>
+      </c>
+      <c r="E13" s="1">
+        <v>2</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I13" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J13" s="2">
-        <v>46314.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K13" s="2">
-        <v>46314.75</v>
+        <v>46315.75</v>
       </c>
       <c r="L13" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="G14" t="s">
-        <v>25</v>
+        <v>65</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J14" s="2">
-        <v>46314.25</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K14" s="2">
-        <v>46314.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L14" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:12">
@@ -1674,1064 +1659,1058 @@
         <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>38</v>
+      </c>
+      <c r="C15" t="s">
+        <v>39</v>
       </c>
       <c r="D15" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="G15" t="s">
-        <v>25</v>
-      </c>
-      <c r="H15" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J15" s="2">
-        <v>46314.625</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46315.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="1">
-        <v>34</v>
+        <v>70</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="G16" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="2">
-        <v>46314.625</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K16" s="2">
-        <v>46318.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="1">
-        <v>2</v>
+        <v>73</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>74</v>
       </c>
       <c r="F17" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G17" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="H17" t="s">
+        <v>75</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J17" s="2">
-        <v>46315.208333333336</v>
+        <v>46316.25</v>
       </c>
       <c r="K17" s="2">
-        <v>46315.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L17" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>68</v>
+        <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
+      </c>
+      <c r="E18" s="1">
+        <v>63</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J18" s="2">
-        <v>46315.208333333336</v>
+        <v>46316.25</v>
       </c>
       <c r="K18" s="2">
-        <v>46317.166666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L18" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s">
-        <v>31</v>
+        <v>82</v>
+      </c>
+      <c r="H19" t="s">
+        <v>19</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J19" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K19" s="2">
-        <v>46317.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C20" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F20" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="G20" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K20" s="2">
-        <v>46317.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="G21" t="s">
-        <v>25</v>
-      </c>
-      <c r="H21" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J21" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K21" s="2">
-        <v>46316.75</v>
+        <v>46319.75</v>
       </c>
       <c r="L21" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E22" s="1">
-        <v>63</v>
+        <v>26169</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>31</v>
+        <v>90</v>
+      </c>
+      <c r="H22" t="s">
+        <v>90</v>
       </c>
       <c r="I22" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="J22" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K22" s="2">
-        <v>46316.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L22" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s">
-        <v>89</v>
+        <v>28</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J23" s="2">
-        <v>46316.291666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K23" s="2">
-        <v>46316.916666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L23" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
-      </c>
-      <c r="C24" t="s">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="D24" t="s">
-        <v>92</v>
-      </c>
-      <c r="E24" s="1">
-        <v>26169</v>
+        <v>93</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>94</v>
       </c>
       <c r="F24" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="G24" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J24" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K24" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F25" t="s">
-        <v>98</v>
-      </c>
-      <c r="G25" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25" s="2">
-        <v>46316.625</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46319.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="C26" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D26" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
+      </c>
+      <c r="E26" s="1">
+        <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G26" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J26" s="2">
-        <v>46316.625</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K26" s="2">
-        <v>46319.75</v>
+        <v>46320.75</v>
       </c>
       <c r="L26" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D27" t="s">
-        <v>80</v>
-      </c>
-      <c r="E27" s="1" t="s">
         <v>99</v>
       </c>
+      <c r="E27" s="1">
+        <v>1</v>
+      </c>
       <c r="F27" t="s">
-        <v>59</v>
+        <v>100</v>
       </c>
       <c r="G27" t="s">
-        <v>25</v>
-      </c>
-      <c r="H27" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="I27" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J27" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46317.75</v>
+        <v>46320.75</v>
       </c>
       <c r="L27" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>101</v>
       </c>
       <c r="D28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>71</v>
-      </c>
-      <c r="G28" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J28" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K28" s="2">
-        <v>46318.708333333336</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
-      </c>
-      <c r="E29" s="1" t="s">
         <v>105</v>
       </c>
       <c r="F29" t="s">
-        <v>51</v>
+        <v>82</v>
+      </c>
+      <c r="G29" t="s">
+        <v>82</v>
+      </c>
+      <c r="H29" t="s">
+        <v>19</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J29" s="2">
-        <v>46317.291666666664</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K29" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D30" t="s">
         <v>106</v>
       </c>
-      <c r="E30" s="1">
-        <v>1</v>
+      <c r="E30" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="F30" t="s">
-        <v>107</v>
+        <v>52</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I30" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J30" s="2">
-        <v>46317.541666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K30" s="2">
-        <v>46320.75</v>
+        <v>46318.75</v>
       </c>
       <c r="L30" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="C31" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
+        <v>108</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="F31" t="s">
-        <v>107</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s">
-        <v>25</v>
+        <v>18</v>
+      </c>
+      <c r="H31" t="s">
+        <v>19</v>
       </c>
       <c r="I31" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J31" s="2">
-        <v>46317.541666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K31" s="2">
-        <v>46320.75</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C32" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D32" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
+        <v>82</v>
+      </c>
+      <c r="G32" t="s">
+        <v>82</v>
+      </c>
+      <c r="H32" t="s">
+        <v>19</v>
       </c>
       <c r="I32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J32" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K32" s="2">
-        <v>46318.969444444447</v>
+        <v>46319.125</v>
       </c>
       <c r="L32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
+        <v>114</v>
+      </c>
+      <c r="E33" s="1">
+        <v>26168</v>
       </c>
       <c r="F33" t="s">
         <v>89</v>
       </c>
       <c r="G33" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H33" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J33" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.625</v>
       </c>
       <c r="K33" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L33" t="s">
-        <v>26</v>
+        <v>115</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C34" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="F34" t="s">
-        <v>55</v>
-      </c>
-      <c r="G34" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K34" s="2">
-        <v>46318.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L34" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C35" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
+      </c>
+      <c r="E35" s="1">
+        <v>4</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>59</v>
       </c>
       <c r="G35" t="s">
-        <v>31</v>
-      </c>
-      <c r="H35" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J35" s="2">
-        <v>46318.25</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K35" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L35" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B36" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="D36" t="s">
         <v>117</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>118</v>
+      <c r="E36" s="1">
+        <v>4</v>
       </c>
       <c r="F36" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G36" t="s">
-        <v>89</v>
-      </c>
-      <c r="H36" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J36" s="2">
-        <v>46318.291666666664</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K36" s="2">
-        <v>46319.125</v>
+        <v>46319.75</v>
       </c>
       <c r="L36" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B37" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
+        <v>44</v>
+      </c>
+      <c r="D37" t="s">
+        <v>118</v>
+      </c>
+      <c r="E37" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D37" t="s">
-        <v>120</v>
-      </c>
-      <c r="E37" s="1">
-        <v>26168</v>
-      </c>
       <c r="F37" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s">
-        <v>94</v>
-      </c>
-      <c r="H37" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="J37" s="2">
-        <v>46318.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K37" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L37" t="s">
-        <v>121</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F38" t="s">
         <v>122</v>
       </c>
-      <c r="E38" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F38" t="s">
-        <v>89</v>
+      <c r="G38" t="s">
+        <v>18</v>
+      </c>
+      <c r="H38" t="s">
+        <v>123</v>
       </c>
       <c r="I38" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J38" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K38" s="2">
-        <v>46319.204861111109</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D39" t="s">
+        <v>120</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F39" t="s">
+        <v>122</v>
+      </c>
+      <c r="G39" t="s">
+        <v>18</v>
+      </c>
+      <c r="H39" t="s">
         <v>123</v>
       </c>
-      <c r="E39" s="1">
-        <v>4</v>
-      </c>
-      <c r="F39" t="s">
-        <v>66</v>
-      </c>
-      <c r="G39" t="s">
-        <v>25</v>
-      </c>
       <c r="I39" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J39" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L39" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="C40" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>123</v>
-      </c>
-      <c r="E40" s="1">
-        <v>4</v>
+        <v>118</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="F40" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G40" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J40" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.25</v>
       </c>
       <c r="K40" s="2">
         <v>46319.75</v>
       </c>
       <c r="L40" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>52</v>
-      </c>
-      <c r="C41" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D41" t="s">
         <v>124</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="F41" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G41" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="H41" t="s">
+        <v>19</v>
       </c>
       <c r="I41" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J41" s="2">
-        <v>46319.25</v>
+        <v>46319.625</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B42" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F42" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G42" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J42" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K42" s="2">
-        <v>46319.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L42" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="C43" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D43" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F43" t="s">
-        <v>128</v>
-      </c>
-      <c r="G43" t="s">
-        <v>31</v>
-      </c>
-      <c r="H43" t="s">
-        <v>129</v>
+        <v>64</v>
       </c>
       <c r="I43" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K43" s="2">
-        <v>46320.166666666664</v>
+        <v>46322</v>
       </c>
       <c r="L43" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B44" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="C44" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F44" t="s">
-        <v>128</v>
-      </c>
-      <c r="G44" t="s">
-        <v>31</v>
-      </c>
-      <c r="H44" t="s">
-        <v>129</v>
+        <v>32</v>
       </c>
       <c r="I44" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.25</v>
+        <v>46320.21875</v>
       </c>
       <c r="K44" s="2">
-        <v>46320.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L44" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="45" spans="1:12">
@@ -2741,1540 +2720,1546 @@
       <c r="B45" t="s">
         <v>13</v>
       </c>
+      <c r="C45" t="s">
+        <v>33</v>
+      </c>
       <c r="D45" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>61</v>
+        <v>133</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="G45" t="s">
-        <v>25</v>
-      </c>
-      <c r="H45" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.625</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K45" s="2">
-        <v>46320.166666666664</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="C46" t="s">
-        <v>131</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F46" t="s">
-        <v>77</v>
-      </c>
-      <c r="G46" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J46" s="2">
-        <v>46319.666666666664</v>
+        <v>46321.21875</v>
       </c>
       <c r="K46" s="2">
-        <v>46321.75</v>
+        <v>46323.21875</v>
       </c>
       <c r="L46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C47" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F47" t="s">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="G47" t="s">
+        <v>18</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J47" s="2">
-        <v>46320</v>
+        <v>46321.25</v>
       </c>
       <c r="K47" s="2">
-        <v>46322</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C48" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="E48" s="1">
+        <v>21</v>
       </c>
       <c r="F48" t="s">
-        <v>24</v>
+        <v>72</v>
+      </c>
+      <c r="G48" t="s">
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J48" s="2">
-        <v>46320.21875</v>
+        <v>46321.625</v>
       </c>
       <c r="K48" s="2">
-        <v>46324.59375</v>
+        <v>46325.75</v>
       </c>
       <c r="L48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C49" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F49" t="s">
-        <v>45</v>
+        <v>122</v>
       </c>
       <c r="G49" t="s">
-        <v>46</v>
+        <v>18</v>
+      </c>
+      <c r="H49" t="s">
+        <v>123</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.208333333336</v>
+        <v>46322.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46322.166666666664</v>
+        <v>46322.75</v>
       </c>
       <c r="L49" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C50" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F50" t="s">
-        <v>51</v>
+        <v>85</v>
+      </c>
+      <c r="G50" t="s">
+        <v>28</v>
       </c>
       <c r="I50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.21875</v>
+        <v>46322.625</v>
       </c>
       <c r="K50" s="2">
-        <v>46323.21875</v>
+        <v>46325.75</v>
       </c>
       <c r="L50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C51" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D51" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F51" t="s">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="G51" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.25</v>
+        <v>46323.25</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L51" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C52" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D52" t="s">
-        <v>144</v>
-      </c>
-      <c r="E52" s="1">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="F52" t="s">
-        <v>77</v>
-      </c>
-      <c r="G52" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J52" s="2">
-        <v>46321.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K52" s="2">
-        <v>46325.75</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L52" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>145</v>
+        <v>86</v>
       </c>
       <c r="C53" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>88</v>
+      </c>
+      <c r="E53" s="1">
+        <v>26173</v>
       </c>
       <c r="F53" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="G53" t="s">
-        <v>31</v>
+        <v>90</v>
       </c>
       <c r="H53" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="I53" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="J53" s="2">
-        <v>46322.25</v>
+        <v>46323.625</v>
       </c>
       <c r="K53" s="2">
-        <v>46322.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C54" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F54" t="s">
-        <v>98</v>
+        <v>52</v>
       </c>
       <c r="G54" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J54" s="2">
-        <v>46322.625</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K54" s="2">
-        <v>46325.75</v>
+        <v>46324.75</v>
       </c>
       <c r="L54" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
-      </c>
-      <c r="C55" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D55" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
-      </c>
-      <c r="G55" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="I55" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.25</v>
+        <v>46324</v>
       </c>
       <c r="K55" s="2">
-        <v>46323.75</v>
+        <v>46326</v>
       </c>
       <c r="L55" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B56" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C56" t="s">
-        <v>86</v>
+        <v>148</v>
       </c>
       <c r="D56" t="s">
-        <v>151</v>
+        <v>149</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F56" t="s">
-        <v>89</v>
+        <v>32</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.291666666664</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K56" s="2">
-        <v>46323.791666666664</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L56" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="C57" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D57" t="s">
-        <v>92</v>
-      </c>
-      <c r="E57" s="1">
-        <v>26173</v>
+        <v>151</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="F57" t="s">
-        <v>93</v>
-      </c>
-      <c r="G57" t="s">
-        <v>94</v>
-      </c>
-      <c r="H57" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.625</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K57" s="2">
-        <v>46324.041666666664</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="C58" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="D58" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F58" t="s">
-        <v>55</v>
-      </c>
-      <c r="G58" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="I58" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J58" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K58" s="2">
-        <v>46324.75</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L58" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>78</v>
+      </c>
+      <c r="C59" t="s">
+        <v>79</v>
       </c>
       <c r="D59" t="s">
-        <v>152</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="F59" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J59" s="2">
-        <v>46324</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K59" s="2">
-        <v>46326</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C60" t="s">
-        <v>154</v>
+        <v>113</v>
       </c>
       <c r="D60" t="s">
-        <v>155</v>
-      </c>
-      <c r="E60" s="1" t="s">
-        <v>156</v>
+        <v>114</v>
+      </c>
+      <c r="E60" s="1">
+        <v>26172</v>
       </c>
       <c r="F60" t="s">
-        <v>24</v>
+        <v>89</v>
+      </c>
+      <c r="G60" t="s">
+        <v>90</v>
+      </c>
+      <c r="H60" t="s">
+        <v>90</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J60" s="2">
-        <v>46324.647916666669</v>
+        <v>46325.625</v>
       </c>
       <c r="K60" s="2">
-        <v>46326.147916666669</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L60" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C61" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="D61" t="s">
+        <v>156</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>158</v>
-      </c>
       <c r="F61" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46325.878472222219</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="C62" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F62" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.625</v>
       </c>
       <c r="K62" s="2">
-        <v>46326.098611111112</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B63" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="C63" t="s">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="D63" t="s">
-        <v>87</v>
+        <v>158</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F63" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.333333333336</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K63" s="2">
-        <v>46325.833333333336</v>
+        <v>46328.125</v>
       </c>
       <c r="L63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="C64" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>120</v>
-      </c>
-      <c r="E64" s="1">
-        <v>26172</v>
+        <v>160</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="F64" t="s">
-        <v>93</v>
-      </c>
-      <c r="G64" t="s">
-        <v>94</v>
-      </c>
-      <c r="H64" t="s">
-        <v>94</v>
+        <v>52</v>
       </c>
       <c r="I64" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J64" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K64" s="2">
-        <v>46326.041666666664</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L64" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C65" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="D65" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F65" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J65" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K65" s="2">
-        <v>46329.708333333336</v>
+        <v>46328.125</v>
       </c>
       <c r="L65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>63</v>
+        <v>125</v>
       </c>
       <c r="D66" t="s">
+        <v>160</v>
+      </c>
+      <c r="E66" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E66" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="F66" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J66" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46329.708333333336</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="C67" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" t="s">
+        <v>162</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="F67" t="s">
+        <v>52</v>
+      </c>
+      <c r="G67" t="s">
+        <v>28</v>
+      </c>
+      <c r="I67" t="s">
         <v>48</v>
       </c>
-      <c r="D67" t="s">
-        <v>163</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F67" t="s">
-        <v>51</v>
-      </c>
-      <c r="I67" t="s">
-        <v>19</v>
-      </c>
       <c r="J67" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L67" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="C68" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D68" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F68" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G68" t="s">
+        <v>28</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J68" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K68" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L68" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B69" t="s">
+        <v>43</v>
+      </c>
+      <c r="C69" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" t="s">
+        <v>164</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F69" t="s">
         <v>47</v>
       </c>
-      <c r="C69" t="s">
+      <c r="G69" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" t="s">
         <v>48</v>
       </c>
-      <c r="D69" t="s">
-        <v>163</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="F69" t="s">
-        <v>51</v>
-      </c>
-      <c r="I69" t="s">
-        <v>19</v>
-      </c>
       <c r="J69" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K69" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L69" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C70" t="s">
-        <v>131</v>
+        <v>44</v>
       </c>
       <c r="D70" t="s">
+        <v>164</v>
+      </c>
+      <c r="E70" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="E70" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="F70" t="s">
-        <v>55</v>
+        <v>47</v>
+      </c>
+      <c r="G70" t="s">
+        <v>28</v>
       </c>
       <c r="I70" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J70" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K70" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L70" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C71" t="s">
-        <v>21</v>
+        <v>110</v>
       </c>
       <c r="D71" t="s">
-        <v>167</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F71" t="s">
-        <v>59</v>
-      </c>
-      <c r="G71" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I71" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.25</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K71" s="2">
         <v>46326.75</v>
       </c>
       <c r="L71" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="C72" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F72" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G72" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.25</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46326.75</v>
+        <v>46327.75</v>
       </c>
       <c r="L72" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="C73" t="s">
-        <v>21</v>
+        <v>125</v>
       </c>
       <c r="D73" t="s">
+        <v>167</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="F73" t="s">
         <v>169</v>
       </c>
-      <c r="E73" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="F73" t="s">
-        <v>55</v>
-      </c>
-      <c r="G73" t="s">
-        <v>25</v>
-      </c>
       <c r="I73" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K73" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L73" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B74" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="C74" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D74" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F74" t="s">
-        <v>55</v>
-      </c>
-      <c r="G74" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I74" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J74" s="2">
-        <v>46326.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46326.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L74" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>171</v>
+        <v>172</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F75" t="s">
-        <v>89</v>
+        <v>52</v>
+      </c>
+      <c r="G75" t="s">
+        <v>28</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J75" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.25</v>
       </c>
       <c r="K75" s="2">
-        <v>46326.75</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L75" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>145</v>
-      </c>
-      <c r="C76" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
-        <v>59</v>
-      </c>
-      <c r="G76" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="I76" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J76" s="2">
-        <v>46326.791666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K76" s="2">
-        <v>46327.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L76" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B77" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C77" t="s">
-        <v>131</v>
+        <v>69</v>
       </c>
       <c r="D77" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F77" t="s">
-        <v>174</v>
+        <v>52</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J77" s="2">
-        <v>46326.833333333336</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K77" s="2">
-        <v>46329.583333333336</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C78" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F78" t="s">
-        <v>24</v>
+        <v>64</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J78" s="2">
-        <v>46327.166666666664</v>
+        <v>46329</v>
       </c>
       <c r="K78" s="2">
-        <v>46328.541666666664</v>
+        <v>46330</v>
       </c>
       <c r="L78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>145</v>
+        <v>43</v>
       </c>
       <c r="C79" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F79" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G79" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J79" s="2">
-        <v>46327.25</v>
+        <v>46329.25</v>
       </c>
       <c r="K79" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.75</v>
       </c>
       <c r="L79" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="C80" t="s">
+        <v>24</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>181</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>182</v>
       </c>
       <c r="F80" t="s">
-        <v>62</v>
+        <v>169</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J80" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46328.833333333336</v>
+        <v>46332.625</v>
       </c>
       <c r="L80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="C81" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D81" t="s">
+        <v>179</v>
+      </c>
+      <c r="E81" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="E81" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="F81" t="s">
-        <v>55</v>
+        <v>52</v>
+      </c>
+      <c r="G81" t="s">
+        <v>28</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J81" s="2">
-        <v>46327.904861111114</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K81" s="2">
-        <v>46331.196527777778</v>
+        <v>46330.75</v>
       </c>
       <c r="L81" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="C82" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="D82" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F82" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" s="2">
-        <v>46329</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K82" s="2">
-        <v>46330</v>
+        <v>46334</v>
       </c>
       <c r="L82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B83" t="s">
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>53</v>
+      </c>
+      <c r="D83" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F83" t="s">
         <v>52</v>
       </c>
-      <c r="C83" t="s">
-        <v>21</v>
-      </c>
-      <c r="D83" t="s">
-        <v>184</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="F83" t="s">
-        <v>55</v>
-      </c>
-      <c r="G83" t="s">
-        <v>25</v>
-      </c>
       <c r="I83" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J83" s="2">
-        <v>46329.25</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K83" s="2">
-        <v>46329.75</v>
+        <v>46334</v>
       </c>
       <c r="L83" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>86</v>
       </c>
       <c r="C84" t="s">
-        <v>35</v>
+        <v>87</v>
       </c>
       <c r="D84" t="s">
-        <v>186</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>187</v>
+        <v>88</v>
       </c>
       <c r="F84" t="s">
-        <v>174</v>
+        <v>89</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J84" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.625</v>
       </c>
       <c r="K84" s="2">
-        <v>46332.625</v>
+        <v>46331.125</v>
       </c>
       <c r="L84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>145</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D85" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F85" t="s">
-        <v>55</v>
-      </c>
-      <c r="G85" t="s">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="I85" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J85" s="2">
-        <v>46329.791666666664</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K85" s="2">
-        <v>46330.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L85" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B86" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C86" t="s">
-        <v>63</v>
+        <v>24</v>
       </c>
       <c r="D86" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F86" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K86" s="2">
-        <v>46334</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>34</v>
+        <v>78</v>
       </c>
       <c r="C87" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D87" t="s">
-        <v>188</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>189</v>
+        <v>116</v>
       </c>
       <c r="F87" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="I87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K87" s="2">
-        <v>46334</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="C88" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
+        <v>187</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F88" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="I88" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.625</v>
+        <v>46330.75</v>
       </c>
       <c r="K88" s="2">
-        <v>46331.125</v>
+        <v>46332.75</v>
       </c>
       <c r="L88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C89" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D89" t="s">
-        <v>190</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
+      </c>
+      <c r="E89" s="1">
+        <v>1</v>
       </c>
       <c r="F89" t="s">
-        <v>174</v>
+        <v>59</v>
+      </c>
+      <c r="G89" t="s">
+        <v>28</v>
       </c>
       <c r="I89" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J89" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L89" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C90" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="D90" t="s">
         <v>190</v>
       </c>
-      <c r="E90" s="1" t="s">
-        <v>191</v>
+      <c r="E90" s="1">
+        <v>10</v>
       </c>
       <c r="F90" t="s">
-        <v>174</v>
+        <v>59</v>
+      </c>
+      <c r="G90" t="s">
+        <v>28</v>
       </c>
       <c r="I90" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J90" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K90" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L90" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B91" t="s">
-        <v>85</v>
+        <v>43</v>
       </c>
       <c r="C91" t="s">
-        <v>86</v>
+        <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>122</v>
+        <v>191</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F91" t="s">
-        <v>89</v>
+        <v>47</v>
+      </c>
+      <c r="G91" t="s">
+        <v>28</v>
+      </c>
+      <c r="H91" t="s">
+        <v>193</v>
       </c>
       <c r="I91" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J91" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.25</v>
       </c>
       <c r="K91" s="2">
-        <v>46331.204861111109</v>
+        <v>46331.75</v>
       </c>
       <c r="L91" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4282,404 +4267,377 @@
         <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C92" t="s">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="D92" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F92" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J92" s="2">
-        <v>46330.75</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K92" s="2">
-        <v>46332.75</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B93" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="C93" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
       <c r="F93" t="s">
-        <v>59</v>
-      </c>
-      <c r="G93" t="s">
-        <v>25</v>
-      </c>
-      <c r="H93" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="I93" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K93" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B94" t="s">
-        <v>145</v>
+        <v>68</v>
       </c>
       <c r="C94" t="s">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="D94" t="s">
-        <v>197</v>
-      </c>
-      <c r="E94" s="1">
-        <v>1</v>
+        <v>196</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="F94" t="s">
-        <v>66</v>
-      </c>
-      <c r="G94" t="s">
-        <v>25</v>
+        <v>169</v>
       </c>
       <c r="I94" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K94" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B95" t="s">
-        <v>52</v>
+        <v>139</v>
       </c>
       <c r="C95" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D95" t="s">
-        <v>198</v>
-      </c>
-      <c r="E95" s="1">
-        <v>10</v>
+        <v>191</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F95" t="s">
-        <v>66</v>
+        <v>47</v>
       </c>
       <c r="G95" t="s">
-        <v>25</v>
+        <v>28</v>
+      </c>
+      <c r="H95" t="s">
+        <v>193</v>
       </c>
       <c r="I95" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.25</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L95" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
+        <v>139</v>
       </c>
       <c r="C96" t="s">
-        <v>103</v>
+        <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>199</v>
-      </c>
-      <c r="E96" s="1" t="s">
-        <v>200</v>
+        <v>190</v>
+      </c>
+      <c r="E96" s="1">
+        <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>51</v>
+        <v>59</v>
+      </c>
+      <c r="G96" t="s">
+        <v>28</v>
       </c>
       <c r="I96" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J96" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K96" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L96" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C97" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>201</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>160</v>
+        <v>189</v>
+      </c>
+      <c r="E97" s="1">
+        <v>1</v>
       </c>
       <c r="F97" t="s">
-        <v>174</v>
+        <v>59</v>
+      </c>
+      <c r="G97" t="s">
+        <v>28</v>
       </c>
       <c r="I97" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J97" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.75</v>
       </c>
       <c r="L97" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B98" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="C98" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
       <c r="D98" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="F98" t="s">
-        <v>174</v>
+        <v>104</v>
       </c>
       <c r="I98" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J98" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K98" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B99" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C99" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D99" t="s">
-        <v>197</v>
-      </c>
-      <c r="E99" s="1">
-        <v>1</v>
+        <v>145</v>
       </c>
       <c r="F99" t="s">
-        <v>66</v>
-      </c>
-      <c r="G99" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I99" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J99" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.75</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L99" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B100" t="s">
-        <v>145</v>
-      </c>
-      <c r="C100" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D100" t="s">
-        <v>198</v>
-      </c>
-      <c r="E100" s="1">
-        <v>10</v>
+        <v>199</v>
       </c>
       <c r="F100" t="s">
-        <v>66</v>
-      </c>
-      <c r="G100" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="I100" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J100" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L100" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B101" t="s">
-        <v>145</v>
-      </c>
-      <c r="C101" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D101" t="s">
-        <v>194</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F101" t="s">
-        <v>59</v>
-      </c>
-      <c r="G101" t="s">
-        <v>25</v>
-      </c>
-      <c r="H101" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="I101" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J101" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K101" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L101" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C102" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D102" t="s">
-        <v>202</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F102" t="s">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="I102" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J102" s="2">
-        <v>46332.056250000001</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K102" s="2">
-        <v>46332.597916666666</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
     </row>
     <row r="103" spans="1:12">
       <c r="A103" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>85</v>
+        <v>13</v>
       </c>
       <c r="C103" t="s">
-        <v>86</v>
+        <v>14</v>
       </c>
       <c r="D103" t="s">
-        <v>151</v>
+        <v>200</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="F103" t="s">
-        <v>89</v>
+        <v>17</v>
       </c>
       <c r="I103" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J103" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K103" s="2">
-        <v>46332.791666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="L103" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="104" spans="1:12">
@@ -4689,23 +4647,29 @@
       <c r="B104" t="s">
         <v>13</v>
       </c>
+      <c r="C104" t="s">
+        <v>33</v>
+      </c>
       <c r="D104" t="s">
-        <v>204</v>
+        <v>202</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="I104" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J104" s="2">
-        <v>46332.375</v>
+        <v>46333</v>
       </c>
       <c r="K104" s="2">
-        <v>46333.5</v>
+        <v>46334</v>
       </c>
       <c r="L104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4715,116 +4679,116 @@
       <c r="B105" t="s">
         <v>13</v>
       </c>
+      <c r="C105" t="s">
+        <v>33</v>
+      </c>
       <c r="D105" t="s">
-        <v>204</v>
+        <v>202</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F105" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="I105" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J105" s="2">
-        <v>46332.375</v>
+        <v>46333</v>
       </c>
       <c r="K105" s="2">
-        <v>46333.5</v>
+        <v>46334</v>
       </c>
       <c r="L105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B106" t="s">
-        <v>90</v>
-      </c>
-      <c r="C106" t="s">
-        <v>119</v>
+        <v>60</v>
       </c>
       <c r="D106" t="s">
-        <v>120</v>
+        <v>204</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F106" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="I106" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J106" s="2">
-        <v>46332.541666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K106" s="2">
-        <v>46333.041666666664</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L106" t="s">
-        <v>121</v>
+        <v>21</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
-      </c>
-      <c r="C107" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="D107" t="s">
+        <v>204</v>
+      </c>
+      <c r="E107" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="E107" s="1" t="s">
-        <v>206</v>
-      </c>
       <c r="F107" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="I107" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J107" s="2">
-        <v>46332.875</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K107" s="2">
-        <v>46334.25</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C108" t="s">
-        <v>42</v>
+        <v>110</v>
       </c>
       <c r="D108" t="s">
-        <v>207</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>208</v>
+        <v>111</v>
       </c>
       <c r="F108" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="I108" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J108" s="2">
-        <v>46333</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K108" s="2">
-        <v>46334</v>
+        <v>46333.75</v>
       </c>
       <c r="L108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:12">
@@ -4835,65 +4799,74 @@
         <v>13</v>
       </c>
       <c r="C109" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="D109" t="s">
+        <v>206</v>
+      </c>
+      <c r="E109" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="E109" s="1" t="s">
-        <v>208</v>
-      </c>
       <c r="F109" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="I109" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J109" s="2">
-        <v>46333</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K109" s="2">
-        <v>46334</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>67</v>
+        <v>43</v>
+      </c>
+      <c r="C110" t="s">
+        <v>44</v>
       </c>
       <c r="D110" t="s">
-        <v>209</v>
-      </c>
-      <c r="E110" s="1" t="s">
-        <v>210</v>
+        <v>208</v>
+      </c>
+      <c r="E110" s="1">
+        <v>11</v>
       </c>
       <c r="F110" t="s">
-        <v>71</v>
+        <v>59</v>
+      </c>
+      <c r="G110" t="s">
+        <v>28</v>
       </c>
       <c r="I110" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J110" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K110" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L110" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B111" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="C111" t="s">
+        <v>125</v>
       </c>
       <c r="D111" t="s">
         <v>209</v>
@@ -4902,59 +4875,65 @@
         <v>210</v>
       </c>
       <c r="F111" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="I111" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J111" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K111" s="2">
-        <v>46335.041666666664</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B112" t="s">
-        <v>85</v>
+        <v>139</v>
       </c>
       <c r="C112" t="s">
-        <v>116</v>
+        <v>44</v>
       </c>
       <c r="D112" t="s">
-        <v>117</v>
+        <v>211</v>
+      </c>
+      <c r="E112" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="F112" t="s">
-        <v>89</v>
+        <v>52</v>
+      </c>
+      <c r="G112" t="s">
+        <v>28</v>
       </c>
       <c r="I112" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J112" s="2">
-        <v>46333.416666666664</v>
+        <v>46335.25</v>
       </c>
       <c r="K112" s="2">
-        <v>46333.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L112" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C113" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D113" t="s">
         <v>211</v>
@@ -4963,374 +4942,368 @@
         <v>212</v>
       </c>
       <c r="F113" t="s">
-        <v>24</v>
+        <v>52</v>
+      </c>
+      <c r="G113" t="s">
+        <v>28</v>
       </c>
       <c r="I113" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="J113" s="2">
-        <v>46333.666666666664</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K113" s="2">
-        <v>46335.041666666664</v>
+        <v>46336.75</v>
       </c>
       <c r="L113" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C114" t="s">
-        <v>21</v>
+        <v>61</v>
       </c>
       <c r="D114" t="s">
         <v>213</v>
       </c>
-      <c r="E114" s="1">
-        <v>11</v>
+      <c r="E114" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="F114" t="s">
-        <v>66</v>
-      </c>
-      <c r="G114" t="s">
-        <v>25</v>
+        <v>64</v>
       </c>
       <c r="I114" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J114" s="2">
-        <v>46334.25</v>
+        <v>46337</v>
       </c>
       <c r="K114" s="2">
-        <v>46334.75</v>
+        <v>46339</v>
       </c>
       <c r="L114" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C115" t="s">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="D115" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F115" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I115" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J115" s="2">
-        <v>46334.958333333336</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K115" s="2">
-        <v>46337.708333333336</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L115" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C116" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="D116" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="F116" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G116" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I116" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J116" s="2">
-        <v>46335.25</v>
+        <v>46337.25</v>
       </c>
       <c r="K116" s="2">
-        <v>46335.75</v>
+        <v>46337.75</v>
       </c>
       <c r="L116" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C117" t="s">
-        <v>21</v>
+        <v>79</v>
       </c>
       <c r="D117" t="s">
-        <v>216</v>
-      </c>
-      <c r="E117" s="1" t="s">
-        <v>217</v>
+        <v>80</v>
       </c>
       <c r="F117" t="s">
-        <v>55</v>
-      </c>
-      <c r="G117" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="I117" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J117" s="2">
-        <v>46335.791666666664</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K117" s="2">
-        <v>46336.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L117" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C118" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="D118" t="s">
-        <v>218</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>219</v>
+        <v>88</v>
       </c>
       <c r="F118" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="I118" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="J118" s="2">
-        <v>46337</v>
+        <v>46337.625</v>
       </c>
       <c r="K118" s="2">
-        <v>46339</v>
+        <v>46338.125</v>
       </c>
       <c r="L118" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B119" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="C119" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="D119" t="s">
+        <v>219</v>
+      </c>
+      <c r="E119" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="E119" s="1" t="s">
-        <v>221</v>
-      </c>
       <c r="F119" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J119" s="2">
-        <v>46337.208333333336</v>
+        <v>46337.75</v>
       </c>
       <c r="K119" s="2">
-        <v>46340.208333333336</v>
+        <v>46339.75</v>
       </c>
       <c r="L119" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B120" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="D120" t="s">
-        <v>222</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F120" t="s">
-        <v>55</v>
-      </c>
-      <c r="G120" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="I120" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="J120" s="2">
-        <v>46337.25</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K120" s="2">
-        <v>46337.75</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L120" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>85</v>
+        <v>38</v>
       </c>
       <c r="C121" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="D121" t="s">
-        <v>87</v>
+        <v>222</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="F121" t="s">
-        <v>89</v>
+        <v>42</v>
       </c>
       <c r="I121" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J121" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K121" s="2">
-        <v>46337.833333333336</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L121" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:12">
       <c r="A122" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="C122" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="D122" t="s">
-        <v>92</v>
+        <v>224</v>
+      </c>
+      <c r="E122" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F122" t="s">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="I122" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
       <c r="J122" s="2">
-        <v>46337.625</v>
+        <v>46338.791666666664</v>
       </c>
       <c r="K122" s="2">
-        <v>46338.125</v>
+        <v>46340.166666666664</v>
       </c>
       <c r="L122" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B123" t="s">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C123" t="s">
-        <v>48</v>
+        <v>69</v>
       </c>
       <c r="D123" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F123" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="I123" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J123" s="2">
-        <v>46337.75</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K123" s="2">
-        <v>46339.75</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L123" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C124" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="D124" t="s">
         <v>226</v>
       </c>
+      <c r="E124" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="F124" t="s">
-        <v>17</v>
+        <v>72</v>
       </c>
       <c r="I124" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J124" s="2">
-        <v>46338.431250000001</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K124" s="2">
-        <v>46339.472916666666</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L124" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5338,217 +5311,118 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>103</v>
+        <v>33</v>
       </c>
       <c r="D125" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F125" t="s">
-        <v>51</v>
+        <v>169</v>
       </c>
       <c r="I125" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J125" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K125" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L125" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B126" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C126" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="D126" t="s">
-        <v>229</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>230</v>
+        <v>114</v>
       </c>
       <c r="F126" t="s">
-        <v>30</v>
+        <v>89</v>
       </c>
       <c r="I126" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J126" s="2">
-        <v>46338.791666666664</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K126" s="2">
-        <v>46340.166666666664</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L126" t="s">
-        <v>20</v>
+        <v>115</v>
       </c>
     </row>
     <row r="127" spans="1:12">
       <c r="A127" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B127" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C127" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D127" t="s">
-        <v>231</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>232</v>
+        <v>116</v>
       </c>
       <c r="F127" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I127" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J127" s="2">
-        <v>46338.958333333336</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K127" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L127" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B128" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C128" t="s">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="D128" t="s">
-        <v>231</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="F128" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I128" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J128" s="2">
-        <v>46338.958333333336</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K128" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.75</v>
       </c>
       <c r="L128" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12">
-      <c r="A129" t="s">
-        <v>12</v>
-      </c>
-      <c r="B129" t="s">
-        <v>13</v>
-      </c>
-      <c r="C129" t="s">
-        <v>42</v>
-      </c>
-      <c r="D129" t="s">
-        <v>233</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="F129" t="s">
-        <v>174</v>
-      </c>
-      <c r="I129" t="s">
-        <v>19</v>
-      </c>
-      <c r="J129" s="2">
-        <v>46339.083333333336</v>
-      </c>
-      <c r="K129" s="2">
-        <v>46340.291666666664</v>
-      </c>
-      <c r="L129" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12">
-      <c r="A130" t="s">
-        <v>33</v>
-      </c>
-      <c r="B130" t="s">
-        <v>90</v>
-      </c>
-      <c r="C130" t="s">
-        <v>119</v>
-      </c>
-      <c r="D130" t="s">
-        <v>120</v>
-      </c>
-      <c r="F130" t="s">
-        <v>93</v>
-      </c>
-      <c r="I130" t="s">
-        <v>19</v>
-      </c>
-      <c r="J130" s="2">
-        <v>46339.541666666664</v>
-      </c>
-      <c r="K130" s="2">
-        <v>46340.041666666664</v>
-      </c>
-      <c r="L130" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12">
-      <c r="A131" t="s">
-        <v>33</v>
-      </c>
-      <c r="B131" t="s">
-        <v>85</v>
-      </c>
-      <c r="C131" t="s">
-        <v>86</v>
-      </c>
-      <c r="D131" t="s">
-        <v>122</v>
-      </c>
-      <c r="F131" t="s">
-        <v>89</v>
-      </c>
-      <c r="I131" t="s">
-        <v>19</v>
-      </c>
-      <c r="J131" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K131" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L131" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -5560,6 +5434,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5567,13 +5450,13 @@
 </scriptIds>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5711,27 +5594,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
--- a/data/vessels/2026-10-17.xlsx
+++ b/data/vessels/2026-10-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433430" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B93023C9-DA8C-4454-B058-94159EBDFDDE}"/>
+  <xr:revisionPtr revIDLastSave="433835" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6594652D-3C64-4336-AE90-20982FA52640}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="230">
   <si>
     <t>Harbor</t>
   </si>
@@ -260,6 +260,12 @@
     <t>Yang Ming</t>
   </si>
   <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
     <t>ARC ENDEAVOR</t>
   </si>
   <si>
@@ -269,12 +275,6 @@
     <t>Ports America Group/Pct</t>
   </si>
   <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -386,7 +386,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.1 days</t>
+    <t>Waiting 3 days</t>
   </si>
   <si>
     <t>RJ PFEIFFER</t>
@@ -395,24 +395,24 @@
     <t>POLARIS MILA</t>
   </si>
   <si>
+    <t>LIBERTY PEACE</t>
+  </si>
+  <si>
+    <t>086S</t>
+  </si>
+  <si>
+    <t>Liberty</t>
+  </si>
+  <si>
+    <t>Pacific Terminals</t>
+  </si>
+  <si>
     <t>ARC HONOR</t>
   </si>
   <si>
     <t>ED616</t>
   </si>
   <si>
-    <t>LIBERTY PEACE</t>
-  </si>
-  <si>
-    <t>086S</t>
-  </si>
-  <si>
-    <t>Liberty</t>
-  </si>
-  <si>
-    <t>Pacific Terminals</t>
-  </si>
-  <si>
     <t>SM PORTLAND</t>
   </si>
   <si>
@@ -515,28 +515,28 @@
     <t>OYNT0002E</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>NBBT0001E</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK643R</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>NBBT0001E</t>
+    <t>MORNING LUCY</t>
+  </si>
+  <si>
+    <t>KW665</t>
   </si>
   <si>
     <t>LAVENDER ACE</t>
   </si>
   <si>
     <t>123A</t>
-  </si>
-  <si>
-    <t>MORNING LUCY</t>
-  </si>
-  <si>
-    <t>KW665</t>
   </si>
   <si>
     <t>MANULANI</t>
@@ -1382,28 +1382,28 @@
         <v>13</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
         <v>20</v>
       </c>
       <c r="J7" s="2">
-        <v>46313.208333333336</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K7" s="2">
-        <v>46314.208333333336</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L7" t="s">
         <v>21</v>
@@ -1414,31 +1414,31 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="I8" t="s">
         <v>20</v>
       </c>
       <c r="J8" s="2">
-        <v>46313.25</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K8" s="2">
-        <v>46314.75</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L8" t="s">
         <v>21</v>
@@ -1446,37 +1446,37 @@
     </row>
     <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G9" t="s">
         <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J9" s="2">
-        <v>46314.25</v>
+        <v>46313.25</v>
       </c>
       <c r="K9" s="2">
         <v>46314.75</v>
       </c>
       <c r="L9" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="10" spans="1:12">
@@ -1490,13 +1490,13 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G10" t="s">
         <v>28</v>
@@ -1519,16 +1519,16 @@
         <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C11" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" s="1">
-        <v>34</v>
+        <v>50</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>51</v>
       </c>
       <c r="F11" t="s">
         <v>52</v>
@@ -1537,40 +1537,40 @@
         <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2">
-        <v>46314.625</v>
+        <v>46314.25</v>
       </c>
       <c r="K11" s="2">
-        <v>46318.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L11" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>13</v>
+        <v>23</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
+      </c>
+      <c r="E12" s="1">
+        <v>34</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>
       </c>
-      <c r="H12" t="s">
-        <v>19</v>
-      </c>
       <c r="I12" t="s">
         <v>20</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>46314.625</v>
       </c>
       <c r="K12" s="2">
-        <v>46315.166666666664</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L12" t="s">
         <v>21</v>
@@ -1586,37 +1586,37 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13" s="1">
-        <v>2</v>
+        <v>55</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="F13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
         <v>28</v>
       </c>
+      <c r="H13" t="s">
+        <v>19</v>
+      </c>
       <c r="I13" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J13" s="2">
-        <v>46315.208333333336</v>
+        <v>46314.625</v>
       </c>
       <c r="K13" s="2">
-        <v>46315.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:12">
@@ -1624,66 +1624,66 @@
         <v>22</v>
       </c>
       <c r="B14" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="E14" s="1">
+        <v>2</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G14" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J14" s="2">
         <v>46315.208333333336</v>
       </c>
       <c r="K14" s="2">
-        <v>46317.166666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L14" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>28</v>
+        <v>65</v>
       </c>
       <c r="I15" t="s">
         <v>20</v>
       </c>
       <c r="J15" s="2">
-        <v>46315.666666666664</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K15" s="2">
-        <v>46317.75</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L15" t="s">
         <v>21</v>
@@ -1691,25 +1691,25 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F16" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G16" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -1729,37 +1729,34 @@
         <v>22</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="C17" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="G17" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="I17" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J17" s="2">
-        <v>46316.25</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K17" s="2">
-        <v>46316.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:12">
@@ -1767,13 +1764,13 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C18" t="s">
         <v>44</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E18" s="1">
         <v>63</v>
@@ -1802,37 +1799,37 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="G19" t="s">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="H19" t="s">
-        <v>19</v>
+        <v>77</v>
       </c>
       <c r="I19" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J19" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K19" s="2">
-        <v>46316.916666666664</v>
+        <v>46316.75</v>
       </c>
       <c r="L19" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20" spans="1:12">
@@ -1840,31 +1837,34 @@
         <v>22</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F20" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G20" t="s">
-        <v>28</v>
+        <v>82</v>
+      </c>
+      <c r="H20" t="s">
+        <v>19</v>
       </c>
       <c r="I20" t="s">
         <v>20</v>
       </c>
       <c r="J20" s="2">
-        <v>46316.625</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K20" s="2">
-        <v>46319.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L20" t="s">
         <v>21</v>
@@ -1910,34 +1910,31 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1">
-        <v>26169</v>
+        <v>83</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J22" s="2">
         <v>46316.625</v>
       </c>
       <c r="K22" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
@@ -1948,37 +1945,37 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D23" t="s">
-        <v>73</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>92</v>
+        <v>88</v>
+      </c>
+      <c r="E23" s="1">
+        <v>26169</v>
       </c>
       <c r="F23" t="s">
-        <v>47</v>
+        <v>89</v>
       </c>
       <c r="G23" t="s">
-        <v>28</v>
+        <v>90</v>
       </c>
       <c r="H23" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="J23" s="2">
-        <v>46317.208333333336</v>
+        <v>46316.625</v>
       </c>
       <c r="K23" s="2">
-        <v>46317.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:12">
@@ -1986,60 +1983,66 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>73</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s">
-        <v>95</v>
+        <v>28</v>
+      </c>
+      <c r="H24" t="s">
+        <v>77</v>
       </c>
       <c r="I24" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J24" s="2">
         <v>46317.208333333336</v>
       </c>
       <c r="K24" s="2">
-        <v>46318.708333333336</v>
+        <v>46317.75</v>
       </c>
       <c r="L24" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D25" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F25" t="s">
-        <v>42</v>
+        <v>64</v>
+      </c>
+      <c r="G25" t="s">
+        <v>95</v>
       </c>
       <c r="I25" t="s">
         <v>20</v>
       </c>
       <c r="J25" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K25" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L25" t="s">
         <v>21</v>
@@ -2047,37 +2050,34 @@
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>38</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="D26" t="s">
-        <v>99</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
+        <v>97</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="F26" t="s">
-        <v>100</v>
-      </c>
-      <c r="G26" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I26" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J26" s="2">
-        <v>46317.541666666664</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K26" s="2">
-        <v>46320.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L26" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:12">
@@ -2085,7 +2085,7 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C27" t="s">
         <v>44</v>
@@ -2117,69 +2117,69 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>13</v>
+        <v>73</v>
       </c>
       <c r="C28" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>103</v>
+        <v>99</v>
+      </c>
+      <c r="E28" s="1">
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>104</v>
+        <v>100</v>
+      </c>
+      <c r="G28" t="s">
+        <v>28</v>
       </c>
       <c r="I28" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J28" s="2">
-        <v>46317.927777777775</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K28" s="2">
-        <v>46318.969444444447</v>
+        <v>46320.75</v>
       </c>
       <c r="L28" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C29" t="s">
-        <v>44</v>
+        <v>101</v>
       </c>
       <c r="D29" t="s">
-        <v>105</v>
+        <v>102</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" t="s">
-        <v>82</v>
-      </c>
-      <c r="H29" t="s">
-        <v>19</v>
+        <v>104</v>
       </c>
       <c r="I29" t="s">
         <v>20</v>
       </c>
       <c r="J29" s="2">
-        <v>46318.104166666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K29" s="2">
-        <v>46318.916666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L29" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="30" spans="1:12">
@@ -2187,31 +2187,31 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C30" t="s">
         <v>44</v>
       </c>
       <c r="D30" t="s">
-        <v>106</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F30" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G30" t="s">
-        <v>28</v>
+        <v>82</v>
+      </c>
+      <c r="H30" t="s">
+        <v>19</v>
       </c>
       <c r="I30" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J30" s="2">
-        <v>46318.25</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46318.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L30" t="s">
         <v>49</v>
@@ -2219,63 +2219,60 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B31" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C31" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D31" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F31" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G31" t="s">
-        <v>18</v>
-      </c>
-      <c r="H31" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="I31" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J31" s="2">
         <v>46318.25</v>
       </c>
       <c r="K31" s="2">
-        <v>46319.166666666664</v>
+        <v>46318.75</v>
       </c>
       <c r="L31" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C32" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F32" t="s">
-        <v>82</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s">
-        <v>82</v>
+        <v>18</v>
       </c>
       <c r="H32" t="s">
         <v>19</v>
@@ -2284,10 +2281,10 @@
         <v>20</v>
       </c>
       <c r="J32" s="2">
-        <v>46318.291666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K32" s="2">
-        <v>46319.125</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L32" t="s">
         <v>21</v>
@@ -2298,37 +2295,37 @@
         <v>22</v>
       </c>
       <c r="B33" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D33" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" s="1">
-        <v>26168</v>
+        <v>111</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="F33" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G33" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="H33" t="s">
-        <v>90</v>
+        <v>19</v>
       </c>
       <c r="I33" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J33" s="2">
-        <v>46318.625</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K33" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L33" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:12">
@@ -2336,31 +2333,37 @@
         <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
+      </c>
+      <c r="E34" s="1">
+        <v>26168</v>
       </c>
       <c r="F34" t="s">
-        <v>82</v>
+        <v>89</v>
+      </c>
+      <c r="G34" t="s">
+        <v>90</v>
+      </c>
+      <c r="H34" t="s">
+        <v>90</v>
       </c>
       <c r="I34" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.704861111109</v>
+        <v>46318.625</v>
       </c>
       <c r="K34" s="2">
-        <v>46319.204861111109</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L34" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
     </row>
     <row r="35" spans="1:12">
@@ -2368,34 +2371,31 @@
         <v>22</v>
       </c>
       <c r="B35" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E35" s="1">
-        <v>4</v>
+        <v>116</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="F35" t="s">
-        <v>59</v>
-      </c>
-      <c r="G35" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J35" s="2">
-        <v>46319.208333333336</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K35" s="2">
-        <v>46319.75</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L35" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="36" spans="1:12">
@@ -2444,13 +2444,13 @@
         <v>44</v>
       </c>
       <c r="D37" t="s">
-        <v>118</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
+      </c>
+      <c r="E37" s="1">
+        <v>4</v>
       </c>
       <c r="F37" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2459,7 +2459,7 @@
         <v>48</v>
       </c>
       <c r="J37" s="2">
-        <v>46319.25</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K37" s="2">
         <v>46319.75</v>
@@ -2473,25 +2473,25 @@
         <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
       </c>
       <c r="D38" t="s">
+        <v>118</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F38" t="s">
         <v>120</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="F38" t="s">
-        <v>122</v>
       </c>
       <c r="G38" t="s">
         <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="I38" t="s">
         <v>48</v>
@@ -2511,25 +2511,22 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>43</v>
       </c>
       <c r="C39" t="s">
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F39" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="I39" t="s">
         <v>48</v>
@@ -2538,7 +2535,7 @@
         <v>46319.25</v>
       </c>
       <c r="K39" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L39" t="s">
         <v>49</v>
@@ -2555,10 +2552,10 @@
         <v>44</v>
       </c>
       <c r="D40" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F40" t="s">
         <v>47</v>
@@ -2581,69 +2578,72 @@
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>13</v>
+        <v>73</v>
+      </c>
+      <c r="C41" t="s">
+        <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>56</v>
+        <v>119</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>120</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="H41" t="s">
-        <v>19</v>
+        <v>121</v>
       </c>
       <c r="I41" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J41" s="2">
-        <v>46319.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K41" s="2">
         <v>46320.166666666664</v>
       </c>
       <c r="L41" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B42" t="s">
-        <v>68</v>
-      </c>
-      <c r="C42" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D42" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F42" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G42" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="H42" t="s">
+        <v>19</v>
       </c>
       <c r="I42" t="s">
         <v>20</v>
       </c>
       <c r="J42" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.625</v>
       </c>
       <c r="K42" s="2">
-        <v>46321.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L42" t="s">
         <v>21</v>
@@ -2654,28 +2654,31 @@
         <v>22</v>
       </c>
       <c r="B43" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C43" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="D43" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F43" t="s">
-        <v>64</v>
+        <v>72</v>
+      </c>
+      <c r="G43" t="s">
+        <v>18</v>
       </c>
       <c r="I43" t="s">
         <v>20</v>
       </c>
       <c r="J43" s="2">
-        <v>46320</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K43" s="2">
-        <v>46322</v>
+        <v>46321.75</v>
       </c>
       <c r="L43" t="s">
         <v>21</v>
@@ -2683,31 +2686,31 @@
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F44" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I44" t="s">
         <v>20</v>
       </c>
       <c r="J44" s="2">
-        <v>46320.21875</v>
+        <v>46320</v>
       </c>
       <c r="K44" s="2">
-        <v>46324.59375</v>
+        <v>46322</v>
       </c>
       <c r="L44" t="s">
         <v>21</v>
@@ -2721,28 +2724,25 @@
         <v>13</v>
       </c>
       <c r="C45" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
-      </c>
-      <c r="G45" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="I45" t="s">
         <v>20</v>
       </c>
       <c r="J45" s="2">
-        <v>46321.208333333336</v>
+        <v>46320.21875</v>
       </c>
       <c r="K45" s="2">
-        <v>46322.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L45" t="s">
         <v>21</v>
@@ -2753,28 +2753,31 @@
         <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D46" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="F46" t="s">
-        <v>42</v>
+        <v>36</v>
+      </c>
+      <c r="G46" t="s">
+        <v>37</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
       </c>
       <c r="J46" s="2">
-        <v>46321.21875</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K46" s="2">
-        <v>46323.21875</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L46" t="s">
         <v>21</v>
@@ -2782,34 +2785,31 @@
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C47" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D47" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F47" t="s">
-        <v>72</v>
-      </c>
-      <c r="G47" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
       </c>
       <c r="J47" s="2">
-        <v>46321.25</v>
+        <v>46321.21875</v>
       </c>
       <c r="K47" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.21875</v>
       </c>
       <c r="L47" t="s">
         <v>21</v>
@@ -2820,31 +2820,31 @@
         <v>22</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C48" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
-      </c>
-      <c r="E48" s="1">
-        <v>21</v>
+        <v>136</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="F48" t="s">
         <v>72</v>
       </c>
       <c r="G48" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.625</v>
+        <v>46321.25</v>
       </c>
       <c r="K48" s="2">
-        <v>46325.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L48" t="s">
         <v>21</v>
@@ -2855,34 +2855,34 @@
         <v>22</v>
       </c>
       <c r="B49" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="C49" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D49" t="s">
-        <v>140</v>
+        <v>138</v>
+      </c>
+      <c r="E49" s="1">
+        <v>21</v>
       </c>
       <c r="F49" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="G49" t="s">
-        <v>18</v>
-      </c>
-      <c r="H49" t="s">
-        <v>123</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J49" s="2">
-        <v>46322.25</v>
+        <v>46321.625</v>
       </c>
       <c r="K49" s="2">
-        <v>46322.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L49" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="50" spans="1:12">
@@ -2890,34 +2890,34 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="C50" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>141</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="F50" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="G50" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="H50" t="s">
+        <v>121</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J50" s="2">
-        <v>46322.625</v>
+        <v>46322.25</v>
       </c>
       <c r="K50" s="2">
-        <v>46325.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L50" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2925,34 +2925,34 @@
         <v>22</v>
       </c>
       <c r="B51" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F51" t="s">
-        <v>52</v>
+        <v>85</v>
       </c>
       <c r="G51" t="s">
         <v>28</v>
       </c>
       <c r="I51" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J51" s="2">
-        <v>46323.25</v>
+        <v>46322.625</v>
       </c>
       <c r="K51" s="2">
-        <v>46323.75</v>
+        <v>46325.75</v>
       </c>
       <c r="L51" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="52" spans="1:12">
@@ -2960,25 +2960,31 @@
         <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C52" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="F52" t="s">
-        <v>82</v>
+        <v>52</v>
+      </c>
+      <c r="G52" t="s">
+        <v>28</v>
       </c>
       <c r="I52" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J52" s="2">
-        <v>46323.291666666664</v>
+        <v>46323.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L52" t="s">
         <v>49</v>
@@ -2989,37 +2995,28 @@
         <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C53" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="D53" t="s">
-        <v>88</v>
-      </c>
-      <c r="E53" s="1">
-        <v>26173</v>
+        <v>145</v>
       </c>
       <c r="F53" t="s">
-        <v>89</v>
-      </c>
-      <c r="G53" t="s">
-        <v>90</v>
-      </c>
-      <c r="H53" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J53" s="2">
-        <v>46323.625</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K53" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3027,34 +3024,37 @@
         <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>139</v>
+        <v>86</v>
       </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="D54" t="s">
-        <v>143</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>144</v>
+        <v>88</v>
+      </c>
+      <c r="E54" s="1">
+        <v>26173</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
+        <v>89</v>
       </c>
       <c r="G54" t="s">
-        <v>28</v>
+        <v>90</v>
+      </c>
+      <c r="H54" t="s">
+        <v>90</v>
       </c>
       <c r="I54" t="s">
-        <v>48</v>
+        <v>91</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.791666666664</v>
+        <v>46323.625</v>
       </c>
       <c r="K54" s="2">
-        <v>46324.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L54" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3062,57 +3062,60 @@
         <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>139</v>
+      </c>
+      <c r="C55" t="s">
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F55" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="G55" t="s">
+        <v>28</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J55" s="2">
-        <v>46324</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K55" s="2">
-        <v>46326</v>
+        <v>46324.75</v>
       </c>
       <c r="L55" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>13</v>
-      </c>
-      <c r="C56" t="s">
-        <v>148</v>
+        <v>60</v>
       </c>
       <c r="D56" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F56" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I56" t="s">
         <v>20</v>
       </c>
       <c r="J56" s="2">
-        <v>46324.647916666669</v>
+        <v>46324</v>
       </c>
       <c r="K56" s="2">
-        <v>46326.147916666669</v>
+        <v>46326</v>
       </c>
       <c r="L56" t="s">
         <v>21</v>
@@ -3123,28 +3126,28 @@
         <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C57" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
       <c r="D57" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F57" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
       </c>
       <c r="J57" s="2">
-        <v>46325.003472222219</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K57" s="2">
-        <v>46325.878472222219</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L57" t="s">
         <v>21</v>
@@ -3155,28 +3158,28 @@
         <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C58" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F58" t="s">
-        <v>104</v>
+        <v>42</v>
       </c>
       <c r="I58" t="s">
         <v>20</v>
       </c>
       <c r="J58" s="2">
-        <v>46325.056944444441</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K58" s="2">
-        <v>46326.098611111112</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L58" t="s">
         <v>21</v>
@@ -3184,28 +3187,31 @@
     </row>
     <row r="59" spans="1:12">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B59" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>79</v>
+        <v>153</v>
       </c>
       <c r="D59" t="s">
-        <v>80</v>
+        <v>154</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="F59" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
       </c>
       <c r="J59" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K59" s="2">
-        <v>46325.833333333336</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L59" t="s">
         <v>21</v>
@@ -3216,37 +3222,28 @@
         <v>22</v>
       </c>
       <c r="B60" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="D60" t="s">
-        <v>114</v>
-      </c>
-      <c r="E60" s="1">
-        <v>26172</v>
+        <v>80</v>
       </c>
       <c r="F60" t="s">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s">
-        <v>90</v>
-      </c>
-      <c r="H60" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K60" s="2">
-        <v>46326.041666666664</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L60" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3254,31 +3251,37 @@
         <v>22</v>
       </c>
       <c r="B61" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C61" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D61" t="s">
-        <v>156</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>157</v>
+        <v>114</v>
+      </c>
+      <c r="E61" s="1">
+        <v>26172</v>
       </c>
       <c r="F61" t="s">
-        <v>52</v>
+        <v>89</v>
+      </c>
+      <c r="G61" t="s">
+        <v>90</v>
+      </c>
+      <c r="H61" t="s">
+        <v>90</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J61" s="2">
         <v>46325.625</v>
       </c>
       <c r="K61" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L61" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3315,31 +3318,31 @@
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C63" t="s">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="D63" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F63" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I63" t="s">
         <v>20</v>
       </c>
       <c r="J63" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46328.125</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L63" t="s">
         <v>21</v>
@@ -3356,10 +3359,10 @@
         <v>125</v>
       </c>
       <c r="D64" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F64" t="s">
         <v>52</v>
@@ -3379,13 +3382,13 @@
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="D65" t="s">
         <v>158</v>
@@ -3394,7 +3397,7 @@
         <v>159</v>
       </c>
       <c r="F65" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I65" t="s">
         <v>20</v>
@@ -3403,7 +3406,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K65" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L65" t="s">
         <v>21</v>
@@ -3411,13 +3414,13 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B66" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>39</v>
       </c>
       <c r="D66" t="s">
         <v>160</v>
@@ -3426,7 +3429,7 @@
         <v>161</v>
       </c>
       <c r="F66" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="I66" t="s">
         <v>20</v>
@@ -3435,7 +3438,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K66" s="2">
-        <v>46328.916666666664</v>
+        <v>46328.125</v>
       </c>
       <c r="L66" t="s">
         <v>21</v>
@@ -3443,37 +3446,34 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="C67" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D67" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>52</v>
-      </c>
-      <c r="G67" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I67" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J67" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L67" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3481,7 +3481,7 @@
         <v>22</v>
       </c>
       <c r="B68" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C68" t="s">
         <v>44</v>
@@ -3493,7 +3493,7 @@
         <v>163</v>
       </c>
       <c r="F68" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G68" t="s">
         <v>28</v>
@@ -3516,7 +3516,7 @@
         <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C69" t="s">
         <v>44</v>
@@ -3528,7 +3528,7 @@
         <v>165</v>
       </c>
       <c r="F69" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G69" t="s">
         <v>28</v>
@@ -3551,7 +3551,7 @@
         <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C70" t="s">
         <v>44</v>
@@ -3563,7 +3563,7 @@
         <v>165</v>
       </c>
       <c r="F70" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G70" t="s">
         <v>28</v>
@@ -3586,22 +3586,28 @@
         <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="C71" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>166</v>
+        <v>162</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>163</v>
       </c>
       <c r="F71" t="s">
-        <v>82</v>
+        <v>47</v>
+      </c>
+      <c r="G71" t="s">
+        <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K71" s="2">
         <v>46326.75</v>
@@ -3615,31 +3621,25 @@
         <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="D72" t="s">
-        <v>164</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F72" t="s">
-        <v>47</v>
-      </c>
-      <c r="G72" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I72" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46327.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L72" t="s">
         <v>49</v>
@@ -3650,60 +3650,63 @@
         <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="C73" t="s">
-        <v>125</v>
+        <v>44</v>
       </c>
       <c r="D73" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="F73" t="s">
-        <v>169</v>
+        <v>47</v>
+      </c>
+      <c r="G73" t="s">
+        <v>28</v>
       </c>
       <c r="I73" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K73" s="2">
-        <v>46329.583333333336</v>
+        <v>46327.75</v>
       </c>
       <c r="L73" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="D74" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F74" t="s">
-        <v>32</v>
+        <v>169</v>
       </c>
       <c r="I74" t="s">
         <v>20</v>
       </c>
       <c r="J74" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K74" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L74" t="s">
         <v>21</v>
@@ -3711,92 +3714,92 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D75" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F75" t="s">
-        <v>52</v>
-      </c>
-      <c r="G75" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I75" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46327.708333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>13</v>
+        <v>139</v>
+      </c>
+      <c r="C76" t="s">
+        <v>44</v>
       </c>
       <c r="D76" t="s">
-        <v>174</v>
+        <v>172</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="F76" t="s">
-        <v>57</v>
+        <v>52</v>
+      </c>
+      <c r="G76" t="s">
+        <v>28</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J76" s="2">
+        <v>46327.25</v>
+      </c>
+      <c r="K76" s="2">
         <v>46327.708333333336</v>
       </c>
-      <c r="K76" s="2">
-        <v>46328.833333333336</v>
-      </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="77" spans="1:12">
       <c r="A77" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>68</v>
-      </c>
-      <c r="C77" t="s">
-        <v>69</v>
+        <v>13</v>
       </c>
       <c r="D77" t="s">
-        <v>175</v>
-      </c>
-      <c r="E77" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F77" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="I77" t="s">
         <v>20</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K77" s="2">
-        <v>46331.196527777778</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L77" t="s">
         <v>21</v>
@@ -3807,28 +3810,28 @@
         <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C78" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D78" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F78" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I78" t="s">
         <v>20</v>
       </c>
       <c r="J78" s="2">
-        <v>46329</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K78" s="2">
-        <v>46330</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L78" t="s">
         <v>21</v>
@@ -3839,34 +3842,31 @@
         <v>22</v>
       </c>
       <c r="B79" t="s">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C79" t="s">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="D79" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>52</v>
-      </c>
-      <c r="G79" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="I79" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J79" s="2">
-        <v>46329.25</v>
+        <v>46329</v>
       </c>
       <c r="K79" s="2">
-        <v>46329.75</v>
+        <v>46330</v>
       </c>
       <c r="L79" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="80" spans="1:12">
@@ -3874,31 +3874,34 @@
         <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C80" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D80" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F80" t="s">
-        <v>169</v>
+        <v>52</v>
+      </c>
+      <c r="G80" t="s">
+        <v>28</v>
       </c>
       <c r="I80" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.333333333336</v>
+        <v>46329.25</v>
       </c>
       <c r="K80" s="2">
-        <v>46332.625</v>
+        <v>46329.75</v>
       </c>
       <c r="L80" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3906,34 +3909,31 @@
         <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="C81" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D81" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F81" t="s">
-        <v>52</v>
-      </c>
-      <c r="G81" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="I81" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J81" s="2">
-        <v>46329.791666666664</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K81" s="2">
-        <v>46330.75</v>
+        <v>46332.625</v>
       </c>
       <c r="L81" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:12">
@@ -3941,31 +3941,34 @@
         <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="C82" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D82" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F82" t="s">
         <v>52</v>
       </c>
+      <c r="G82" t="s">
+        <v>28</v>
+      </c>
       <c r="I82" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J82" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K82" s="2">
-        <v>46334</v>
+        <v>46330.75</v>
       </c>
       <c r="L82" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="83" spans="1:12">
@@ -4005,25 +4008,28 @@
         <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C84" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D84" t="s">
-        <v>88</v>
+        <v>183</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="F84" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="I84" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K84" s="2">
-        <v>46331.125</v>
+        <v>46334</v>
       </c>
       <c r="L84" t="s">
         <v>21</v>
@@ -4034,28 +4040,25 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C85" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="F85" t="s">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="I85" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.625</v>
       </c>
       <c r="K85" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.125</v>
       </c>
       <c r="L85" t="s">
         <v>21</v>
@@ -4098,25 +4101,28 @@
         <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="C87" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D87" t="s">
-        <v>116</v>
+        <v>185</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="F87" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="I87" t="s">
         <v>20</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.204861111109</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L87" t="s">
         <v>21</v>
@@ -4124,31 +4130,28 @@
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="C88" t="s">
-        <v>39</v>
+        <v>79</v>
       </c>
       <c r="D88" t="s">
-        <v>187</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>188</v>
+        <v>116</v>
       </c>
       <c r="F88" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="I88" t="s">
         <v>20</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.75</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K88" s="2">
-        <v>46332.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L88" t="s">
         <v>21</v>
@@ -4156,37 +4159,34 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>139</v>
+        <v>38</v>
       </c>
       <c r="C89" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D89" t="s">
-        <v>189</v>
-      </c>
-      <c r="E89" s="1">
-        <v>1</v>
+        <v>187</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F89" t="s">
-        <v>59</v>
-      </c>
-      <c r="G89" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I89" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J89" s="2">
-        <v>46331.25</v>
+        <v>46330.75</v>
       </c>
       <c r="K89" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L89" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:12">
@@ -4194,16 +4194,16 @@
         <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C90" t="s">
         <v>44</v>
       </c>
       <c r="D90" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E90" s="1">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="F90" t="s">
         <v>59</v>
@@ -4235,20 +4235,17 @@
         <v>44</v>
       </c>
       <c r="D91" t="s">
-        <v>191</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
+      </c>
+      <c r="E91" s="1">
+        <v>10</v>
       </c>
       <c r="F91" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="G91" t="s">
         <v>28</v>
       </c>
-      <c r="H91" t="s">
-        <v>193</v>
-      </c>
       <c r="I91" t="s">
         <v>48</v>
       </c>
@@ -4264,63 +4261,69 @@
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B92" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C92" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F92" t="s">
-        <v>42</v>
+        <v>47</v>
+      </c>
+      <c r="G92" t="s">
+        <v>28</v>
+      </c>
+      <c r="H92" t="s">
+        <v>193</v>
       </c>
       <c r="I92" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K92" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L92" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C93" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D93" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F93" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
       <c r="I93" t="s">
         <v>20</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K93" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L93" t="s">
         <v>21</v>
@@ -4363,37 +4366,31 @@
         <v>22</v>
       </c>
       <c r="B95" t="s">
-        <v>139</v>
+        <v>68</v>
       </c>
       <c r="C95" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="D95" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="F95" t="s">
-        <v>47</v>
-      </c>
-      <c r="G95" t="s">
-        <v>28</v>
-      </c>
-      <c r="H95" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="I95" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L95" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4407,17 +4404,20 @@
         <v>44</v>
       </c>
       <c r="D96" t="s">
-        <v>190</v>
-      </c>
-      <c r="E96" s="1">
-        <v>10</v>
+        <v>191</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>192</v>
       </c>
       <c r="F96" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="G96" t="s">
         <v>28</v>
       </c>
+      <c r="H96" t="s">
+        <v>193</v>
+      </c>
       <c r="I96" t="s">
         <v>48</v>
       </c>
@@ -4436,16 +4436,16 @@
         <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C97" t="s">
         <v>44</v>
       </c>
       <c r="D97" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E97" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F97" t="s">
         <v>59</v>
@@ -4468,89 +4468,98 @@
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C98" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>197</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
+      </c>
+      <c r="E98" s="1">
+        <v>1</v>
       </c>
       <c r="F98" t="s">
-        <v>104</v>
+        <v>59</v>
+      </c>
+      <c r="G98" t="s">
+        <v>28</v>
       </c>
       <c r="I98" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J98" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L98" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C99" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="D99" t="s">
-        <v>145</v>
+        <v>197</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F99" t="s">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I99" t="s">
         <v>20</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.291666666664</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L99" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>78</v>
+      </c>
+      <c r="C100" t="s">
+        <v>79</v>
       </c>
       <c r="D100" t="s">
-        <v>199</v>
+        <v>145</v>
       </c>
       <c r="F100" t="s">
-        <v>57</v>
+        <v>82</v>
       </c>
       <c r="I100" t="s">
         <v>20</v>
       </c>
       <c r="J100" s="2">
-        <v>46332.375</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46333.5</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L100" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -5434,29 +5443,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5594,18 +5586,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
-</file>
-
-<file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
--- a/data/vessels/2026-10-17.xlsx
+++ b/data/vessels/2026-10-17.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="433835" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6594652D-3C64-4336-AE90-20982FA52640}"/>
+  <xr:revisionPtr revIDLastSave="434254" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{799A2A08-C030-43C6-9728-FE0684AA2347}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="230">
   <si>
     <t>Harbor</t>
   </si>
@@ -239,25 +239,34 @@
     <t>BEN LINES</t>
   </si>
   <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
     <t>MSC DENISSE X</t>
   </si>
   <si>
     <t>UK641R</t>
   </si>
   <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
   </si>
   <si>
     <t>T7</t>
@@ -266,15 +275,6 @@
     <t>THEMIS LEADER</t>
   </si>
   <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
     <t>WST</t>
   </si>
   <si>
@@ -386,7 +386,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3 days</t>
+    <t>Waiting 3.2 days</t>
   </si>
   <si>
     <t>RJ PFEIFFER</t>
@@ -515,18 +515,18 @@
     <t>OYNT0002E</t>
   </si>
   <si>
+    <t>MSC SOLA</t>
+  </si>
+  <si>
+    <t>UK643R</t>
+  </si>
+  <si>
     <t>ONE DURBAN</t>
   </si>
   <si>
     <t>NBBT0001E</t>
   </si>
   <si>
-    <t>MSC SOLA</t>
-  </si>
-  <si>
-    <t>UK643R</t>
-  </si>
-  <si>
     <t>MORNING LUCY</t>
   </si>
   <si>
@@ -608,19 +608,19 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>TONGALA</t>
+  </si>
+  <si>
+    <t>KW666</t>
+  </si>
+  <si>
+    <t>Jones Stevedoring Co</t>
+  </si>
+  <si>
+    <t>GLOVIS TREASURE</t>
+  </si>
+  <si>
     <t>GLOVIS LEGEND</t>
-  </si>
-  <si>
-    <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>TONGALA</t>
-  </si>
-  <si>
-    <t>KW666</t>
-  </si>
-  <si>
-    <t>Jones Stevedoring Co</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -801,10 +801,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L128" totalsRowShown="0">
-  <autoFilter ref="A1:L128" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L128">
-    <sortCondition ref="J2:J128"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L131" totalsRowShown="0">
+  <autoFilter ref="A1:L131" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L131">
+    <sortCondition ref="J2:J131"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1141,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L128"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1691,25 +1691,25 @@
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I16" t="s">
         <v>20</v>
@@ -1726,25 +1726,25 @@
     </row>
     <row r="17" spans="1:12">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C17" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="G17" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="I17" t="s">
         <v>20</v>
@@ -1764,22 +1764,25 @@
         <v>22</v>
       </c>
       <c r="B18" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
         <v>44</v>
       </c>
       <c r="D18" t="s">
+        <v>73</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="E18" s="1">
-        <v>63</v>
-      </c>
       <c r="F18" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G18" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="H18" t="s">
+        <v>75</v>
       </c>
       <c r="I18" t="s">
         <v>48</v>
@@ -1799,25 +1802,22 @@
         <v>22</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
         <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>75</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="E19" s="1">
+        <v>63</v>
       </c>
       <c r="F19" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G19" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" t="s">
-        <v>77</v>
+        <v>18</v>
       </c>
       <c r="I19" t="s">
         <v>48</v>
@@ -1910,31 +1910,34 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C22" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
+      </c>
+      <c r="E22" s="1">
+        <v>26169</v>
       </c>
       <c r="F22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="G22" t="s">
-        <v>28</v>
+        <v>90</v>
+      </c>
+      <c r="H22" t="s">
+        <v>90</v>
       </c>
       <c r="I22" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J22" s="2">
         <v>46316.625</v>
       </c>
       <c r="K22" s="2">
-        <v>46319.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L22" t="s">
         <v>21</v>
@@ -1945,34 +1948,31 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C23" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
-      </c>
-      <c r="E23" s="1">
-        <v>26169</v>
+        <v>83</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G23" t="s">
-        <v>90</v>
-      </c>
-      <c r="H23" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J23" s="2">
         <v>46316.625</v>
       </c>
       <c r="K23" s="2">
-        <v>46317.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L23" t="s">
         <v>21</v>
@@ -1983,13 +1983,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C24" t="s">
         <v>44</v>
       </c>
       <c r="D24" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E24" s="1" t="s">
         <v>92</v>
@@ -2001,7 +2001,7 @@
         <v>28</v>
       </c>
       <c r="H24" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="I24" t="s">
         <v>48</v>
@@ -2085,7 +2085,7 @@
         <v>22</v>
       </c>
       <c r="B27" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C27" t="s">
         <v>44</v>
@@ -2120,7 +2120,7 @@
         <v>22</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C28" t="s">
         <v>44</v>
@@ -2473,7 +2473,7 @@
         <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
@@ -2511,22 +2511,25 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>43</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
         <v>44</v>
       </c>
       <c r="D39" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="F39" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="H39" t="s">
+        <v>121</v>
       </c>
       <c r="I39" t="s">
         <v>48</v>
@@ -2535,7 +2538,7 @@
         <v>46319.25</v>
       </c>
       <c r="K39" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L39" t="s">
         <v>49</v>
@@ -2581,25 +2584,22 @@
         <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
         <v>44</v>
       </c>
       <c r="D41" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="F41" t="s">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="G41" t="s">
-        <v>18</v>
-      </c>
-      <c r="H41" t="s">
-        <v>121</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
         <v>48</v>
@@ -2608,7 +2608,7 @@
         <v>46319.25</v>
       </c>
       <c r="K41" s="2">
-        <v>46320.166666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L41" t="s">
         <v>49</v>
@@ -2651,34 +2651,34 @@
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" t="s">
-        <v>125</v>
+        <v>13</v>
       </c>
       <c r="D43" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>127</v>
+        <v>56</v>
       </c>
       <c r="F43" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="G43" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="H43" t="s">
+        <v>19</v>
       </c>
       <c r="I43" t="s">
         <v>20</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.666666666664</v>
+        <v>46319.625</v>
       </c>
       <c r="K43" s="2">
-        <v>46321.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L43" t="s">
         <v>21</v>
@@ -2689,28 +2689,31 @@
         <v>22</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="D44" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F44" t="s">
-        <v>64</v>
+        <v>70</v>
+      </c>
+      <c r="G44" t="s">
+        <v>18</v>
       </c>
       <c r="I44" t="s">
         <v>20</v>
       </c>
       <c r="J44" s="2">
-        <v>46320</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K44" s="2">
-        <v>46322</v>
+        <v>46321.75</v>
       </c>
       <c r="L44" t="s">
         <v>21</v>
@@ -2718,31 +2721,34 @@
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B45" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>125</v>
       </c>
       <c r="D45" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F45" t="s">
-        <v>32</v>
+        <v>70</v>
+      </c>
+      <c r="G45" t="s">
+        <v>18</v>
       </c>
       <c r="I45" t="s">
         <v>20</v>
       </c>
       <c r="J45" s="2">
-        <v>46320.21875</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K45" s="2">
-        <v>46324.59375</v>
+        <v>46321.75</v>
       </c>
       <c r="L45" t="s">
         <v>21</v>
@@ -2750,34 +2756,31 @@
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B46" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C46" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="D46" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G46" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="I46" t="s">
         <v>20</v>
       </c>
       <c r="J46" s="2">
-        <v>46321.208333333336</v>
+        <v>46320</v>
       </c>
       <c r="K46" s="2">
-        <v>46322.166666666664</v>
+        <v>46322</v>
       </c>
       <c r="L46" t="s">
         <v>21</v>
@@ -2788,28 +2791,28 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
       </c>
       <c r="J47" s="2">
-        <v>46321.21875</v>
+        <v>46320.21875</v>
       </c>
       <c r="K47" s="2">
-        <v>46323.21875</v>
+        <v>46324.59375</v>
       </c>
       <c r="L47" t="s">
         <v>21</v>
@@ -2817,34 +2820,34 @@
     </row>
     <row r="48" spans="1:12">
       <c r="A48" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F48" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="G48" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.25</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K48" s="2">
-        <v>46323.166666666664</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L48" t="s">
         <v>21</v>
@@ -2852,34 +2855,31 @@
     </row>
     <row r="49" spans="1:12">
       <c r="A49" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B49" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="C49" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>138</v>
-      </c>
-      <c r="E49" s="1">
-        <v>21</v>
+        <v>134</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>135</v>
       </c>
       <c r="F49" t="s">
-        <v>72</v>
-      </c>
-      <c r="G49" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
         <v>20</v>
       </c>
       <c r="J49" s="2">
-        <v>46321.625</v>
+        <v>46321.21875</v>
       </c>
       <c r="K49" s="2">
-        <v>46325.75</v>
+        <v>46323.21875</v>
       </c>
       <c r="L49" t="s">
         <v>21</v>
@@ -2890,34 +2890,34 @@
         <v>22</v>
       </c>
       <c r="B50" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C50" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D50" t="s">
-        <v>140</v>
+        <v>136</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="F50" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="G50" t="s">
         <v>18</v>
       </c>
-      <c r="H50" t="s">
-        <v>121</v>
-      </c>
       <c r="I50" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J50" s="2">
-        <v>46322.25</v>
+        <v>46321.25</v>
       </c>
       <c r="K50" s="2">
-        <v>46322.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L50" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51" spans="1:12">
@@ -2928,16 +2928,16 @@
         <v>23</v>
       </c>
       <c r="C51" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D51" t="s">
-        <v>141</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>142</v>
+        <v>138</v>
+      </c>
+      <c r="E51" s="1">
+        <v>21</v>
       </c>
       <c r="F51" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="G51" t="s">
         <v>28</v>
@@ -2946,7 +2946,7 @@
         <v>20</v>
       </c>
       <c r="J51" s="2">
-        <v>46322.625</v>
+        <v>46321.625</v>
       </c>
       <c r="K51" s="2">
         <v>46325.75</v>
@@ -2960,31 +2960,31 @@
         <v>22</v>
       </c>
       <c r="B52" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C52" t="s">
         <v>44</v>
       </c>
       <c r="D52" t="s">
-        <v>143</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F52" t="s">
-        <v>52</v>
+        <v>120</v>
       </c>
       <c r="G52" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="H52" t="s">
+        <v>121</v>
       </c>
       <c r="I52" t="s">
         <v>48</v>
       </c>
       <c r="J52" s="2">
-        <v>46323.25</v>
+        <v>46322.25</v>
       </c>
       <c r="K52" s="2">
-        <v>46323.75</v>
+        <v>46322.75</v>
       </c>
       <c r="L52" t="s">
         <v>49</v>
@@ -2995,28 +2995,34 @@
         <v>22</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="C53" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D53" t="s">
-        <v>145</v>
+        <v>141</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="F53" t="s">
-        <v>82</v>
+        <v>85</v>
+      </c>
+      <c r="G53" t="s">
+        <v>28</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
       </c>
       <c r="J53" s="2">
-        <v>46323.291666666664</v>
+        <v>46322.625</v>
       </c>
       <c r="K53" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L53" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="1:12">
@@ -3024,37 +3030,34 @@
         <v>22</v>
       </c>
       <c r="B54" t="s">
-        <v>86</v>
+        <v>43</v>
       </c>
       <c r="C54" t="s">
-        <v>87</v>
+        <v>44</v>
       </c>
       <c r="D54" t="s">
-        <v>88</v>
-      </c>
-      <c r="E54" s="1">
-        <v>26173</v>
+        <v>143</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>144</v>
       </c>
       <c r="F54" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="G54" t="s">
-        <v>90</v>
-      </c>
-      <c r="H54" t="s">
-        <v>90</v>
+        <v>28</v>
       </c>
       <c r="I54" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.625</v>
+        <v>46323.25</v>
       </c>
       <c r="K54" s="2">
-        <v>46324.041666666664</v>
+        <v>46323.75</v>
       </c>
       <c r="L54" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:12">
@@ -3062,31 +3065,25 @@
         <v>22</v>
       </c>
       <c r="B55" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="C55" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>143</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F55" t="s">
-        <v>52</v>
-      </c>
-      <c r="G55" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J55" s="2">
+        <v>46323.291666666664</v>
+      </c>
+      <c r="K55" s="2">
         <v>46323.791666666664</v>
-      </c>
-      <c r="K55" s="2">
-        <v>46324.75</v>
       </c>
       <c r="L55" t="s">
         <v>49</v>
@@ -3097,25 +3094,34 @@
         <v>22</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>86</v>
+      </c>
+      <c r="C56" t="s">
+        <v>87</v>
       </c>
       <c r="D56" t="s">
-        <v>146</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>147</v>
+        <v>88</v>
+      </c>
+      <c r="E56" s="1">
+        <v>26173</v>
       </c>
       <c r="F56" t="s">
-        <v>64</v>
+        <v>89</v>
+      </c>
+      <c r="G56" t="s">
+        <v>90</v>
+      </c>
+      <c r="H56" t="s">
+        <v>90</v>
       </c>
       <c r="I56" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J56" s="2">
-        <v>46324</v>
+        <v>46323.625</v>
       </c>
       <c r="K56" s="2">
-        <v>46326</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L56" t="s">
         <v>21</v>
@@ -3123,63 +3129,63 @@
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B57" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C57" t="s">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="D57" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="F57" t="s">
-        <v>32</v>
+        <v>52</v>
+      </c>
+      <c r="G57" t="s">
+        <v>28</v>
       </c>
       <c r="I57" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J57" s="2">
-        <v>46324.647916666669</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K57" s="2">
-        <v>46326.147916666669</v>
+        <v>46324.75</v>
       </c>
       <c r="L57" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B58" t="s">
-        <v>38</v>
-      </c>
-      <c r="C58" t="s">
-        <v>96</v>
+        <v>60</v>
       </c>
       <c r="D58" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="F58" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="I58" t="s">
         <v>20</v>
       </c>
       <c r="J58" s="2">
-        <v>46325.003472222219</v>
+        <v>46324</v>
       </c>
       <c r="K58" s="2">
-        <v>46325.878472222219</v>
+        <v>46326</v>
       </c>
       <c r="L58" t="s">
         <v>21</v>
@@ -3193,25 +3199,25 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D59" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F59" t="s">
-        <v>104</v>
+        <v>32</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
       </c>
       <c r="J59" s="2">
-        <v>46325.056944444441</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K59" s="2">
-        <v>46326.098611111112</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L59" t="s">
         <v>21</v>
@@ -3219,28 +3225,31 @@
     </row>
     <row r="60" spans="1:12">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C60" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="D60" t="s">
-        <v>80</v>
+        <v>151</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="F60" t="s">
-        <v>82</v>
+        <v>42</v>
       </c>
       <c r="I60" t="s">
         <v>20</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.333333333336</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K60" s="2">
-        <v>46325.833333333336</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L60" t="s">
         <v>21</v>
@@ -3248,40 +3257,34 @@
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="C61" t="s">
-        <v>113</v>
+        <v>153</v>
       </c>
       <c r="D61" t="s">
-        <v>114</v>
-      </c>
-      <c r="E61" s="1">
-        <v>26172</v>
+        <v>154</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="F61" t="s">
-        <v>89</v>
-      </c>
-      <c r="G61" t="s">
-        <v>90</v>
-      </c>
-      <c r="H61" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="I61" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.625</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K61" s="2">
-        <v>46326.041666666664</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L61" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:12">
@@ -3289,28 +3292,25 @@
         <v>22</v>
       </c>
       <c r="B62" t="s">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D62" t="s">
-        <v>156</v>
-      </c>
-      <c r="E62" s="1" t="s">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="F62" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.625</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K62" s="2">
-        <v>46329.708333333336</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L62" t="s">
         <v>21</v>
@@ -3321,31 +3321,37 @@
         <v>22</v>
       </c>
       <c r="B63" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C63" t="s">
-        <v>53</v>
+        <v>113</v>
       </c>
       <c r="D63" t="s">
-        <v>156</v>
-      </c>
-      <c r="E63" s="1" t="s">
-        <v>157</v>
+        <v>114</v>
+      </c>
+      <c r="E63" s="1">
+        <v>26172</v>
       </c>
       <c r="F63" t="s">
-        <v>52</v>
+        <v>89</v>
+      </c>
+      <c r="G63" t="s">
+        <v>90</v>
+      </c>
+      <c r="H63" t="s">
+        <v>90</v>
       </c>
       <c r="I63" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J63" s="2">
         <v>46325.625</v>
       </c>
       <c r="K63" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L63" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:12">
@@ -3353,16 +3359,16 @@
         <v>22</v>
       </c>
       <c r="B64" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="D64" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F64" t="s">
         <v>52</v>
@@ -3371,10 +3377,10 @@
         <v>20</v>
       </c>
       <c r="J64" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K64" s="2">
-        <v>46328.916666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L64" t="s">
         <v>21</v>
@@ -3385,16 +3391,16 @@
         <v>22</v>
       </c>
       <c r="B65" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="C65" t="s">
-        <v>125</v>
+        <v>53</v>
       </c>
       <c r="D65" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F65" t="s">
         <v>52</v>
@@ -3403,10 +3409,10 @@
         <v>20</v>
       </c>
       <c r="J65" s="2">
-        <v>46326.166666666664</v>
+        <v>46325.625</v>
       </c>
       <c r="K65" s="2">
-        <v>46328.916666666664</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L65" t="s">
         <v>21</v>
@@ -3423,10 +3429,10 @@
         <v>39</v>
       </c>
       <c r="D66" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F66" t="s">
         <v>42</v>
@@ -3446,13 +3452,13 @@
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B67" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="C67" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="D67" t="s">
         <v>160</v>
@@ -3461,7 +3467,7 @@
         <v>161</v>
       </c>
       <c r="F67" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="I67" t="s">
         <v>20</v>
@@ -3470,7 +3476,7 @@
         <v>46326.166666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.125</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L67" t="s">
         <v>21</v>
@@ -3478,37 +3484,34 @@
     </row>
     <row r="68" spans="1:12">
       <c r="A68" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C68" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D68" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="F68" t="s">
-        <v>47</v>
-      </c>
-      <c r="G68" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J68" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46326.75</v>
+        <v>46328.125</v>
       </c>
       <c r="L68" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3516,34 +3519,31 @@
         <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C69" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D69" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F69" t="s">
         <v>52</v>
       </c>
-      <c r="G69" t="s">
-        <v>28</v>
-      </c>
       <c r="I69" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.25</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46326.75</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L69" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3551,19 +3551,19 @@
         <v>22</v>
       </c>
       <c r="B70" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C70" t="s">
         <v>44</v>
       </c>
       <c r="D70" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F70" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="G70" t="s">
         <v>28</v>
@@ -3586,19 +3586,19 @@
         <v>22</v>
       </c>
       <c r="B71" t="s">
-        <v>43</v>
+        <v>139</v>
       </c>
       <c r="C71" t="s">
         <v>44</v>
       </c>
       <c r="D71" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F71" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="G71" t="s">
         <v>28</v>
@@ -3621,22 +3621,28 @@
         <v>22</v>
       </c>
       <c r="B72" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="C72" t="s">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="D72" t="s">
-        <v>166</v>
+        <v>164</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="F72" t="s">
-        <v>82</v>
+        <v>52</v>
+      </c>
+      <c r="G72" t="s">
+        <v>28</v>
       </c>
       <c r="I72" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.416666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K72" s="2">
         <v>46326.75</v>
@@ -3650,7 +3656,7 @@
         <v>22</v>
       </c>
       <c r="B73" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C73" t="s">
         <v>44</v>
@@ -3671,10 +3677,10 @@
         <v>48</v>
       </c>
       <c r="J73" s="2">
-        <v>46326.791666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K73" s="2">
-        <v>46327.75</v>
+        <v>46326.75</v>
       </c>
       <c r="L73" t="s">
         <v>49</v>
@@ -3685,63 +3691,63 @@
         <v>22</v>
       </c>
       <c r="B74" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="C74" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="D74" t="s">
-        <v>167</v>
-      </c>
-      <c r="E74" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F74" t="s">
-        <v>169</v>
+        <v>82</v>
       </c>
       <c r="I74" t="s">
         <v>20</v>
       </c>
       <c r="J74" s="2">
-        <v>46326.833333333336</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K74" s="2">
-        <v>46329.583333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L74" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B75" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D75" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="F75" t="s">
-        <v>32</v>
+        <v>47</v>
+      </c>
+      <c r="G75" t="s">
+        <v>28</v>
       </c>
       <c r="I75" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J75" s="2">
-        <v>46327.166666666664</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K75" s="2">
-        <v>46328.541666666664</v>
+        <v>46327.75</v>
       </c>
       <c r="L75" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -3749,34 +3755,31 @@
         <v>22</v>
       </c>
       <c r="B76" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C76" t="s">
-        <v>44</v>
+        <v>125</v>
       </c>
       <c r="D76" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="F76" t="s">
-        <v>52</v>
-      </c>
-      <c r="G76" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="I76" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J76" s="2">
-        <v>46327.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K76" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L76" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3786,20 +3789,26 @@
       <c r="B77" t="s">
         <v>13</v>
       </c>
+      <c r="C77" t="s">
+        <v>29</v>
+      </c>
       <c r="D77" t="s">
-        <v>174</v>
+        <v>170</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="F77" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="I77" t="s">
         <v>20</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.708333333336</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K77" s="2">
-        <v>46328.833333333336</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L77" t="s">
         <v>21</v>
@@ -3810,60 +3819,57 @@
         <v>22</v>
       </c>
       <c r="B78" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="C78" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D78" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F78" t="s">
         <v>52</v>
       </c>
+      <c r="G78" t="s">
+        <v>28</v>
+      </c>
       <c r="I78" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J78" s="2">
-        <v>46327.904861111114</v>
+        <v>46327.25</v>
       </c>
       <c r="K78" s="2">
-        <v>46331.196527777778</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="L78" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>60</v>
-      </c>
-      <c r="C79" t="s">
-        <v>61</v>
+        <v>13</v>
       </c>
       <c r="D79" t="s">
-        <v>177</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F79" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="I79" t="s">
         <v>20</v>
       </c>
       <c r="J79" s="2">
-        <v>46329</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K79" s="2">
-        <v>46330</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L79" t="s">
         <v>21</v>
@@ -3874,34 +3880,31 @@
         <v>22</v>
       </c>
       <c r="B80" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C80" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D80" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F80" t="s">
         <v>52</v>
       </c>
-      <c r="G80" t="s">
-        <v>28</v>
-      </c>
       <c r="I80" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J80" s="2">
-        <v>46329.25</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K80" s="2">
-        <v>46329.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L80" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="81" spans="1:12">
@@ -3909,28 +3912,28 @@
         <v>22</v>
       </c>
       <c r="B81" t="s">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="C81" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="D81" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F81" t="s">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="I81" t="s">
         <v>20</v>
       </c>
       <c r="J81" s="2">
-        <v>46329.333333333336</v>
+        <v>46329</v>
       </c>
       <c r="K81" s="2">
-        <v>46332.625</v>
+        <v>46330</v>
       </c>
       <c r="L81" t="s">
         <v>21</v>
@@ -3941,7 +3944,7 @@
         <v>22</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C82" t="s">
         <v>44</v>
@@ -3962,10 +3965,10 @@
         <v>48</v>
       </c>
       <c r="J82" s="2">
-        <v>46329.791666666664</v>
+        <v>46329.25</v>
       </c>
       <c r="K82" s="2">
-        <v>46330.75</v>
+        <v>46329.75</v>
       </c>
       <c r="L82" t="s">
         <v>49</v>
@@ -3979,25 +3982,25 @@
         <v>23</v>
       </c>
       <c r="C83" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D83" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F83" t="s">
-        <v>52</v>
+        <v>169</v>
       </c>
       <c r="I83" t="s">
         <v>20</v>
       </c>
       <c r="J83" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K83" s="2">
-        <v>46334</v>
+        <v>46332.625</v>
       </c>
       <c r="L83" t="s">
         <v>21</v>
@@ -4008,31 +4011,34 @@
         <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="C84" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="D84" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="F84" t="s">
         <v>52</v>
       </c>
+      <c r="G84" t="s">
+        <v>28</v>
+      </c>
       <c r="I84" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J84" s="2">
-        <v>46330.208333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K84" s="2">
-        <v>46334</v>
+        <v>46330.75</v>
       </c>
       <c r="L84" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4040,25 +4046,28 @@
         <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="D85" t="s">
-        <v>88</v>
+        <v>183</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>184</v>
       </c>
       <c r="F85" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="I85" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.625</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K85" s="2">
-        <v>46331.125</v>
+        <v>46334</v>
       </c>
       <c r="L85" t="s">
         <v>21</v>
@@ -4072,25 +4081,25 @@
         <v>23</v>
       </c>
       <c r="C86" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D86" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F86" t="s">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="I86" t="s">
         <v>20</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K86" s="2">
-        <v>46333.925000000003</v>
+        <v>46334</v>
       </c>
       <c r="L86" t="s">
         <v>21</v>
@@ -4101,28 +4110,25 @@
         <v>22</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="C87" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D87" t="s">
-        <v>185</v>
-      </c>
-      <c r="E87" s="1" t="s">
-        <v>186</v>
+        <v>88</v>
       </c>
       <c r="F87" t="s">
-        <v>169</v>
+        <v>89</v>
       </c>
       <c r="I87" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.633333333331</v>
+        <v>46330.625</v>
       </c>
       <c r="K87" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.125</v>
       </c>
       <c r="L87" t="s">
         <v>21</v>
@@ -4133,25 +4139,28 @@
         <v>22</v>
       </c>
       <c r="B88" t="s">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="C88" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D88" t="s">
-        <v>116</v>
+        <v>185</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>186</v>
       </c>
       <c r="F88" t="s">
-        <v>82</v>
+        <v>169</v>
       </c>
       <c r="I88" t="s">
         <v>20</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.704861111109</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K88" s="2">
-        <v>46331.204861111109</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L88" t="s">
         <v>21</v>
@@ -4159,31 +4168,31 @@
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B89" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="C89" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D89" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F89" t="s">
-        <v>42</v>
+        <v>169</v>
       </c>
       <c r="I89" t="s">
         <v>20</v>
       </c>
       <c r="J89" s="2">
-        <v>46330.75</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K89" s="2">
-        <v>46332.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L89" t="s">
         <v>21</v>
@@ -4194,69 +4203,60 @@
         <v>22</v>
       </c>
       <c r="B90" t="s">
-        <v>139</v>
+        <v>78</v>
       </c>
       <c r="C90" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="D90" t="s">
-        <v>189</v>
-      </c>
-      <c r="E90" s="1">
-        <v>1</v>
+        <v>116</v>
       </c>
       <c r="F90" t="s">
-        <v>59</v>
-      </c>
-      <c r="G90" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I90" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J90" s="2">
-        <v>46331.25</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K90" s="2">
-        <v>46331.75</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L90" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:12">
       <c r="A91" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C91" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="D91" t="s">
-        <v>190</v>
-      </c>
-      <c r="E91" s="1">
-        <v>10</v>
+        <v>187</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>188</v>
       </c>
       <c r="F91" t="s">
-        <v>59</v>
-      </c>
-      <c r="G91" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="I91" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J91" s="2">
-        <v>46331.25</v>
+        <v>46330.75</v>
       </c>
       <c r="K91" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L91" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4270,10 +4270,10 @@
         <v>44</v>
       </c>
       <c r="D92" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F92" t="s">
         <v>47</v>
@@ -4282,7 +4282,7 @@
         <v>28</v>
       </c>
       <c r="H92" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I92" t="s">
         <v>48</v>
@@ -4299,34 +4299,37 @@
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B93" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C93" t="s">
-        <v>96</v>
+        <v>44</v>
       </c>
       <c r="D93" t="s">
-        <v>194</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
+      </c>
+      <c r="E93" s="1">
+        <v>10</v>
       </c>
       <c r="F93" t="s">
-        <v>42</v>
+        <v>59</v>
+      </c>
+      <c r="G93" t="s">
+        <v>28</v>
       </c>
       <c r="I93" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J93" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.25</v>
       </c>
       <c r="K93" s="2">
-        <v>46332.166666666664</v>
+        <v>46331.75</v>
       </c>
       <c r="L93" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:12">
@@ -4334,60 +4337,63 @@
         <v>22</v>
       </c>
       <c r="B94" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="C94" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="D94" t="s">
-        <v>196</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>155</v>
+        <v>193</v>
+      </c>
+      <c r="E94" s="1">
+        <v>1</v>
       </c>
       <c r="F94" t="s">
-        <v>169</v>
+        <v>59</v>
+      </c>
+      <c r="G94" t="s">
+        <v>28</v>
       </c>
       <c r="I94" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.25</v>
       </c>
       <c r="K94" s="2">
-        <v>46334.746527777781</v>
+        <v>46331.75</v>
       </c>
       <c r="L94" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="95" spans="1:12">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B95" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C95" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D95" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="F95" t="s">
-        <v>169</v>
+        <v>42</v>
       </c>
       <c r="I95" t="s">
         <v>20</v>
       </c>
       <c r="J95" s="2">
-        <v>46331.496527777781</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L95" t="s">
         <v>21</v>
@@ -4398,37 +4404,31 @@
         <v>22</v>
       </c>
       <c r="B96" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C96" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D96" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>192</v>
+        <v>155</v>
       </c>
       <c r="F96" t="s">
-        <v>47</v>
-      </c>
-      <c r="G96" t="s">
-        <v>28</v>
-      </c>
-      <c r="H96" t="s">
-        <v>193</v>
+        <v>169</v>
       </c>
       <c r="I96" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J96" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K96" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L96" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4436,34 +4436,31 @@
         <v>22</v>
       </c>
       <c r="B97" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="C97" t="s">
-        <v>44</v>
+        <v>67</v>
       </c>
       <c r="D97" t="s">
-        <v>190</v>
-      </c>
-      <c r="E97" s="1">
-        <v>10</v>
+        <v>196</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>155</v>
       </c>
       <c r="F97" t="s">
-        <v>59</v>
-      </c>
-      <c r="G97" t="s">
-        <v>28</v>
+        <v>169</v>
       </c>
       <c r="I97" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J97" s="2">
-        <v>46331.791666666664</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K97" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L97" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -4477,7 +4474,7 @@
         <v>44</v>
       </c>
       <c r="D98" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E98" s="1">
         <v>1</v>
@@ -4503,34 +4500,37 @@
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>139</v>
       </c>
       <c r="C99" t="s">
-        <v>101</v>
+        <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>197</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>198</v>
+        <v>192</v>
+      </c>
+      <c r="E99" s="1">
+        <v>10</v>
       </c>
       <c r="F99" t="s">
-        <v>104</v>
+        <v>59</v>
+      </c>
+      <c r="G99" t="s">
+        <v>28</v>
       </c>
       <c r="I99" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J99" s="2">
-        <v>46332.056250000001</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.597916666666</v>
+        <v>46332.75</v>
       </c>
       <c r="L99" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="100" spans="1:12">
@@ -4538,25 +4538,34 @@
         <v>22</v>
       </c>
       <c r="B100" t="s">
-        <v>78</v>
+        <v>139</v>
       </c>
       <c r="C100" t="s">
-        <v>79</v>
+        <v>44</v>
       </c>
       <c r="D100" t="s">
-        <v>145</v>
+        <v>189</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>190</v>
       </c>
       <c r="F100" t="s">
-        <v>82</v>
+        <v>47</v>
+      </c>
+      <c r="G100" t="s">
+        <v>28</v>
+      </c>
+      <c r="H100" t="s">
+        <v>191</v>
       </c>
       <c r="I100" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J100" s="2">
-        <v>46332.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.791666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L100" t="s">
         <v>49</v>
@@ -4569,20 +4578,26 @@
       <c r="B101" t="s">
         <v>13</v>
       </c>
+      <c r="C101" t="s">
+        <v>101</v>
+      </c>
       <c r="D101" t="s">
-        <v>199</v>
+        <v>197</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>198</v>
       </c>
       <c r="F101" t="s">
-        <v>57</v>
+        <v>104</v>
       </c>
       <c r="I101" t="s">
         <v>20</v>
       </c>
       <c r="J101" s="2">
-        <v>46332.375</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K101" s="2">
-        <v>46333.5</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L101" t="s">
         <v>21</v>
@@ -4593,28 +4608,28 @@
         <v>22</v>
       </c>
       <c r="B102" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C102" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="D102" t="s">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="F102" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I102" t="s">
         <v>20</v>
       </c>
       <c r="J102" s="2">
-        <v>46332.541666666664</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K102" s="2">
-        <v>46333.041666666664</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L102" t="s">
-        <v>115</v>
+        <v>49</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4624,26 +4639,20 @@
       <c r="B103" t="s">
         <v>13</v>
       </c>
-      <c r="C103" t="s">
-        <v>14</v>
-      </c>
       <c r="D103" t="s">
-        <v>200</v>
-      </c>
-      <c r="E103" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F103" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="I103" t="s">
         <v>20</v>
       </c>
       <c r="J103" s="2">
-        <v>46332.875</v>
+        <v>46332.375</v>
       </c>
       <c r="K103" s="2">
-        <v>46334.25</v>
+        <v>46333.5</v>
       </c>
       <c r="L103" t="s">
         <v>21</v>
@@ -4651,34 +4660,31 @@
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>86</v>
       </c>
       <c r="C104" t="s">
-        <v>33</v>
+        <v>113</v>
       </c>
       <c r="D104" t="s">
-        <v>202</v>
-      </c>
-      <c r="E104" s="1" t="s">
-        <v>203</v>
+        <v>114</v>
       </c>
       <c r="F104" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
       <c r="I104" t="s">
         <v>20</v>
       </c>
       <c r="J104" s="2">
-        <v>46333</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K104" s="2">
-        <v>46334</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L104" t="s">
-        <v>21</v>
+        <v>115</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4689,25 +4695,25 @@
         <v>13</v>
       </c>
       <c r="C105" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D105" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F105" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="I105" t="s">
         <v>20</v>
       </c>
       <c r="J105" s="2">
-        <v>46333</v>
+        <v>46332.875</v>
       </c>
       <c r="K105" s="2">
-        <v>46334</v>
+        <v>46334.25</v>
       </c>
       <c r="L105" t="s">
         <v>21</v>
@@ -4715,28 +4721,31 @@
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B106" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="C106" t="s">
+        <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F106" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I106" t="s">
         <v>20</v>
       </c>
       <c r="J106" s="2">
-        <v>46333.041666666664</v>
+        <v>46333</v>
       </c>
       <c r="K106" s="2">
-        <v>46335.041666666664</v>
+        <v>46334</v>
       </c>
       <c r="L106" t="s">
         <v>21</v>
@@ -4744,28 +4753,31 @@
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B107" t="s">
-        <v>60</v>
+        <v>13</v>
+      </c>
+      <c r="C107" t="s">
+        <v>33</v>
       </c>
       <c r="D107" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F107" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I107" t="s">
         <v>20</v>
       </c>
       <c r="J107" s="2">
-        <v>46333.041666666664</v>
+        <v>46333</v>
       </c>
       <c r="K107" s="2">
-        <v>46335.041666666664</v>
+        <v>46334</v>
       </c>
       <c r="L107" t="s">
         <v>21</v>
@@ -4776,25 +4788,25 @@
         <v>22</v>
       </c>
       <c r="B108" t="s">
-        <v>78</v>
-      </c>
-      <c r="C108" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="D108" t="s">
-        <v>111</v>
+        <v>204</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="F108" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I108" t="s">
         <v>20</v>
       </c>
       <c r="J108" s="2">
-        <v>46333.416666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K108" s="2">
-        <v>46333.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L108" t="s">
         <v>21</v>
@@ -4802,28 +4814,25 @@
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
-      </c>
-      <c r="C109" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="D109" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F109" t="s">
-        <v>32</v>
+        <v>64</v>
       </c>
       <c r="I109" t="s">
         <v>20</v>
       </c>
       <c r="J109" s="2">
-        <v>46333.666666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K109" s="2">
         <v>46335.041666666664</v>
@@ -4837,63 +4846,57 @@
         <v>22</v>
       </c>
       <c r="B110" t="s">
-        <v>43</v>
+        <v>78</v>
       </c>
       <c r="C110" t="s">
-        <v>44</v>
+        <v>110</v>
       </c>
       <c r="D110" t="s">
-        <v>208</v>
-      </c>
-      <c r="E110" s="1">
-        <v>11</v>
+        <v>111</v>
       </c>
       <c r="F110" t="s">
-        <v>59</v>
-      </c>
-      <c r="G110" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I110" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J110" s="2">
-        <v>46334.25</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K110" s="2">
-        <v>46334.75</v>
+        <v>46333.75</v>
       </c>
       <c r="L110" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="111" spans="1:12">
       <c r="A111" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C111" t="s">
-        <v>125</v>
+        <v>29</v>
       </c>
       <c r="D111" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F111" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="I111" t="s">
         <v>20</v>
       </c>
       <c r="J111" s="2">
-        <v>46334.958333333336</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K111" s="2">
-        <v>46337.708333333336</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L111" t="s">
         <v>21</v>
@@ -4901,37 +4904,34 @@
     </row>
     <row r="112" spans="1:12">
       <c r="A112" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="C112" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D112" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="F112" t="s">
-        <v>52</v>
-      </c>
-      <c r="G112" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I112" t="s">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="J112" s="2">
-        <v>46335.25</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K112" s="2">
-        <v>46335.75</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L112" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -4945,13 +4945,13 @@
         <v>44</v>
       </c>
       <c r="D113" t="s">
-        <v>211</v>
-      </c>
-      <c r="E113" s="1" t="s">
-        <v>212</v>
+        <v>208</v>
+      </c>
+      <c r="E113" s="1">
+        <v>11</v>
       </c>
       <c r="F113" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G113" t="s">
         <v>28</v>
@@ -4960,10 +4960,10 @@
         <v>48</v>
       </c>
       <c r="J113" s="2">
-        <v>46335.791666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K113" s="2">
-        <v>46336.75</v>
+        <v>46334.75</v>
       </c>
       <c r="L113" t="s">
         <v>49</v>
@@ -4974,28 +4974,28 @@
         <v>22</v>
       </c>
       <c r="B114" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C114" t="s">
-        <v>61</v>
+        <v>125</v>
       </c>
       <c r="D114" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F114" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I114" t="s">
         <v>20</v>
       </c>
       <c r="J114" s="2">
-        <v>46337</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K114" s="2">
-        <v>46339</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L114" t="s">
         <v>21</v>
@@ -5006,31 +5006,34 @@
         <v>22</v>
       </c>
       <c r="B115" t="s">
-        <v>60</v>
+        <v>139</v>
       </c>
       <c r="C115" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="D115" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F115" t="s">
-        <v>64</v>
+        <v>52</v>
+      </c>
+      <c r="G115" t="s">
+        <v>28</v>
       </c>
       <c r="I115" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J115" s="2">
-        <v>46337.208333333336</v>
+        <v>46335.25</v>
       </c>
       <c r="K115" s="2">
-        <v>46340.208333333336</v>
+        <v>46335.75</v>
       </c>
       <c r="L115" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5038,16 +5041,16 @@
         <v>22</v>
       </c>
       <c r="B116" t="s">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="C116" t="s">
         <v>44</v>
       </c>
       <c r="D116" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F116" t="s">
         <v>52</v>
@@ -5059,10 +5062,10 @@
         <v>48</v>
       </c>
       <c r="J116" s="2">
-        <v>46337.25</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K116" s="2">
-        <v>46337.75</v>
+        <v>46336.75</v>
       </c>
       <c r="L116" t="s">
         <v>49</v>
@@ -5073,25 +5076,28 @@
         <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C117" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="D117" t="s">
-        <v>80</v>
+        <v>213</v>
+      </c>
+      <c r="E117" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="F117" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="I117" t="s">
         <v>20</v>
       </c>
       <c r="J117" s="2">
-        <v>46337.333333333336</v>
+        <v>46337</v>
       </c>
       <c r="K117" s="2">
-        <v>46337.833333333336</v>
+        <v>46339</v>
       </c>
       <c r="L117" t="s">
         <v>21</v>
@@ -5102,25 +5108,28 @@
         <v>22</v>
       </c>
       <c r="B118" t="s">
-        <v>86</v>
+        <v>60</v>
       </c>
       <c r="C118" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="D118" t="s">
-        <v>88</v>
+        <v>215</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="F118" t="s">
-        <v>89</v>
+        <v>64</v>
       </c>
       <c r="I118" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="J118" s="2">
-        <v>46337.625</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K118" s="2">
-        <v>46338.125</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L118" t="s">
         <v>21</v>
@@ -5128,60 +5137,63 @@
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B119" t="s">
-        <v>38</v>
+        <v>139</v>
       </c>
       <c r="C119" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D119" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="F119" t="s">
-        <v>42</v>
+        <v>52</v>
+      </c>
+      <c r="G119" t="s">
+        <v>28</v>
       </c>
       <c r="I119" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J119" s="2">
+        <v>46337.25</v>
+      </c>
+      <c r="K119" s="2">
         <v>46337.75</v>
       </c>
-      <c r="K119" s="2">
-        <v>46339.75</v>
-      </c>
       <c r="L119" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B120" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="C120" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="D120" t="s">
-        <v>221</v>
+        <v>80</v>
       </c>
       <c r="F120" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="I120" t="s">
         <v>20</v>
       </c>
       <c r="J120" s="2">
-        <v>46338.431250000001</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K120" s="2">
-        <v>46339.472916666666</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L120" t="s">
         <v>21</v>
@@ -5189,31 +5201,28 @@
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>86</v>
       </c>
       <c r="C121" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="D121" t="s">
-        <v>222</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>223</v>
+        <v>88</v>
       </c>
       <c r="F121" t="s">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="I121" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="J121" s="2">
-        <v>46338.709027777775</v>
+        <v>46337.625</v>
       </c>
       <c r="K121" s="2">
-        <v>46339.584027777775</v>
+        <v>46338.125</v>
       </c>
       <c r="L121" t="s">
         <v>21</v>
@@ -5224,28 +5233,28 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C122" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="D122" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F122" t="s">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c r="I122" t="s">
         <v>20</v>
       </c>
       <c r="J122" s="2">
-        <v>46338.791666666664</v>
+        <v>46337.75</v>
       </c>
       <c r="K122" s="2">
-        <v>46340.166666666664</v>
+        <v>46339.75</v>
       </c>
       <c r="L122" t="s">
         <v>21</v>
@@ -5253,31 +5262,28 @@
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="C123" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="D123" t="s">
-        <v>226</v>
-      </c>
-      <c r="E123" s="1" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="F123" t="s">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="I123" t="s">
         <v>20</v>
       </c>
       <c r="J123" s="2">
-        <v>46338.958333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K123" s="2">
-        <v>46342.208333333336</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L123" t="s">
         <v>21</v>
@@ -5285,31 +5291,31 @@
     </row>
     <row r="124" spans="1:12">
       <c r="A124" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C124" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="D124" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F124" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="I124" t="s">
         <v>20</v>
       </c>
       <c r="J124" s="2">
-        <v>46338.958333333336</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K124" s="2">
-        <v>46342.208333333336</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L124" t="s">
         <v>21</v>
@@ -5323,25 +5329,25 @@
         <v>13</v>
       </c>
       <c r="C125" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D125" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F125" t="s">
-        <v>169</v>
+        <v>17</v>
       </c>
       <c r="I125" t="s">
         <v>20</v>
       </c>
       <c r="J125" s="2">
-        <v>46339.083333333336</v>
+        <v>46338.791666666664</v>
       </c>
       <c r="K125" s="2">
-        <v>46340.291666666664</v>
+        <v>46340.166666666664</v>
       </c>
       <c r="L125" t="s">
         <v>21</v>
@@ -5352,28 +5358,31 @@
         <v>22</v>
       </c>
       <c r="B126" t="s">
-        <v>86</v>
+        <v>66</v>
       </c>
       <c r="C126" t="s">
-        <v>113</v>
+        <v>67</v>
       </c>
       <c r="D126" t="s">
-        <v>114</v>
+        <v>226</v>
+      </c>
+      <c r="E126" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="F126" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="I126" t="s">
         <v>20</v>
       </c>
       <c r="J126" s="2">
-        <v>46339.541666666664</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K126" s="2">
-        <v>46340.041666666664</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L126" t="s">
-        <v>115</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:12">
@@ -5381,25 +5390,28 @@
         <v>22</v>
       </c>
       <c r="B127" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="C127" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="D127" t="s">
-        <v>116</v>
+        <v>226</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="F127" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I127" t="s">
         <v>20</v>
       </c>
       <c r="J127" s="2">
-        <v>46339.704861111109</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K127" s="2">
-        <v>46340.204861111109</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L127" t="s">
         <v>21</v>
@@ -5407,30 +5419,120 @@
     </row>
     <row r="128" spans="1:12">
       <c r="A128" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B128" t="s">
+        <v>13</v>
+      </c>
+      <c r="C128" t="s">
+        <v>33</v>
+      </c>
+      <c r="D128" t="s">
+        <v>228</v>
+      </c>
+      <c r="E128" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="F128" t="s">
+        <v>169</v>
+      </c>
+      <c r="I128" t="s">
+        <v>20</v>
+      </c>
+      <c r="J128" s="2">
+        <v>46339.083333333336</v>
+      </c>
+      <c r="K128" s="2">
+        <v>46340.291666666664</v>
+      </c>
+      <c r="L128" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12">
+      <c r="A129" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" t="s">
+        <v>86</v>
+      </c>
+      <c r="C129" t="s">
+        <v>113</v>
+      </c>
+      <c r="D129" t="s">
+        <v>114</v>
+      </c>
+      <c r="F129" t="s">
+        <v>89</v>
+      </c>
+      <c r="I129" t="s">
+        <v>20</v>
+      </c>
+      <c r="J129" s="2">
+        <v>46339.541666666664</v>
+      </c>
+      <c r="K129" s="2">
+        <v>46340.041666666664</v>
+      </c>
+      <c r="L129" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12">
+      <c r="A130" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130" t="s">
         <v>78</v>
       </c>
-      <c r="C128" t="s">
+      <c r="C130" t="s">
+        <v>79</v>
+      </c>
+      <c r="D130" t="s">
+        <v>116</v>
+      </c>
+      <c r="F130" t="s">
+        <v>82</v>
+      </c>
+      <c r="I130" t="s">
+        <v>20</v>
+      </c>
+      <c r="J130" s="2">
+        <v>46339.704861111109</v>
+      </c>
+      <c r="K130" s="2">
+        <v>46340.204861111109</v>
+      </c>
+      <c r="L130" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12">
+      <c r="A131" t="s">
+        <v>22</v>
+      </c>
+      <c r="B131" t="s">
+        <v>78</v>
+      </c>
+      <c r="C131" t="s">
         <v>110</v>
       </c>
-      <c r="D128" t="s">
+      <c r="D131" t="s">
         <v>166</v>
       </c>
-      <c r="F128" t="s">
+      <c r="F131" t="s">
         <v>82</v>
       </c>
-      <c r="I128" t="s">
-        <v>20</v>
-      </c>
-      <c r="J128" s="2">
+      <c r="I131" t="s">
+        <v>20</v>
+      </c>
+      <c r="J131" s="2">
         <v>46340.416666666664</v>
       </c>
-      <c r="K128" s="2">
+      <c r="K131" s="2">
         <v>46340.75</v>
       </c>
-      <c r="L128" t="s">
+      <c r="L131" t="s">
         <v>49</v>
       </c>
     </row>
@@ -5443,12 +5545,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5586,7 +5682,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -5595,7 +5691,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
   <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
   <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
@@ -5603,18 +5699,24 @@
 </scriptIds>
 </file>
 
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
--- a/data/vessels/2026-10-17.xlsx
+++ b/data/vessels/2026-10-17.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30611"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://portoftacoma.sharepoint.com/sites/dnateam-Technical/Shared Documents/Technical/External Dashboards/Vessel Schedule/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="434254" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{799A2A08-C030-43C6-9728-FE0684AA2347}"/>
+  <xr:revisionPtr revIDLastSave="434799" documentId="8_{7437B347-3B45-47A9-B5DF-E84211A5B205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C0C7EF6C-12B4-4FDB-BE16-21EFA4D20FD9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6E7AA7D4-05A2-4831-A105-C5B1AC660A61}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="228">
   <si>
     <t>Harbor</t>
   </si>
@@ -77,300 +77,294 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>Husky</t>
+  </si>
+  <si>
+    <t>WC4/TP5</t>
+  </si>
+  <si>
+    <t>MAERSK TORINO</t>
+  </si>
+  <si>
+    <t>639E/642W</t>
+  </si>
+  <si>
+    <t>Maersk</t>
+  </si>
+  <si>
+    <t>Norton Lilly International</t>
+  </si>
+  <si>
+    <t>Container</t>
+  </si>
+  <si>
+    <t>In transit</t>
+  </si>
+  <si>
     <t>Seattle</t>
   </si>
   <si>
     <t>T18</t>
   </si>
   <si>
+    <t>CPNW</t>
+  </si>
+  <si>
+    <t>CMA CGM ALMAVIVA</t>
+  </si>
+  <si>
+    <t>CPN02/CPN03</t>
+  </si>
+  <si>
+    <t>CMA CGM</t>
+  </si>
+  <si>
+    <t>CPV</t>
+  </si>
+  <si>
+    <t>XIN YING KOU</t>
+  </si>
+  <si>
+    <t>269N/269S</t>
+  </si>
+  <si>
+    <t>COSCO</t>
+  </si>
+  <si>
+    <t>COSCO SHIPPING LINES</t>
+  </si>
+  <si>
+    <t>T5</t>
+  </si>
+  <si>
+    <t>Chinook</t>
+  </si>
+  <si>
+    <t>EXPRESS ROME</t>
+  </si>
+  <si>
+    <t>UK640R</t>
+  </si>
+  <si>
+    <t>MSC</t>
+  </si>
+  <si>
+    <t>EB1</t>
+  </si>
+  <si>
+    <t>Ad Hoc</t>
+  </si>
+  <si>
+    <t>THEMISA</t>
+  </si>
+  <si>
+    <t>ED615</t>
+  </si>
+  <si>
+    <t>Wallenius</t>
+  </si>
+  <si>
+    <t>Car Carrier</t>
+  </si>
+  <si>
+    <t>Not available</t>
+  </si>
+  <si>
+    <t>SALVIA ACE</t>
+  </si>
+  <si>
+    <t>177A</t>
+  </si>
+  <si>
+    <t>ONE</t>
+  </si>
+  <si>
+    <t>SM QINGDAO</t>
+  </si>
+  <si>
+    <t>2607E/2607W</t>
+  </si>
+  <si>
+    <t>SM Line</t>
+  </si>
+  <si>
+    <t>SSA Marine</t>
+  </si>
+  <si>
+    <t>FP2</t>
+  </si>
+  <si>
+    <t>ONE OWL</t>
+  </si>
+  <si>
+    <t>MODERN LINK</t>
+  </si>
+  <si>
+    <t>Hyundai Glovis</t>
+  </si>
+  <si>
+    <t>PCT</t>
+  </si>
+  <si>
+    <t>TPN</t>
+  </si>
+  <si>
+    <t>EVER ELITE</t>
+  </si>
+  <si>
+    <t>186W</t>
+  </si>
+  <si>
+    <t>Evergreen</t>
+  </si>
+  <si>
+    <t>BEN LINES</t>
+  </si>
+  <si>
+    <t>WUT</t>
+  </si>
+  <si>
+    <t>PN1</t>
+  </si>
+  <si>
+    <t>YM COSMOS</t>
+  </si>
+  <si>
+    <t>PN12639W</t>
+  </si>
+  <si>
+    <t>Yang Ming</t>
+  </si>
+  <si>
+    <t>Inchcape</t>
+  </si>
+  <si>
+    <t>MSC DENISSE X</t>
+  </si>
+  <si>
+    <t>UK641R</t>
+  </si>
+  <si>
+    <t>T7</t>
+  </si>
+  <si>
+    <t>THEMIS LEADER</t>
+  </si>
+  <si>
+    <t>ARC ENDEAVOR</t>
+  </si>
+  <si>
+    <t>A6180</t>
+  </si>
+  <si>
+    <t>Ports America Group/Pct</t>
+  </si>
+  <si>
+    <t>WST</t>
+  </si>
+  <si>
+    <t>Matson - AK</t>
+  </si>
+  <si>
+    <t>MATSON ANCHORAGE</t>
+  </si>
+  <si>
+    <t>643S</t>
+  </si>
+  <si>
+    <t>Matson</t>
+  </si>
+  <si>
+    <t>TOTE</t>
+  </si>
+  <si>
+    <t>Tote - AK1</t>
+  </si>
+  <si>
+    <t>MIDNIGHT SUN</t>
+  </si>
+  <si>
+    <t>Tote</t>
+  </si>
+  <si>
+    <t>Tote Maritime Alaska Inc</t>
+  </si>
+  <si>
+    <t>Multipurpose</t>
+  </si>
+  <si>
+    <t>VIENNA EXPRESS</t>
+  </si>
+  <si>
+    <t>638E/641W</t>
+  </si>
+  <si>
+    <t>Hapag-Lloyd</t>
+  </si>
+  <si>
+    <t>KW664</t>
+  </si>
+  <si>
+    <t>EVER MACH</t>
+  </si>
+  <si>
+    <t>018W</t>
+  </si>
+  <si>
+    <t>BEN LINE</t>
+  </si>
+  <si>
+    <t>CLX</t>
+  </si>
+  <si>
+    <t>MSC FLORA</t>
+  </si>
+  <si>
+    <t>MC636A</t>
+  </si>
+  <si>
+    <t>ARC INDEPENDENCE</t>
+  </si>
+  <si>
+    <t>ARC</t>
+  </si>
+  <si>
+    <t>EB Service 1</t>
+  </si>
+  <si>
+    <t>WESTWOOD RAINIER</t>
+  </si>
+  <si>
+    <t>159E</t>
+  </si>
+  <si>
+    <t>Swire</t>
+  </si>
+  <si>
+    <t>R.J. PFEIFFER</t>
+  </si>
+  <si>
+    <t>CARNATION ACE</t>
+  </si>
+  <si>
+    <t>107A</t>
+  </si>
+  <si>
     <t>PNW1</t>
   </si>
   <si>
-    <t>OOCL NEW YORK</t>
-  </si>
-  <si>
-    <t>122E/122W</t>
+    <t>OOCL SAN FRANCISCO</t>
+  </si>
+  <si>
+    <t>199E/199W</t>
   </si>
   <si>
     <t>OOCL</t>
   </si>
   <si>
-    <t>Inchcape</t>
-  </si>
-  <si>
-    <t>SSA Marine</t>
-  </si>
-  <si>
-    <t>Container</t>
-  </si>
-  <si>
-    <t>In transit</t>
-  </si>
-  <si>
-    <t>Tacoma</t>
-  </si>
-  <si>
-    <t>Husky</t>
-  </si>
-  <si>
-    <t>WC4/TP5</t>
-  </si>
-  <si>
-    <t>MAERSK TORINO</t>
-  </si>
-  <si>
-    <t>639E/642W</t>
-  </si>
-  <si>
-    <t>Maersk</t>
-  </si>
-  <si>
-    <t>Norton Lilly International</t>
-  </si>
-  <si>
-    <t>CPNW</t>
-  </si>
-  <si>
-    <t>CMA CGM ALMAVIVA</t>
-  </si>
-  <si>
-    <t>CPN02/CPN03</t>
-  </si>
-  <si>
-    <t>CMA CGM</t>
-  </si>
-  <si>
-    <t>CPV</t>
-  </si>
-  <si>
-    <t>XIN YING KOU</t>
-  </si>
-  <si>
-    <t>269N/269S</t>
-  </si>
-  <si>
-    <t>COSCO</t>
-  </si>
-  <si>
-    <t>COSCO SHIPPING LINES</t>
-  </si>
-  <si>
-    <t>T5</t>
-  </si>
-  <si>
-    <t>Chinook</t>
-  </si>
-  <si>
-    <t>EXPRESS ROME</t>
-  </si>
-  <si>
-    <t>UK640R</t>
-  </si>
-  <si>
-    <t>MSC</t>
-  </si>
-  <si>
-    <t>EB1</t>
-  </si>
-  <si>
-    <t>Ad Hoc</t>
-  </si>
-  <si>
-    <t>THEMISA</t>
-  </si>
-  <si>
-    <t>ED615</t>
-  </si>
-  <si>
-    <t>Wallenius</t>
-  </si>
-  <si>
-    <t>Car Carrier</t>
-  </si>
-  <si>
-    <t>Not available</t>
-  </si>
-  <si>
-    <t>SALVIA ACE</t>
-  </si>
-  <si>
-    <t>177A</t>
-  </si>
-  <si>
-    <t>ONE</t>
-  </si>
-  <si>
-    <t>FP2</t>
-  </si>
-  <si>
-    <t>ONE OWL</t>
-  </si>
-  <si>
-    <t>SM QINGDAO</t>
-  </si>
-  <si>
-    <t>2607E/2607W</t>
-  </si>
-  <si>
-    <t>SM Line</t>
-  </si>
-  <si>
-    <t>MODERN LINK</t>
-  </si>
-  <si>
-    <t>Hyundai Glovis</t>
-  </si>
-  <si>
-    <t>PCT</t>
-  </si>
-  <si>
-    <t>TPN</t>
-  </si>
-  <si>
-    <t>EVER ELITE</t>
-  </si>
-  <si>
-    <t>186W</t>
-  </si>
-  <si>
-    <t>Evergreen</t>
-  </si>
-  <si>
-    <t>BEN LINES</t>
-  </si>
-  <si>
-    <t>WUT</t>
-  </si>
-  <si>
-    <t>PN1</t>
-  </si>
-  <si>
-    <t>YM COSMOS</t>
-  </si>
-  <si>
-    <t>PN12639W</t>
-  </si>
-  <si>
-    <t>Yang Ming</t>
-  </si>
-  <si>
-    <t>MSC DENISSE X</t>
-  </si>
-  <si>
-    <t>UK641R</t>
-  </si>
-  <si>
-    <t>ARC ENDEAVOR</t>
-  </si>
-  <si>
-    <t>A6180</t>
-  </si>
-  <si>
-    <t>Ports America Group/Pct</t>
-  </si>
-  <si>
-    <t>T7</t>
-  </si>
-  <si>
-    <t>THEMIS LEADER</t>
-  </si>
-  <si>
-    <t>WST</t>
-  </si>
-  <si>
-    <t>Matson - AK</t>
-  </si>
-  <si>
-    <t>MATSON ANCHORAGE</t>
-  </si>
-  <si>
-    <t>643S</t>
-  </si>
-  <si>
-    <t>Matson</t>
-  </si>
-  <si>
-    <t>VIENNA EXPRESS</t>
-  </si>
-  <si>
-    <t>638E/641W</t>
-  </si>
-  <si>
-    <t>Hapag-Lloyd</t>
-  </si>
-  <si>
-    <t>TOTE</t>
-  </si>
-  <si>
-    <t>Tote - AK1</t>
-  </si>
-  <si>
-    <t>MIDNIGHT SUN</t>
-  </si>
-  <si>
-    <t>Tote</t>
-  </si>
-  <si>
-    <t>Tote Maritime Alaska Inc</t>
-  </si>
-  <si>
-    <t>Multipurpose</t>
-  </si>
-  <si>
-    <t>KW664</t>
-  </si>
-  <si>
-    <t>EVER MACH</t>
-  </si>
-  <si>
-    <t>018W</t>
-  </si>
-  <si>
-    <t>BEN LINE</t>
-  </si>
-  <si>
-    <t>CLX</t>
-  </si>
-  <si>
-    <t>MSC FLORA</t>
-  </si>
-  <si>
-    <t>MC636A</t>
-  </si>
-  <si>
-    <t>ARC INDEPENDENCE</t>
-  </si>
-  <si>
-    <t>ARC</t>
-  </si>
-  <si>
-    <t>EB Service 1</t>
-  </si>
-  <si>
-    <t>WESTWOOD RAINIER</t>
-  </si>
-  <si>
-    <t>159E</t>
-  </si>
-  <si>
-    <t>Swire</t>
-  </si>
-  <si>
-    <t>R.J. PFEIFFER</t>
-  </si>
-  <si>
-    <t>CARNATION ACE</t>
-  </si>
-  <si>
-    <t>107A</t>
-  </si>
-  <si>
-    <t>OOCL SAN FRANCISCO</t>
-  </si>
-  <si>
-    <t>199E/199W</t>
-  </si>
-  <si>
     <t>Matson - HI2</t>
   </si>
   <si>
@@ -386,7 +380,7 @@
     <t>NORTH STAR</t>
   </si>
   <si>
-    <t>Waiting 3.2 days</t>
+    <t>Waiting 3.3 days</t>
   </si>
   <si>
     <t>RJ PFEIFFER</t>
@@ -395,6 +389,12 @@
     <t>POLARIS MILA</t>
   </si>
   <si>
+    <t>ARC HONOR</t>
+  </si>
+  <si>
+    <t>ED616</t>
+  </si>
+  <si>
     <t>LIBERTY PEACE</t>
   </si>
   <si>
@@ -407,12 +407,6 @@
     <t>Pacific Terminals</t>
   </si>
   <si>
-    <t>ARC HONOR</t>
-  </si>
-  <si>
-    <t>ED616</t>
-  </si>
-  <si>
     <t>SM PORTLAND</t>
   </si>
   <si>
@@ -515,16 +509,22 @@
     <t>OYNT0002E</t>
   </si>
   <si>
+    <t>ONE DURBAN</t>
+  </si>
+  <si>
+    <t>NBBT0001E</t>
+  </si>
+  <si>
     <t>MSC SOLA</t>
   </si>
   <si>
     <t>UK643R</t>
   </si>
   <si>
-    <t>ONE DURBAN</t>
-  </si>
-  <si>
-    <t>NBBT0001E</t>
+    <t>LAVENDER ACE</t>
+  </si>
+  <si>
+    <t>123A</t>
   </si>
   <si>
     <t>MORNING LUCY</t>
@@ -533,12 +533,6 @@
     <t>KW665</t>
   </si>
   <si>
-    <t>LAVENDER ACE</t>
-  </si>
-  <si>
-    <t>123A</t>
-  </si>
-  <si>
     <t>MANULANI</t>
   </si>
   <si>
@@ -608,6 +602,9 @@
     <t>UK640A</t>
   </si>
   <si>
+    <t>GLOVIS LEGEND</t>
+  </si>
+  <si>
     <t>TONGALA</t>
   </si>
   <si>
@@ -618,9 +615,6 @@
   </si>
   <si>
     <t>GLOVIS TREASURE</t>
-  </si>
-  <si>
-    <t>GLOVIS LEGEND</t>
   </si>
   <si>
     <t>MSC SABRINA</t>
@@ -801,10 +795,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L131" totalsRowShown="0">
-  <autoFilter ref="A1:L131" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L131">
-    <sortCondition ref="J2:J131"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}" name="Table1" displayName="Table1" ref="A1:L126" totalsRowShown="0">
+  <autoFilter ref="A1:L126" xr:uid="{3550F4AE-23F8-4167-8A9B-24FFB9156E08}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L126">
+    <sortCondition ref="J2:J126"/>
   </sortState>
   <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{3ED8A004-BAC7-4959-9663-633E38656002}" name="Harbor"/>
@@ -1141,7 +1135,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9E2A47A-528B-46DE-AE1C-82EC550E6AFE}">
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="10.7109375" customWidth="1"/>
@@ -1215,20 +1209,17 @@
       <c r="G2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K2" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:12">
@@ -1253,160 +1244,157 @@
       <c r="G3" t="s">
         <v>18</v>
       </c>
-      <c r="H3" t="s">
-        <v>19</v>
-      </c>
       <c r="I3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J3" s="2">
-        <v>46312.208333333336</v>
+        <v>46312.3125</v>
       </c>
       <c r="K3" s="2">
-        <v>46313.166666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>24</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F4" t="s">
         <v>26</v>
       </c>
-      <c r="F4" t="s">
-        <v>27</v>
-      </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J4" s="2">
-        <v>46312.3125</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K4" s="2">
-        <v>46314.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
-        <v>27</v>
-      </c>
       <c r="G5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J5" s="2">
-        <v>46312.3125</v>
+        <v>46312.541666666664</v>
       </c>
       <c r="K5" s="2">
-        <v>46314.75</v>
+        <v>46314.791666666664</v>
       </c>
       <c r="L5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="G6" t="s">
         <v>31</v>
       </c>
-      <c r="F6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" t="s">
-        <v>28</v>
-      </c>
       <c r="I6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J6" s="2">
-        <v>46312.541666666664</v>
+        <v>46313.208333333336</v>
       </c>
       <c r="K6" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.208333333336</v>
       </c>
       <c r="L6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="F7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G7" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J7" s="2">
-        <v>46312.541666666664</v>
+        <v>46313.25</v>
       </c>
       <c r="K7" s="2">
-        <v>46314.791666666664</v>
+        <v>46314.75</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:12">
@@ -1414,34 +1402,34 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F8" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I8" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2">
-        <v>46313.208333333336</v>
+        <v>46314.25</v>
       </c>
       <c r="K8" s="2">
-        <v>46314.208333333336</v>
+        <v>46314.75</v>
       </c>
       <c r="L8" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:12">
@@ -1449,139 +1437,139 @@
         <v>12</v>
       </c>
       <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
         <v>38</v>
       </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
+        <v>46</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" t="s">
         <v>42</v>
       </c>
-      <c r="G9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" t="s">
-        <v>20</v>
-      </c>
       <c r="J9" s="2">
-        <v>46313.25</v>
+        <v>46314.25</v>
       </c>
       <c r="K9" s="2">
         <v>46314.75</v>
       </c>
       <c r="L9" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:12">
       <c r="A10" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" t="s">
         <v>22</v>
       </c>
-      <c r="B10" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G10" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="H10" t="s">
+        <v>50</v>
       </c>
       <c r="I10" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J10" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K10" s="2">
-        <v>46314.75</v>
+        <v>46315.166666666664</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="E11" s="1">
+        <v>34</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="G11" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I11" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J11" s="2">
-        <v>46314.25</v>
+        <v>46314.625</v>
       </c>
       <c r="K11" s="2">
-        <v>46314.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L11" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
         <v>53</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" s="1">
+        <v>2</v>
+      </c>
+      <c r="F12" t="s">
         <v>54</v>
       </c>
-      <c r="E12" s="1">
-        <v>34</v>
-      </c>
-      <c r="F12" t="s">
-        <v>52</v>
-      </c>
       <c r="G12" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I12" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J12" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K12" s="2">
-        <v>46318.166666666664</v>
+        <v>46315.75</v>
       </c>
       <c r="L12" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -1589,139 +1577,139 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>55</v>
+      </c>
+      <c r="C13" t="s">
+        <v>56</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G13" t="s">
-        <v>28</v>
-      </c>
-      <c r="H13" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
       <c r="I13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J13" s="2">
-        <v>46314.625</v>
+        <v>46315.208333333336</v>
       </c>
       <c r="K13" s="2">
-        <v>46315.166666666664</v>
+        <v>46317.166666666664</v>
       </c>
       <c r="L13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" s="1">
-        <v>2</v>
+        <v>63</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="F14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G14" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I14" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J14" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K14" s="2">
-        <v>46315.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="G15" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="I15" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J15" s="2">
-        <v>46315.208333333336</v>
+        <v>46315.666666666664</v>
       </c>
       <c r="K15" s="2">
-        <v>46317.166666666664</v>
+        <v>46317.75</v>
       </c>
       <c r="L15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:12">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>70</v>
+      </c>
+      <c r="E16" s="1">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" t="s">
         <v>66</v>
       </c>
-      <c r="C16" t="s">
-        <v>67</v>
-      </c>
-      <c r="D16" t="s">
-        <v>68</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="F16" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" t="s">
-        <v>18</v>
-      </c>
       <c r="I16" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J16" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K16" s="2">
-        <v>46317.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L16" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:12">
@@ -1729,10 +1717,10 @@
         <v>12</v>
       </c>
       <c r="B17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C17" t="s">
         <v>38</v>
-      </c>
-      <c r="C17" t="s">
-        <v>39</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
@@ -1741,515 +1729,524 @@
         <v>72</v>
       </c>
       <c r="F17" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" t="s">
+        <v>18</v>
+      </c>
+      <c r="H17" t="s">
+        <v>73</v>
+      </c>
+      <c r="I17" t="s">
         <v>42</v>
       </c>
-      <c r="G17" t="s">
-        <v>28</v>
-      </c>
-      <c r="I17" t="s">
-        <v>20</v>
-      </c>
       <c r="J17" s="2">
-        <v>46315.666666666664</v>
+        <v>46316.25</v>
       </c>
       <c r="K17" s="2">
-        <v>46317.75</v>
+        <v>46316.75</v>
       </c>
       <c r="L17" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B18" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="C18" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D18" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="H18" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="I18" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J18" s="2">
-        <v>46316.25</v>
+        <v>46316.291666666664</v>
       </c>
       <c r="K18" s="2">
-        <v>46316.75</v>
+        <v>46316.916666666664</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C19" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D19" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E19" s="1">
-        <v>63</v>
+        <v>26169</v>
       </c>
       <c r="F19" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G19" t="s">
-        <v>18</v>
+        <v>83</v>
+      </c>
+      <c r="H19" t="s">
+        <v>83</v>
       </c>
       <c r="I19" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="J19" s="2">
-        <v>46316.25</v>
+        <v>46316.625</v>
       </c>
       <c r="K19" s="2">
-        <v>46316.75</v>
+        <v>46317.041666666664</v>
       </c>
       <c r="L19" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:12">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="C20" t="s">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G20" t="s">
-        <v>82</v>
-      </c>
-      <c r="H20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J20" s="2">
-        <v>46316.291666666664</v>
+        <v>46316.625</v>
       </c>
       <c r="K20" s="2">
-        <v>46316.916666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L20" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C21" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="G21" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="H21" t="s">
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J21" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K21" s="2">
-        <v>46319.75</v>
+        <v>46317.75</v>
       </c>
       <c r="L21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:12">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="D22" t="s">
-        <v>88</v>
-      </c>
-      <c r="E22" s="1">
-        <v>26169</v>
+        <v>89</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>90</v>
       </c>
       <c r="F22" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>90</v>
-      </c>
-      <c r="H22" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I22" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="J22" s="2">
-        <v>46316.625</v>
+        <v>46317.208333333336</v>
       </c>
       <c r="K22" s="2">
-        <v>46317.041666666664</v>
+        <v>46318.708333333336</v>
       </c>
       <c r="L22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23" spans="1:12">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="D23" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="F23" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J23" s="2">
-        <v>46316.625</v>
+        <v>46317.291666666664</v>
       </c>
       <c r="K23" s="2">
-        <v>46319.75</v>
+        <v>46318.166666666664</v>
       </c>
       <c r="L23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:12">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B24" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="C24" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>92</v>
+        <v>95</v>
+      </c>
+      <c r="E24" s="1">
+        <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>47</v>
+        <v>96</v>
       </c>
       <c r="G24" t="s">
-        <v>28</v>
-      </c>
-      <c r="H24" t="s">
-        <v>75</v>
+        <v>18</v>
       </c>
       <c r="I24" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J24" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K24" s="2">
-        <v>46317.75</v>
+        <v>46320.75</v>
       </c>
       <c r="L24" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>38</v>
       </c>
       <c r="D25" t="s">
-        <v>93</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="E25" s="1">
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="G25" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="I25" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J25" s="2">
-        <v>46317.208333333336</v>
+        <v>46317.541666666664</v>
       </c>
       <c r="K25" s="2">
-        <v>46318.708333333336</v>
+        <v>46320.75</v>
       </c>
       <c r="L25" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F26" t="s">
-        <v>42</v>
+        <v>100</v>
       </c>
       <c r="I26" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J26" s="2">
-        <v>46317.291666666664</v>
+        <v>46317.927777777775</v>
       </c>
       <c r="K26" s="2">
-        <v>46318.166666666664</v>
+        <v>46318.969444444447</v>
       </c>
       <c r="L26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27" spans="1:12">
       <c r="A27" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D27" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s">
-        <v>28</v>
+        <v>78</v>
+      </c>
+      <c r="H27" t="s">
+        <v>50</v>
       </c>
       <c r="I27" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J27" s="2">
-        <v>46317.541666666664</v>
+        <v>46318.104166666664</v>
       </c>
       <c r="K27" s="2">
-        <v>46320.75</v>
+        <v>46318.916666666664</v>
       </c>
       <c r="L27" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
+        <v>102</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="F28" t="s">
-        <v>100</v>
+        <v>46</v>
       </c>
       <c r="G28" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I28" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J28" s="2">
-        <v>46317.541666666664</v>
+        <v>46318.25</v>
       </c>
       <c r="K28" s="2">
-        <v>46320.75</v>
+        <v>46318.75</v>
       </c>
       <c r="L28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D29" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F29" t="s">
-        <v>104</v>
+        <v>107</v>
+      </c>
+      <c r="G29" t="s">
+        <v>66</v>
+      </c>
+      <c r="H29" t="s">
+        <v>50</v>
       </c>
       <c r="I29" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J29" s="2">
-        <v>46317.927777777775</v>
+        <v>46318.25</v>
       </c>
       <c r="K29" s="2">
-        <v>46318.969444444447</v>
+        <v>46319.166666666664</v>
       </c>
       <c r="L29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
+        <v>74</v>
+      </c>
+      <c r="C30" t="s">
+        <v>108</v>
+      </c>
+      <c r="D30" t="s">
+        <v>109</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F30" t="s">
         <v>78</v>
       </c>
-      <c r="C30" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" t="s">
-        <v>105</v>
-      </c>
-      <c r="F30" t="s">
-        <v>82</v>
-      </c>
       <c r="G30" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H30" t="s">
-        <v>19</v>
+        <v>50</v>
       </c>
       <c r="I30" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J30" s="2">
-        <v>46318.104166666664</v>
+        <v>46318.291666666664</v>
       </c>
       <c r="K30" s="2">
-        <v>46318.916666666664</v>
+        <v>46319.125</v>
       </c>
       <c r="L30" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C31" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="D31" t="s">
-        <v>106</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>107</v>
+        <v>112</v>
+      </c>
+      <c r="E31" s="1">
+        <v>26168</v>
       </c>
       <c r="F31" t="s">
-        <v>52</v>
+        <v>82</v>
       </c>
       <c r="G31" t="s">
-        <v>28</v>
+        <v>83</v>
+      </c>
+      <c r="H31" t="s">
+        <v>83</v>
       </c>
       <c r="I31" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="J31" s="2">
-        <v>46318.25</v>
+        <v>46318.625</v>
       </c>
       <c r="K31" s="2">
-        <v>46318.75</v>
+        <v>46319.041666666664</v>
       </c>
       <c r="L31" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:12">
@@ -2257,533 +2254,518 @@
         <v>12</v>
       </c>
       <c r="B32" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C32" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D32" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F32" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" t="s">
-        <v>18</v>
-      </c>
-      <c r="H32" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="I32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J32" s="2">
-        <v>46318.25</v>
+        <v>46318.704861111109</v>
       </c>
       <c r="K32" s="2">
-        <v>46319.166666666664</v>
+        <v>46319.204861111109</v>
       </c>
       <c r="L32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:12">
       <c r="A33" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="C33" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>112</v>
+        <v>115</v>
+      </c>
+      <c r="E33" s="1">
+        <v>4</v>
       </c>
       <c r="F33" t="s">
-        <v>82</v>
+        <v>54</v>
       </c>
       <c r="G33" t="s">
-        <v>82</v>
-      </c>
-      <c r="H33" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I33" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J33" s="2">
-        <v>46318.291666666664</v>
+        <v>46319.208333333336</v>
       </c>
       <c r="K33" s="2">
-        <v>46319.125</v>
+        <v>46319.75</v>
       </c>
       <c r="L33" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B34" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
       <c r="C34" t="s">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="D34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" s="1">
-        <v>26168</v>
+        <v>116</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="F34" t="s">
-        <v>89</v>
+        <v>41</v>
       </c>
       <c r="G34" t="s">
-        <v>90</v>
-      </c>
-      <c r="H34" t="s">
-        <v>90</v>
+        <v>18</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="J34" s="2">
-        <v>46318.625</v>
+        <v>46319.25</v>
       </c>
       <c r="K34" s="2">
-        <v>46319.041666666664</v>
+        <v>46319.75</v>
       </c>
       <c r="L34" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
     </row>
     <row r="35" spans="1:12">
       <c r="A35" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B35" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="D35" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F35" t="s">
-        <v>82</v>
+        <v>120</v>
+      </c>
+      <c r="G35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" t="s">
+        <v>121</v>
       </c>
       <c r="I35" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J35" s="2">
-        <v>46318.704861111109</v>
+        <v>46319.25</v>
       </c>
       <c r="K35" s="2">
-        <v>46319.204861111109</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L35" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:12">
       <c r="A36" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B36" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" t="s">
+        <v>38</v>
+      </c>
+      <c r="D36" t="s">
+        <v>118</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F36" t="s">
+        <v>120</v>
+      </c>
+      <c r="G36" t="s">
+        <v>66</v>
+      </c>
+      <c r="H36" t="s">
+        <v>121</v>
+      </c>
+      <c r="I36" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36" s="2">
+        <v>46319.25</v>
+      </c>
+      <c r="K36" s="2">
+        <v>46320.166666666664</v>
+      </c>
+      <c r="L36" t="s">
         <v>43</v>
-      </c>
-      <c r="C36" t="s">
-        <v>44</v>
-      </c>
-      <c r="D36" t="s">
-        <v>117</v>
-      </c>
-      <c r="E36" s="1">
-        <v>4</v>
-      </c>
-      <c r="F36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G36" t="s">
-        <v>28</v>
-      </c>
-      <c r="I36" t="s">
-        <v>48</v>
-      </c>
-      <c r="J36" s="2">
-        <v>46319.208333333336</v>
-      </c>
-      <c r="K36" s="2">
-        <v>46319.75</v>
-      </c>
-      <c r="L36" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="37" spans="1:12">
       <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
         <v>22</v>
       </c>
-      <c r="B37" t="s">
-        <v>43</v>
-      </c>
-      <c r="C37" t="s">
-        <v>44</v>
-      </c>
       <c r="D37" t="s">
-        <v>117</v>
-      </c>
-      <c r="E37" s="1">
-        <v>4</v>
+        <v>122</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="F37" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G37" t="s">
-        <v>28</v>
+        <v>18</v>
+      </c>
+      <c r="H37" t="s">
+        <v>50</v>
       </c>
       <c r="I37" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J37" s="2">
-        <v>46319.208333333336</v>
+        <v>46319.625</v>
       </c>
       <c r="K37" s="2">
-        <v>46319.75</v>
+        <v>46320.166666666664</v>
       </c>
       <c r="L37" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:12">
       <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
         <v>22</v>
       </c>
-      <c r="B38" t="s">
-        <v>76</v>
-      </c>
-      <c r="C38" t="s">
-        <v>44</v>
-      </c>
       <c r="D38" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="F38" t="s">
-        <v>120</v>
+        <v>49</v>
       </c>
       <c r="G38" t="s">
         <v>18</v>
       </c>
       <c r="H38" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="I38" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J38" s="2">
-        <v>46319.25</v>
+        <v>46319.625</v>
       </c>
       <c r="K38" s="2">
         <v>46320.166666666664</v>
       </c>
       <c r="L38" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:12">
       <c r="A39" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B39" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D39" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="F39" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="G39" t="s">
-        <v>18</v>
-      </c>
-      <c r="H39" t="s">
-        <v>121</v>
+        <v>66</v>
       </c>
       <c r="I39" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J39" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K39" s="2">
-        <v>46320.166666666664</v>
+        <v>46321.75</v>
       </c>
       <c r="L39" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B40" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D40" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F40" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="G40" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="I40" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J40" s="2">
-        <v>46319.25</v>
+        <v>46319.666666666664</v>
       </c>
       <c r="K40" s="2">
-        <v>46319.75</v>
+        <v>46321.75</v>
       </c>
       <c r="L40" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41" spans="1:12">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B41" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D41" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="F41" t="s">
-        <v>47</v>
-      </c>
-      <c r="G41" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I41" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J41" s="2">
-        <v>46319.25</v>
+        <v>46320</v>
       </c>
       <c r="K41" s="2">
-        <v>46319.75</v>
+        <v>46322</v>
       </c>
       <c r="L41" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B42" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="C42" t="s">
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>56</v>
+        <v>129</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
-      </c>
-      <c r="G42" t="s">
-        <v>28</v>
-      </c>
-      <c r="H42" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="I42" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J42" s="2">
-        <v>46319.625</v>
+        <v>46320.21875</v>
       </c>
       <c r="K42" s="2">
-        <v>46320.166666666664</v>
+        <v>46324.59375</v>
       </c>
       <c r="L42" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B43" t="s">
-        <v>13</v>
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>56</v>
+        <v>131</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>28</v>
-      </c>
-      <c r="H43" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="I43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J43" s="2">
-        <v>46319.625</v>
+        <v>46321.208333333336</v>
       </c>
       <c r="K43" s="2">
-        <v>46320.166666666664</v>
+        <v>46322.166666666664</v>
       </c>
       <c r="L43" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44" spans="1:12">
       <c r="A44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B44" t="s">
-        <v>66</v>
+        <v>32</v>
       </c>
       <c r="C44" t="s">
-        <v>125</v>
+        <v>33</v>
       </c>
       <c r="D44" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
-      </c>
-      <c r="G44" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J44" s="2">
-        <v>46319.666666666664</v>
+        <v>46321.21875</v>
       </c>
       <c r="K44" s="2">
-        <v>46321.75</v>
+        <v>46323.21875</v>
       </c>
       <c r="L44" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:12">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B45" t="s">
+        <v>61</v>
+      </c>
+      <c r="C45" t="s">
+        <v>62</v>
+      </c>
+      <c r="D45" t="s">
+        <v>134</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" t="s">
+        <v>65</v>
+      </c>
+      <c r="G45" t="s">
         <v>66</v>
       </c>
-      <c r="C45" t="s">
-        <v>125</v>
-      </c>
-      <c r="D45" t="s">
-        <v>126</v>
-      </c>
-      <c r="E45" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F45" t="s">
-        <v>70</v>
-      </c>
-      <c r="G45" t="s">
-        <v>18</v>
-      </c>
       <c r="I45" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J45" s="2">
-        <v>46319.666666666664</v>
+        <v>46321.25</v>
       </c>
       <c r="K45" s="2">
-        <v>46321.75</v>
+        <v>46323.166666666664</v>
       </c>
       <c r="L45" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46" spans="1:12">
       <c r="A46" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B46" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C46" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>129</v>
+        <v>136</v>
+      </c>
+      <c r="E46" s="1">
+        <v>21</v>
       </c>
       <c r="F46" t="s">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="G46" t="s">
+        <v>18</v>
       </c>
       <c r="I46" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J46" s="2">
-        <v>46320</v>
+        <v>46321.625</v>
       </c>
       <c r="K46" s="2">
-        <v>46322</v>
+        <v>46325.75</v>
       </c>
       <c r="L46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47" spans="1:12">
@@ -2791,31 +2773,34 @@
         <v>12</v>
       </c>
       <c r="B47" t="s">
-        <v>13</v>
+        <v>137</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="F47" t="s">
-        <v>32</v>
+        <v>120</v>
+      </c>
+      <c r="G47" t="s">
+        <v>66</v>
+      </c>
+      <c r="H47" t="s">
+        <v>121</v>
       </c>
       <c r="I47" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J47" s="2">
-        <v>46320.21875</v>
+        <v>46322.25</v>
       </c>
       <c r="K47" s="2">
-        <v>46324.59375</v>
+        <v>46322.75</v>
       </c>
       <c r="L47" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:12">
@@ -2826,31 +2811,31 @@
         <v>13</v>
       </c>
       <c r="C48" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="F48" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="G48" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="I48" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J48" s="2">
-        <v>46321.208333333336</v>
+        <v>46322.625</v>
       </c>
       <c r="K48" s="2">
-        <v>46322.166666666664</v>
+        <v>46325.75</v>
       </c>
       <c r="L48" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:12">
@@ -2858,337 +2843,328 @@
         <v>12</v>
       </c>
       <c r="B49" t="s">
+        <v>37</v>
+      </c>
+      <c r="C49" t="s">
         <v>38</v>
       </c>
-      <c r="C49" t="s">
-        <v>39</v>
-      </c>
       <c r="D49" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F49" t="s">
+        <v>46</v>
+      </c>
+      <c r="G49" t="s">
+        <v>18</v>
+      </c>
+      <c r="I49" t="s">
         <v>42</v>
       </c>
-      <c r="I49" t="s">
-        <v>20</v>
-      </c>
       <c r="J49" s="2">
-        <v>46321.21875</v>
+        <v>46323.25</v>
       </c>
       <c r="K49" s="2">
-        <v>46323.21875</v>
+        <v>46323.75</v>
       </c>
       <c r="L49" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50" spans="1:12">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B50" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C50" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
-      </c>
-      <c r="E50" s="1" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
-      </c>
-      <c r="G50" t="s">
-        <v>18</v>
+        <v>78</v>
       </c>
       <c r="I50" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J50" s="2">
-        <v>46321.25</v>
+        <v>46323.291666666664</v>
       </c>
       <c r="K50" s="2">
-        <v>46323.166666666664</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="L50" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51" spans="1:12">
       <c r="A51" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B51" t="s">
-        <v>23</v>
+        <v>79</v>
       </c>
       <c r="C51" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>81</v>
       </c>
       <c r="E51" s="1">
-        <v>21</v>
+        <v>26173</v>
       </c>
       <c r="F51" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="G51" t="s">
-        <v>28</v>
+        <v>83</v>
+      </c>
+      <c r="H51" t="s">
+        <v>83</v>
       </c>
       <c r="I51" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="J51" s="2">
-        <v>46321.625</v>
+        <v>46323.625</v>
       </c>
       <c r="K51" s="2">
-        <v>46325.75</v>
+        <v>46324.041666666664</v>
       </c>
       <c r="L51" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52" spans="1:12">
       <c r="A52" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B52" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C52" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D52" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="F52" t="s">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="G52" t="s">
         <v>18</v>
       </c>
-      <c r="H52" t="s">
-        <v>121</v>
-      </c>
       <c r="I52" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J52" s="2">
-        <v>46322.25</v>
+        <v>46323.791666666664</v>
       </c>
       <c r="K52" s="2">
-        <v>46322.75</v>
+        <v>46324.75</v>
       </c>
       <c r="L52" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B53" t="s">
-        <v>23</v>
-      </c>
-      <c r="C53" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="D53" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F53" t="s">
-        <v>85</v>
-      </c>
-      <c r="G53" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="I53" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J53" s="2">
-        <v>46322.625</v>
+        <v>46324</v>
       </c>
       <c r="K53" s="2">
-        <v>46325.75</v>
+        <v>46326</v>
       </c>
       <c r="L53" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="54" spans="1:12">
       <c r="A54" t="s">
+        <v>21</v>
+      </c>
+      <c r="B54" t="s">
         <v>22</v>
       </c>
-      <c r="B54" t="s">
-        <v>43</v>
-      </c>
       <c r="C54" t="s">
-        <v>44</v>
+        <v>146</v>
       </c>
       <c r="D54" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F54" t="s">
-        <v>52</v>
-      </c>
-      <c r="G54" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I54" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J54" s="2">
-        <v>46323.25</v>
+        <v>46324.647916666669</v>
       </c>
       <c r="K54" s="2">
-        <v>46323.75</v>
+        <v>46326.147916666669</v>
       </c>
       <c r="L54" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B55" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C55" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>149</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F55" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="I55" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J55" s="2">
-        <v>46323.291666666664</v>
+        <v>46325.003472222219</v>
       </c>
       <c r="K55" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.878472222219</v>
       </c>
       <c r="L55" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="56" spans="1:12">
       <c r="A56" t="s">
+        <v>21</v>
+      </c>
+      <c r="B56" t="s">
         <v>22</v>
       </c>
-      <c r="B56" t="s">
-        <v>86</v>
-      </c>
       <c r="C56" t="s">
-        <v>87</v>
+        <v>151</v>
       </c>
       <c r="D56" t="s">
-        <v>88</v>
-      </c>
-      <c r="E56" s="1">
-        <v>26173</v>
+        <v>152</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="F56" t="s">
-        <v>89</v>
-      </c>
-      <c r="G56" t="s">
-        <v>90</v>
-      </c>
-      <c r="H56" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I56" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="J56" s="2">
-        <v>46323.625</v>
+        <v>46325.056944444441</v>
       </c>
       <c r="K56" s="2">
-        <v>46324.041666666664</v>
+        <v>46326.098611111112</v>
       </c>
       <c r="L56" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:12">
       <c r="A57" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="C57" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
-      </c>
-      <c r="E57" s="1" t="s">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="F57" t="s">
-        <v>52</v>
-      </c>
-      <c r="G57" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="I57" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J57" s="2">
-        <v>46323.791666666664</v>
+        <v>46325.333333333336</v>
       </c>
       <c r="K57" s="2">
-        <v>46324.75</v>
+        <v>46325.833333333336</v>
       </c>
       <c r="L57" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B58" t="s">
-        <v>60</v>
+        <v>79</v>
+      </c>
+      <c r="C58" t="s">
+        <v>111</v>
       </c>
       <c r="D58" t="s">
-        <v>146</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>147</v>
+        <v>112</v>
+      </c>
+      <c r="E58" s="1">
+        <v>26172</v>
       </c>
       <c r="F58" t="s">
-        <v>64</v>
+        <v>82</v>
+      </c>
+      <c r="G58" t="s">
+        <v>83</v>
+      </c>
+      <c r="H58" t="s">
+        <v>83</v>
       </c>
       <c r="I58" t="s">
-        <v>20</v>
+        <v>84</v>
       </c>
       <c r="J58" s="2">
-        <v>46324</v>
+        <v>46325.625</v>
       </c>
       <c r="K58" s="2">
-        <v>46326</v>
+        <v>46326.041666666664</v>
       </c>
       <c r="L58" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="59" spans="1:12">
@@ -3199,28 +3175,28 @@
         <v>13</v>
       </c>
       <c r="C59" t="s">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="D59" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="F59" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J59" s="2">
-        <v>46324.647916666669</v>
+        <v>46325.625</v>
       </c>
       <c r="K59" s="2">
-        <v>46326.147916666669</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L59" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60" spans="1:12">
@@ -3228,31 +3204,31 @@
         <v>12</v>
       </c>
       <c r="B60" t="s">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="D60" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F60" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I60" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J60" s="2">
-        <v>46325.003472222219</v>
+        <v>46325.625</v>
       </c>
       <c r="K60" s="2">
-        <v>46325.878472222219</v>
+        <v>46329.708333333336</v>
       </c>
       <c r="L60" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="61" spans="1:12">
@@ -3260,109 +3236,106 @@
         <v>12</v>
       </c>
       <c r="B61" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="D61" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F61" t="s">
-        <v>104</v>
+        <v>46</v>
       </c>
       <c r="I61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J61" s="2">
-        <v>46325.056944444441</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K61" s="2">
-        <v>46326.098611111112</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L61" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:12">
       <c r="A62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B62" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>158</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F62" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="I62" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J62" s="2">
-        <v>46325.333333333336</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K62" s="2">
-        <v>46325.833333333336</v>
+        <v>46328.125</v>
       </c>
       <c r="L62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="63" spans="1:12">
       <c r="A63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B63" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="C63" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="D63" t="s">
-        <v>114</v>
-      </c>
-      <c r="E63" s="1">
-        <v>26172</v>
+        <v>158</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>159</v>
       </c>
       <c r="F63" t="s">
-        <v>89</v>
-      </c>
-      <c r="G63" t="s">
-        <v>90</v>
-      </c>
-      <c r="H63" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="I63" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="J63" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K63" s="2">
-        <v>46326.041666666664</v>
+        <v>46328.125</v>
       </c>
       <c r="L63" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:12">
       <c r="A64" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B64" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>53</v>
+        <v>123</v>
       </c>
       <c r="D64" t="s">
         <v>156</v>
@@ -3371,51 +3344,54 @@
         <v>157</v>
       </c>
       <c r="F64" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I64" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J64" s="2">
-        <v>46325.625</v>
+        <v>46326.166666666664</v>
       </c>
       <c r="K64" s="2">
-        <v>46329.708333333336</v>
+        <v>46328.916666666664</v>
       </c>
       <c r="L64" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="C65" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F65" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="G65" t="s">
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J65" s="2">
-        <v>46325.625</v>
+        <v>46326.25</v>
       </c>
       <c r="K65" s="2">
-        <v>46329.708333333336</v>
+        <v>46326.75</v>
       </c>
       <c r="L65" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="66" spans="1:12">
@@ -3423,63 +3399,63 @@
         <v>12</v>
       </c>
       <c r="B66" t="s">
+        <v>37</v>
+      </c>
+      <c r="C66" t="s">
         <v>38</v>
       </c>
-      <c r="C66" t="s">
-        <v>39</v>
-      </c>
       <c r="D66" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F66" t="s">
+        <v>41</v>
+      </c>
+      <c r="G66" t="s">
+        <v>18</v>
+      </c>
+      <c r="I66" t="s">
         <v>42</v>
       </c>
-      <c r="I66" t="s">
-        <v>20</v>
-      </c>
       <c r="J66" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.25</v>
       </c>
       <c r="K66" s="2">
-        <v>46328.125</v>
+        <v>46326.75</v>
       </c>
       <c r="L66" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="67" spans="1:12">
       <c r="A67" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B67" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C67" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="D67" t="s">
-        <v>160</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F67" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I67" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J67" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.416666666664</v>
       </c>
       <c r="K67" s="2">
-        <v>46328.916666666664</v>
+        <v>46326.75</v>
       </c>
       <c r="L67" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3487,299 +3463,290 @@
         <v>12</v>
       </c>
       <c r="B68" t="s">
+        <v>137</v>
+      </c>
+      <c r="C68" t="s">
         <v>38</v>
       </c>
-      <c r="C68" t="s">
-        <v>39</v>
-      </c>
       <c r="D68" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="F68" t="s">
+        <v>41</v>
+      </c>
+      <c r="G68" t="s">
+        <v>18</v>
+      </c>
+      <c r="I68" t="s">
         <v>42</v>
       </c>
-      <c r="I68" t="s">
-        <v>20</v>
-      </c>
       <c r="J68" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K68" s="2">
-        <v>46328.125</v>
+        <v>46327.75</v>
       </c>
       <c r="L68" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:12">
       <c r="A69" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="C69" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="D69" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F69" t="s">
-        <v>52</v>
+        <v>41</v>
+      </c>
+      <c r="G69" t="s">
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J69" s="2">
-        <v>46326.166666666664</v>
+        <v>46326.791666666664</v>
       </c>
       <c r="K69" s="2">
-        <v>46328.916666666664</v>
+        <v>46327.75</v>
       </c>
       <c r="L69" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="70" spans="1:12">
       <c r="A70" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B70" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D70" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="F70" t="s">
-        <v>47</v>
-      </c>
-      <c r="G70" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="I70" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J70" s="2">
-        <v>46326.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K70" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L70" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B71" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="C71" t="s">
-        <v>44</v>
+        <v>123</v>
       </c>
       <c r="D71" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F71" t="s">
-        <v>52</v>
-      </c>
-      <c r="G71" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="I71" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J71" s="2">
-        <v>46326.25</v>
+        <v>46326.833333333336</v>
       </c>
       <c r="K71" s="2">
-        <v>46326.75</v>
+        <v>46329.583333333336</v>
       </c>
       <c r="L71" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="72" spans="1:12">
       <c r="A72" t="s">
+        <v>21</v>
+      </c>
+      <c r="B72" t="s">
         <v>22</v>
       </c>
-      <c r="B72" t="s">
-        <v>139</v>
-      </c>
       <c r="C72" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D72" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F72" t="s">
-        <v>52</v>
-      </c>
-      <c r="G72" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="I72" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J72" s="2">
-        <v>46326.25</v>
+        <v>46327.166666666664</v>
       </c>
       <c r="K72" s="2">
-        <v>46326.75</v>
+        <v>46328.541666666664</v>
       </c>
       <c r="L72" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="73" spans="1:12">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" t="s">
+        <v>38</v>
+      </c>
+      <c r="D73" t="s">
+        <v>170</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73" t="s">
+        <v>46</v>
+      </c>
+      <c r="G73" t="s">
+        <v>18</v>
+      </c>
+      <c r="I73" t="s">
+        <v>42</v>
+      </c>
+      <c r="J73" s="2">
+        <v>46327.25</v>
+      </c>
+      <c r="K73" s="2">
+        <v>46327.708333333336</v>
+      </c>
+      <c r="L73" t="s">
         <v>43</v>
-      </c>
-      <c r="C73" t="s">
-        <v>44</v>
-      </c>
-      <c r="D73" t="s">
-        <v>162</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="F73" t="s">
-        <v>47</v>
-      </c>
-      <c r="G73" t="s">
-        <v>28</v>
-      </c>
-      <c r="I73" t="s">
-        <v>48</v>
-      </c>
-      <c r="J73" s="2">
-        <v>46326.25</v>
-      </c>
-      <c r="K73" s="2">
-        <v>46326.75</v>
-      </c>
-      <c r="L73" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="74" spans="1:12">
       <c r="A74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B74" t="s">
         <v>22</v>
       </c>
-      <c r="B74" t="s">
-        <v>78</v>
-      </c>
-      <c r="C74" t="s">
-        <v>110</v>
-      </c>
       <c r="D74" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="F74" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="I74" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J74" s="2">
-        <v>46326.416666666664</v>
+        <v>46327.708333333336</v>
       </c>
       <c r="K74" s="2">
-        <v>46326.75</v>
+        <v>46328.833333333336</v>
       </c>
       <c r="L74" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="75" spans="1:12">
       <c r="A75" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B75" t="s">
-        <v>139</v>
+        <v>61</v>
       </c>
       <c r="C75" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D75" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
-        <v>47</v>
-      </c>
-      <c r="G75" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I75" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J75" s="2">
-        <v>46326.791666666664</v>
+        <v>46327.904861111114</v>
       </c>
       <c r="K75" s="2">
-        <v>46327.75</v>
+        <v>46331.196527777778</v>
       </c>
       <c r="L75" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="76" spans="1:12">
       <c r="A76" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B76" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>125</v>
+        <v>56</v>
       </c>
       <c r="D76" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="F76" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="I76" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J76" s="2">
-        <v>46326.833333333336</v>
+        <v>46329</v>
       </c>
       <c r="K76" s="2">
-        <v>46329.583333333336</v>
+        <v>46330</v>
       </c>
       <c r="L76" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -3787,66 +3754,66 @@
         <v>12</v>
       </c>
       <c r="B77" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C77" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D77" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="F77" t="s">
-        <v>32</v>
+        <v>46</v>
+      </c>
+      <c r="G77" t="s">
+        <v>18</v>
       </c>
       <c r="I77" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J77" s="2">
-        <v>46327.166666666664</v>
+        <v>46329.25</v>
       </c>
       <c r="K77" s="2">
-        <v>46328.541666666664</v>
+        <v>46329.75</v>
       </c>
       <c r="L77" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="78" spans="1:12">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B78" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="C78" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="F78" t="s">
-        <v>52</v>
-      </c>
-      <c r="G78" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="I78" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J78" s="2">
-        <v>46327.25</v>
+        <v>46329.333333333336</v>
       </c>
       <c r="K78" s="2">
-        <v>46327.708333333336</v>
+        <v>46332.625</v>
       </c>
       <c r="L78" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:12">
@@ -3854,377 +3821,392 @@
         <v>12</v>
       </c>
       <c r="B79" t="s">
-        <v>13</v>
+        <v>137</v>
+      </c>
+      <c r="C79" t="s">
+        <v>38</v>
       </c>
       <c r="D79" t="s">
-        <v>174</v>
+        <v>177</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>178</v>
       </c>
       <c r="F79" t="s">
-        <v>57</v>
+        <v>46</v>
+      </c>
+      <c r="G79" t="s">
+        <v>18</v>
       </c>
       <c r="I79" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J79" s="2">
-        <v>46327.708333333336</v>
+        <v>46329.791666666664</v>
       </c>
       <c r="K79" s="2">
-        <v>46328.833333333336</v>
+        <v>46330.75</v>
       </c>
       <c r="L79" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="80" spans="1:12">
       <c r="A80" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B80" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="C80" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="D80" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F80" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I80" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J80" s="2">
-        <v>46327.904861111114</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K80" s="2">
-        <v>46331.196527777778</v>
+        <v>46334</v>
       </c>
       <c r="L80" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B81" t="s">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="C81" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F81" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I81" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J81" s="2">
-        <v>46329</v>
+        <v>46330.208333333336</v>
       </c>
       <c r="K81" s="2">
-        <v>46330</v>
+        <v>46334</v>
       </c>
       <c r="L81" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B82" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C82" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D82" t="s">
-        <v>179</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>180</v>
+        <v>81</v>
       </c>
       <c r="F82" t="s">
-        <v>52</v>
-      </c>
-      <c r="G82" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="J82" s="2">
-        <v>46329.25</v>
+        <v>46330.625</v>
       </c>
       <c r="K82" s="2">
-        <v>46329.75</v>
+        <v>46331.125</v>
       </c>
       <c r="L82" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="83" spans="1:12">
       <c r="A83" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C83" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D83" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F83" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I83" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J83" s="2">
-        <v>46329.333333333336</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K83" s="2">
-        <v>46332.625</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L83" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="84" spans="1:12">
       <c r="A84" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="C84" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D84" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F84" t="s">
-        <v>52</v>
-      </c>
-      <c r="G84" t="s">
-        <v>28</v>
+        <v>167</v>
       </c>
       <c r="I84" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J84" s="2">
-        <v>46329.791666666664</v>
+        <v>46330.633333333331</v>
       </c>
       <c r="K84" s="2">
-        <v>46330.75</v>
+        <v>46333.925000000003</v>
       </c>
       <c r="L84" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:12">
       <c r="A85" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B85" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="C85" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="D85" t="s">
-        <v>183</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>184</v>
+        <v>114</v>
       </c>
       <c r="F85" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I85" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J85" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.704861111109</v>
       </c>
       <c r="K85" s="2">
-        <v>46334</v>
+        <v>46331.204861111109</v>
       </c>
       <c r="L85" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:12">
       <c r="A86" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C86" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D86" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F86" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="I86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J86" s="2">
-        <v>46330.208333333336</v>
+        <v>46330.75</v>
       </c>
       <c r="K86" s="2">
-        <v>46334</v>
+        <v>46332.75</v>
       </c>
       <c r="L86" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="87" spans="1:12">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B87" t="s">
-        <v>86</v>
+        <v>137</v>
       </c>
       <c r="C87" t="s">
-        <v>87</v>
+        <v>38</v>
       </c>
       <c r="D87" t="s">
-        <v>88</v>
+        <v>187</v>
+      </c>
+      <c r="E87" s="1">
+        <v>1</v>
       </c>
       <c r="F87" t="s">
-        <v>89</v>
+        <v>54</v>
+      </c>
+      <c r="G87" t="s">
+        <v>18</v>
       </c>
       <c r="I87" t="s">
-        <v>91</v>
+        <v>42</v>
       </c>
       <c r="J87" s="2">
-        <v>46330.625</v>
+        <v>46331.25</v>
       </c>
       <c r="K87" s="2">
-        <v>46331.125</v>
+        <v>46331.75</v>
       </c>
       <c r="L87" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="88" spans="1:12">
       <c r="A88" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B88" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C88" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D88" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F88" t="s">
-        <v>169</v>
+        <v>41</v>
+      </c>
+      <c r="G88" t="s">
+        <v>18</v>
+      </c>
+      <c r="H88" t="s">
+        <v>190</v>
       </c>
       <c r="I88" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J88" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K88" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L88" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B89" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C89" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D89" t="s">
-        <v>185</v>
-      </c>
-      <c r="E89" s="1" t="s">
-        <v>186</v>
+        <v>191</v>
+      </c>
+      <c r="E89" s="1">
+        <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>169</v>
+        <v>54</v>
+      </c>
+      <c r="G89" t="s">
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J89" s="2">
-        <v>46330.633333333331</v>
+        <v>46331.25</v>
       </c>
       <c r="K89" s="2">
-        <v>46333.925000000003</v>
+        <v>46331.75</v>
       </c>
       <c r="L89" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:12">
       <c r="A90" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B90" t="s">
-        <v>78</v>
+        <v>32</v>
       </c>
       <c r="C90" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="D90" t="s">
-        <v>116</v>
+        <v>192</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="F90" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="I90" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J90" s="2">
-        <v>46330.704861111109</v>
+        <v>46331.291666666664</v>
       </c>
       <c r="K90" s="2">
-        <v>46331.204861111109</v>
+        <v>46332.166666666664</v>
       </c>
       <c r="L90" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="91" spans="1:12">
@@ -4232,139 +4214,136 @@
         <v>12</v>
       </c>
       <c r="B91" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D91" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="F91" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="I91" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J91" s="2">
-        <v>46330.75</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K91" s="2">
-        <v>46332.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L91" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:12">
       <c r="A92" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B92" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="C92" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="D92" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>190</v>
+        <v>153</v>
       </c>
       <c r="F92" t="s">
-        <v>47</v>
-      </c>
-      <c r="G92" t="s">
-        <v>28</v>
-      </c>
-      <c r="H92" t="s">
-        <v>191</v>
+        <v>167</v>
       </c>
       <c r="I92" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J92" s="2">
-        <v>46331.25</v>
+        <v>46331.496527777781</v>
       </c>
       <c r="K92" s="2">
-        <v>46331.75</v>
+        <v>46334.746527777781</v>
       </c>
       <c r="L92" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B93" t="s">
+        <v>137</v>
+      </c>
+      <c r="C93" t="s">
+        <v>38</v>
+      </c>
+      <c r="D93" t="s">
+        <v>188</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F93" t="s">
+        <v>41</v>
+      </c>
+      <c r="G93" t="s">
+        <v>18</v>
+      </c>
+      <c r="H93" t="s">
+        <v>190</v>
+      </c>
+      <c r="I93" t="s">
+        <v>42</v>
+      </c>
+      <c r="J93" s="2">
+        <v>46331.791666666664</v>
+      </c>
+      <c r="K93" s="2">
+        <v>46332.75</v>
+      </c>
+      <c r="L93" t="s">
         <v>43</v>
-      </c>
-      <c r="C93" t="s">
-        <v>44</v>
-      </c>
-      <c r="D93" t="s">
-        <v>192</v>
-      </c>
-      <c r="E93" s="1">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>59</v>
-      </c>
-      <c r="G93" t="s">
-        <v>28</v>
-      </c>
-      <c r="I93" t="s">
-        <v>48</v>
-      </c>
-      <c r="J93" s="2">
-        <v>46331.25</v>
-      </c>
-      <c r="K93" s="2">
-        <v>46331.75</v>
-      </c>
-      <c r="L93" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="94" spans="1:12">
       <c r="A94" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B94" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C94" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D94" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E94" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F94" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G94" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="I94" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J94" s="2">
-        <v>46331.25</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K94" s="2">
-        <v>46331.75</v>
+        <v>46332.75</v>
       </c>
       <c r="L94" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4372,264 +4351,246 @@
         <v>12</v>
       </c>
       <c r="B95" t="s">
+        <v>37</v>
+      </c>
+      <c r="C95" t="s">
         <v>38</v>
       </c>
-      <c r="C95" t="s">
-        <v>96</v>
-      </c>
       <c r="D95" t="s">
-        <v>194</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>195</v>
+        <v>187</v>
+      </c>
+      <c r="E95" s="1">
+        <v>1</v>
       </c>
       <c r="F95" t="s">
+        <v>54</v>
+      </c>
+      <c r="G95" t="s">
+        <v>18</v>
+      </c>
+      <c r="I95" t="s">
         <v>42</v>
       </c>
-      <c r="I95" t="s">
-        <v>20</v>
-      </c>
       <c r="J95" s="2">
-        <v>46331.291666666664</v>
+        <v>46331.791666666664</v>
       </c>
       <c r="K95" s="2">
-        <v>46332.166666666664</v>
+        <v>46332.75</v>
       </c>
       <c r="L95" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96" spans="1:12">
       <c r="A96" t="s">
+        <v>21</v>
+      </c>
+      <c r="B96" t="s">
         <v>22</v>
       </c>
-      <c r="B96" t="s">
-        <v>66</v>
-      </c>
       <c r="C96" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="D96" t="s">
+        <v>195</v>
+      </c>
+      <c r="E96" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="E96" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="F96" t="s">
-        <v>169</v>
+        <v>100</v>
       </c>
       <c r="I96" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J96" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.056250000001</v>
       </c>
       <c r="K96" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.597916666666</v>
       </c>
       <c r="L96" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="97" spans="1:12">
       <c r="A97" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B97" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C97" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="D97" t="s">
-        <v>196</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="F97" t="s">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="I97" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J97" s="2">
-        <v>46331.496527777781</v>
+        <v>46332.291666666664</v>
       </c>
       <c r="K97" s="2">
-        <v>46334.746527777781</v>
+        <v>46332.791666666664</v>
       </c>
       <c r="L97" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="98" spans="1:12">
       <c r="A98" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98" t="s">
         <v>22</v>
       </c>
-      <c r="B98" t="s">
-        <v>43</v>
-      </c>
-      <c r="C98" t="s">
-        <v>44</v>
-      </c>
       <c r="D98" t="s">
-        <v>193</v>
-      </c>
-      <c r="E98" s="1">
-        <v>1</v>
+        <v>197</v>
       </c>
       <c r="F98" t="s">
-        <v>59</v>
-      </c>
-      <c r="G98" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="I98" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J98" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.375</v>
       </c>
       <c r="K98" s="2">
-        <v>46332.75</v>
+        <v>46333.5</v>
       </c>
       <c r="L98" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B99" t="s">
-        <v>139</v>
+        <v>79</v>
       </c>
       <c r="C99" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
       <c r="D99" t="s">
-        <v>192</v>
-      </c>
-      <c r="E99" s="1">
-        <v>10</v>
+        <v>112</v>
       </c>
       <c r="F99" t="s">
-        <v>59</v>
-      </c>
-      <c r="G99" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I99" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J99" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.541666666664</v>
       </c>
       <c r="K99" s="2">
-        <v>46332.75</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="L99" t="s">
-        <v>49</v>
+        <v>113</v>
       </c>
     </row>
     <row r="100" spans="1:12">
       <c r="A100" t="s">
+        <v>21</v>
+      </c>
+      <c r="B100" t="s">
         <v>22</v>
       </c>
-      <c r="B100" t="s">
-        <v>139</v>
-      </c>
       <c r="C100" t="s">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="D100" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F100" t="s">
-        <v>47</v>
-      </c>
-      <c r="G100" t="s">
-        <v>28</v>
-      </c>
-      <c r="H100" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="I100" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J100" s="2">
-        <v>46331.791666666664</v>
+        <v>46332.875</v>
       </c>
       <c r="K100" s="2">
-        <v>46332.75</v>
+        <v>46334.25</v>
       </c>
       <c r="L100" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="101" spans="1:12">
       <c r="A101" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C101" t="s">
-        <v>101</v>
+        <v>27</v>
       </c>
       <c r="D101" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F101" t="s">
-        <v>104</v>
+        <v>30</v>
       </c>
       <c r="I101" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J101" s="2">
-        <v>46332.056250000001</v>
+        <v>46333</v>
       </c>
       <c r="K101" s="2">
-        <v>46332.597916666666</v>
+        <v>46334</v>
       </c>
       <c r="L101" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="102" spans="1:12">
       <c r="A102" t="s">
+        <v>21</v>
+      </c>
+      <c r="B102" t="s">
         <v>22</v>
       </c>
-      <c r="B102" t="s">
-        <v>78</v>
-      </c>
       <c r="C102" t="s">
-        <v>79</v>
+        <v>27</v>
       </c>
       <c r="D102" t="s">
-        <v>145</v>
+        <v>200</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>201</v>
       </c>
       <c r="F102" t="s">
-        <v>82</v>
+        <v>30</v>
       </c>
       <c r="I102" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J102" s="2">
-        <v>46332.291666666664</v>
+        <v>46333</v>
       </c>
       <c r="K102" s="2">
-        <v>46332.791666666664</v>
+        <v>46334</v>
       </c>
       <c r="L102" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="103" spans="1:12">
@@ -4637,54 +4598,57 @@
         <v>12</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="D103" t="s">
-        <v>199</v>
+        <v>202</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F103" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I103" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J103" s="2">
-        <v>46332.375</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K103" s="2">
-        <v>46333.5</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L103" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104" spans="1:12">
       <c r="A104" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B104" t="s">
-        <v>86</v>
-      </c>
-      <c r="C104" t="s">
-        <v>113</v>
+        <v>55</v>
       </c>
       <c r="D104" t="s">
-        <v>114</v>
+        <v>202</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>203</v>
       </c>
       <c r="F104" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
       <c r="I104" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J104" s="2">
-        <v>46332.541666666664</v>
+        <v>46333.041666666664</v>
       </c>
       <c r="K104" s="2">
-        <v>46333.041666666664</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L104" t="s">
-        <v>115</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105" spans="1:12">
@@ -4692,182 +4656,194 @@
         <v>12</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C105" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="D105" t="s">
-        <v>200</v>
-      </c>
-      <c r="E105" s="1" t="s">
-        <v>201</v>
+        <v>109</v>
       </c>
       <c r="F105" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I105" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J105" s="2">
-        <v>46332.875</v>
+        <v>46333.416666666664</v>
       </c>
       <c r="K105" s="2">
-        <v>46334.25</v>
+        <v>46333.75</v>
       </c>
       <c r="L105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="106" spans="1:12">
       <c r="A106" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C106" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D106" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F106" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I106" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J106" s="2">
-        <v>46333</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K106" s="2">
-        <v>46334</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L106" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="107" spans="1:12">
       <c r="A107" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C107" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="D107" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F107" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="I107" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J107" s="2">
-        <v>46333</v>
+        <v>46333.666666666664</v>
       </c>
       <c r="K107" s="2">
-        <v>46334</v>
+        <v>46335.041666666664</v>
       </c>
       <c r="L107" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="108" spans="1:12">
       <c r="A108" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B108" t="s">
-        <v>60</v>
+        <v>37</v>
+      </c>
+      <c r="C108" t="s">
+        <v>38</v>
       </c>
       <c r="D108" t="s">
-        <v>204</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
+      </c>
+      <c r="E108" s="1">
+        <v>11</v>
       </c>
       <c r="F108" t="s">
-        <v>64</v>
+        <v>54</v>
+      </c>
+      <c r="G108" t="s">
+        <v>18</v>
       </c>
       <c r="I108" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J108" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.25</v>
       </c>
       <c r="K108" s="2">
-        <v>46335.041666666664</v>
+        <v>46334.75</v>
       </c>
       <c r="L108" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109" spans="1:12">
       <c r="A109" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B109" t="s">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="C109" t="s">
+        <v>123</v>
       </c>
       <c r="D109" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F109" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="I109" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J109" s="2">
-        <v>46333.041666666664</v>
+        <v>46334.958333333336</v>
       </c>
       <c r="K109" s="2">
-        <v>46335.041666666664</v>
+        <v>46337.708333333336</v>
       </c>
       <c r="L109" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110" spans="1:12">
       <c r="A110" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B110" t="s">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="C110" t="s">
-        <v>110</v>
+        <v>38</v>
       </c>
       <c r="D110" t="s">
-        <v>111</v>
+        <v>209</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="F110" t="s">
-        <v>82</v>
+        <v>46</v>
+      </c>
+      <c r="G110" t="s">
+        <v>18</v>
       </c>
       <c r="I110" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J110" s="2">
-        <v>46333.416666666664</v>
+        <v>46335.25</v>
       </c>
       <c r="K110" s="2">
-        <v>46333.75</v>
+        <v>46335.75</v>
       </c>
       <c r="L110" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111" spans="1:12">
@@ -4875,31 +4851,34 @@
         <v>12</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D111" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F111" t="s">
-        <v>32</v>
+        <v>46</v>
+      </c>
+      <c r="G111" t="s">
+        <v>18</v>
       </c>
       <c r="I111" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J111" s="2">
-        <v>46333.666666666664</v>
+        <v>46335.791666666664</v>
       </c>
       <c r="K111" s="2">
-        <v>46335.041666666664</v>
+        <v>46336.75</v>
       </c>
       <c r="L111" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="112" spans="1:12">
@@ -4907,325 +4886,313 @@
         <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="D112" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F112" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="I112" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J112" s="2">
-        <v>46333.666666666664</v>
+        <v>46337</v>
       </c>
       <c r="K112" s="2">
-        <v>46335.041666666664</v>
+        <v>46339</v>
       </c>
       <c r="L112" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="113" spans="1:12">
       <c r="A113" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="D113" t="s">
-        <v>208</v>
-      </c>
-      <c r="E113" s="1">
-        <v>11</v>
+        <v>213</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="F113" t="s">
         <v>59</v>
       </c>
-      <c r="G113" t="s">
-        <v>28</v>
-      </c>
       <c r="I113" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J113" s="2">
-        <v>46334.25</v>
+        <v>46337.208333333336</v>
       </c>
       <c r="K113" s="2">
-        <v>46334.75</v>
+        <v>46340.208333333336</v>
       </c>
       <c r="L113" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:12">
       <c r="A114" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B114" t="s">
-        <v>66</v>
+        <v>137</v>
       </c>
       <c r="C114" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="D114" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F114" t="s">
-        <v>52</v>
+        <v>46</v>
+      </c>
+      <c r="G114" t="s">
+        <v>18</v>
       </c>
       <c r="I114" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="J114" s="2">
-        <v>46334.958333333336</v>
+        <v>46337.25</v>
       </c>
       <c r="K114" s="2">
-        <v>46337.708333333336</v>
+        <v>46337.75</v>
       </c>
       <c r="L114" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
     </row>
     <row r="115" spans="1:12">
       <c r="A115" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B115" t="s">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="C115" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D115" t="s">
-        <v>211</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>212</v>
+        <v>76</v>
       </c>
       <c r="F115" t="s">
-        <v>52</v>
-      </c>
-      <c r="G115" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="I115" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J115" s="2">
-        <v>46335.25</v>
+        <v>46337.333333333336</v>
       </c>
       <c r="K115" s="2">
-        <v>46335.75</v>
+        <v>46337.833333333336</v>
       </c>
       <c r="L115" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116" spans="1:12">
       <c r="A116" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B116" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="C116" t="s">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="D116" t="s">
-        <v>211</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>212</v>
+        <v>81</v>
       </c>
       <c r="F116" t="s">
-        <v>52</v>
-      </c>
-      <c r="G116" t="s">
-        <v>28</v>
+        <v>82</v>
       </c>
       <c r="I116" t="s">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="J116" s="2">
-        <v>46335.791666666664</v>
+        <v>46337.625</v>
       </c>
       <c r="K116" s="2">
-        <v>46336.75</v>
+        <v>46338.125</v>
       </c>
       <c r="L116" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="117" spans="1:12">
       <c r="A117" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B117" t="s">
-        <v>60</v>
+        <v>32</v>
       </c>
       <c r="C117" t="s">
-        <v>61</v>
+        <v>33</v>
       </c>
       <c r="D117" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F117" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="I117" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J117" s="2">
-        <v>46337</v>
+        <v>46337.75</v>
       </c>
       <c r="K117" s="2">
-        <v>46339</v>
+        <v>46339.75</v>
       </c>
       <c r="L117" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="118" spans="1:12">
       <c r="A118" t="s">
+        <v>21</v>
+      </c>
+      <c r="B118" t="s">
         <v>22</v>
       </c>
-      <c r="B118" t="s">
-        <v>60</v>
-      </c>
       <c r="C118" t="s">
-        <v>61</v>
+        <v>151</v>
       </c>
       <c r="D118" t="s">
-        <v>215</v>
-      </c>
-      <c r="E118" s="1" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F118" t="s">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="I118" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J118" s="2">
-        <v>46337.208333333336</v>
+        <v>46338.431250000001</v>
       </c>
       <c r="K118" s="2">
-        <v>46340.208333333336</v>
+        <v>46339.472916666666</v>
       </c>
       <c r="L118" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="119" spans="1:12">
       <c r="A119" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B119" t="s">
-        <v>139</v>
+        <v>32</v>
       </c>
       <c r="C119" t="s">
-        <v>44</v>
+        <v>92</v>
       </c>
       <c r="D119" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F119" t="s">
-        <v>52</v>
-      </c>
-      <c r="G119" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="I119" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="J119" s="2">
-        <v>46337.25</v>
+        <v>46338.709027777775</v>
       </c>
       <c r="K119" s="2">
-        <v>46337.75</v>
+        <v>46339.584027777775</v>
       </c>
       <c r="L119" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="120" spans="1:12">
       <c r="A120" t="s">
+        <v>21</v>
+      </c>
+      <c r="B120" t="s">
         <v>22</v>
       </c>
-      <c r="B120" t="s">
-        <v>78</v>
-      </c>
       <c r="C120" t="s">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="D120" t="s">
-        <v>80</v>
+        <v>222</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="F120" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="I120" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J120" s="2">
-        <v>46337.333333333336</v>
+        <v>46338.791666666664</v>
       </c>
       <c r="K120" s="2">
-        <v>46337.833333333336</v>
+        <v>46340.166666666664</v>
       </c>
       <c r="L120" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="121" spans="1:12">
       <c r="A121" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B121" t="s">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C121" t="s">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="D121" t="s">
-        <v>88</v>
+        <v>224</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F121" t="s">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="I121" t="s">
-        <v>91</v>
+        <v>19</v>
       </c>
       <c r="J121" s="2">
-        <v>46337.625</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K121" s="2">
-        <v>46338.125</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L121" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="122" spans="1:12">
@@ -5233,60 +5200,63 @@
         <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="C122" t="s">
-        <v>39</v>
+        <v>62</v>
       </c>
       <c r="D122" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F122" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="I122" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J122" s="2">
-        <v>46337.75</v>
+        <v>46338.958333333336</v>
       </c>
       <c r="K122" s="2">
-        <v>46339.75</v>
+        <v>46342.208333333336</v>
       </c>
       <c r="L122" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="123" spans="1:12">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B123" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C123" t="s">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="D123" t="s">
-        <v>221</v>
+        <v>226</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="F123" t="s">
-        <v>104</v>
+        <v>167</v>
       </c>
       <c r="I123" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J123" s="2">
-        <v>46338.431250000001</v>
+        <v>46339.083333333336</v>
       </c>
       <c r="K123" s="2">
-        <v>46339.472916666666</v>
+        <v>46340.291666666664</v>
       </c>
       <c r="L123" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="124" spans="1:12">
@@ -5294,31 +5264,28 @@
         <v>12</v>
       </c>
       <c r="B124" t="s">
-        <v>38</v>
+        <v>79</v>
       </c>
       <c r="C124" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="D124" t="s">
-        <v>222</v>
-      </c>
-      <c r="E124" s="1" t="s">
-        <v>223</v>
+        <v>112</v>
       </c>
       <c r="F124" t="s">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="I124" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J124" s="2">
-        <v>46338.709027777775</v>
+        <v>46339.541666666664</v>
       </c>
       <c r="K124" s="2">
-        <v>46339.584027777775</v>
+        <v>46340.041666666664</v>
       </c>
       <c r="L124" t="s">
-        <v>21</v>
+        <v>113</v>
       </c>
     </row>
     <row r="125" spans="1:12">
@@ -5326,214 +5293,57 @@
         <v>12</v>
       </c>
       <c r="B125" t="s">
-        <v>13</v>
+        <v>74</v>
       </c>
       <c r="C125" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="D125" t="s">
-        <v>224</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>225</v>
+        <v>114</v>
       </c>
       <c r="F125" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="I125" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J125" s="2">
-        <v>46338.791666666664</v>
+        <v>46339.704861111109</v>
       </c>
       <c r="K125" s="2">
-        <v>46340.166666666664</v>
+        <v>46340.204861111109</v>
       </c>
       <c r="L125" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="126" spans="1:12">
       <c r="A126" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B126" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C126" t="s">
-        <v>67</v>
+        <v>108</v>
       </c>
       <c r="D126" t="s">
-        <v>226</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
       <c r="F126" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="I126" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J126" s="2">
-        <v>46338.958333333336</v>
+        <v>46340.416666666664</v>
       </c>
       <c r="K126" s="2">
-        <v>46342.208333333336</v>
+        <v>46340.75</v>
       </c>
       <c r="L126" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="127" spans="1:12">
-      <c r="A127" t="s">
-        <v>22</v>
-      </c>
-      <c r="B127" t="s">
-        <v>66</v>
-      </c>
-      <c r="C127" t="s">
-        <v>67</v>
-      </c>
-      <c r="D127" t="s">
-        <v>226</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F127" t="s">
-        <v>70</v>
-      </c>
-      <c r="I127" t="s">
-        <v>20</v>
-      </c>
-      <c r="J127" s="2">
-        <v>46338.958333333336</v>
-      </c>
-      <c r="K127" s="2">
-        <v>46342.208333333336</v>
-      </c>
-      <c r="L127" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="128" spans="1:12">
-      <c r="A128" t="s">
-        <v>12</v>
-      </c>
-      <c r="B128" t="s">
-        <v>13</v>
-      </c>
-      <c r="C128" t="s">
-        <v>33</v>
-      </c>
-      <c r="D128" t="s">
-        <v>228</v>
-      </c>
-      <c r="E128" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="F128" t="s">
-        <v>169</v>
-      </c>
-      <c r="I128" t="s">
-        <v>20</v>
-      </c>
-      <c r="J128" s="2">
-        <v>46339.083333333336</v>
-      </c>
-      <c r="K128" s="2">
-        <v>46340.291666666664</v>
-      </c>
-      <c r="L128" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12">
-      <c r="A129" t="s">
-        <v>22</v>
-      </c>
-      <c r="B129" t="s">
-        <v>86</v>
-      </c>
-      <c r="C129" t="s">
-        <v>113</v>
-      </c>
-      <c r="D129" t="s">
-        <v>114</v>
-      </c>
-      <c r="F129" t="s">
-        <v>89</v>
-      </c>
-      <c r="I129" t="s">
-        <v>20</v>
-      </c>
-      <c r="J129" s="2">
-        <v>46339.541666666664</v>
-      </c>
-      <c r="K129" s="2">
-        <v>46340.041666666664</v>
-      </c>
-      <c r="L129" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12">
-      <c r="A130" t="s">
-        <v>22</v>
-      </c>
-      <c r="B130" t="s">
-        <v>78</v>
-      </c>
-      <c r="C130" t="s">
-        <v>79</v>
-      </c>
-      <c r="D130" t="s">
-        <v>116</v>
-      </c>
-      <c r="F130" t="s">
-        <v>82</v>
-      </c>
-      <c r="I130" t="s">
-        <v>20</v>
-      </c>
-      <c r="J130" s="2">
-        <v>46339.704861111109</v>
-      </c>
-      <c r="K130" s="2">
-        <v>46340.204861111109</v>
-      </c>
-      <c r="L130" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12">
-      <c r="A131" t="s">
-        <v>22</v>
-      </c>
-      <c r="B131" t="s">
-        <v>78</v>
-      </c>
-      <c r="C131" t="s">
-        <v>110</v>
-      </c>
-      <c r="D131" t="s">
-        <v>166</v>
-      </c>
-      <c r="F131" t="s">
-        <v>82</v>
-      </c>
-      <c r="I131" t="s">
-        <v>20</v>
-      </c>
-      <c r="J131" s="2">
-        <v>46340.416666666664</v>
-      </c>
-      <c r="K131" s="2">
-        <v>46340.75</v>
-      </c>
-      <c r="L131" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>
@@ -5545,6 +5355,29 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
+  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
+  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
+</scriptIds>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A69D21F4021FF043AD25F7555C34E75C" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ada5bbc6177f3d5462a6af737539cf89">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="169fe4b0-aa95-4062-90d3-821d069df163" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ce4529c032f5bb0135a70d700e81f25b" ns2:_="">
     <xsd:import namespace="169fe4b0-aa95-4062-90d3-821d069df163"/>
@@ -5682,41 +5515,18 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<scriptIds xmlns="http://schemas.microsoft.com/office/extensibility/maker/v1.0" id="script-ids-node-id">
-  <scriptId id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFlYmU2eGFOY1prSzQ4ZzMwOVNrOE5z"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJYSQ36AWKC2TNDYVMQR2CLHJFKM:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQVNodndMS0ZxYlI0cXlFZENXZEpWTUFiamQ5UnJqRGdfNHFKblptMGRDaTk4"/>
-  <scriptId xmlns="" id="ms-officescript%3A%2F%2Fonedrive_business_itemlink%2F01OIHDBJ4MODS6FV673FDIUJAQKFXKCWHG:ms-officescript%3A%2F%2Fonedrive_business_sharinglink%2Fu!aHR0cHM6Ly9wb3J0b2Z0YWNvbWEtbXkuc2hhcmVwb2ludC5jb20vOnU6L3AvamFsYmVyL0lRQ01jT1hpMTlfWlJvb2tFRkZ1b1ZqbUFjcU1YSmx2clY5eXMzT2hWMXFuc2ZZ"/>
-</scriptIds>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{090E8699-A26C-4C66-9B6D-70C00CB2CACE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF03C61-A585-446F-A57D-D94F9FA6CAC8}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4AF8193A-09E0-4717-9CA6-EF5C70C0F2A4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D94EB81F-BDF3-4640-AE12-B1EC3B704FEB}"/>
 </file>